--- a/risk/Risk_Analysis_T3_50yrs_Present_Perfect.xlsx
+++ b/risk/Risk_Analysis_T3_50yrs_Present_Perfect.xlsx
@@ -25,18 +25,12 @@
     <sheet name="Kashmore_Exp" sheetId="16" state="visible" r:id="rId16"/>
     <sheet name="Kashmore_Vul" sheetId="17" state="visible" r:id="rId17"/>
     <sheet name="Kashmore_Dmg" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="Naushahro Feroze_Exp" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="Naushahro Feroze_Vul" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="Naushahro Feroze_Dmg" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="Qambar Shahdadkot_Exp" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="Qambar Shahdadkot_Vul" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="Qambar Shahdadkot_Dmg" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="Shaheed Benazirabad_Exp" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="Shaheed Benazirabad_Vul" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="Shaheed Benazirabad_Dmg" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="Shikarpur_Exp" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet name="Shikarpur_Vul" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet name="Shikarpur_Dmg" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="Qambar Shahdadkot_Exp" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="Qambar Shahdadkot_Vul" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="Qambar Shahdadkot_Dmg" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="Shikarpur_Exp" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="Shikarpur_Vul" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="Shikarpur_Dmg" sheetId="24" state="visible" r:id="rId24"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -9772,7 +9766,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Naushahro Feroze | Mode: Exp</t>
+          <t>Region: Qambar Shahdadkot | Mode: Exp</t>
         </is>
       </c>
     </row>
@@ -9843,37 +9837,37 @@
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>2331.72</v>
+        <v>27809.82</v>
       </c>
       <c r="C4" t="n">
-        <v>599760</v>
+        <v>5349456</v>
       </c>
       <c r="D4" t="n">
-        <v>471240</v>
+        <v>4203144</v>
       </c>
       <c r="E4" t="n">
-        <v>151200</v>
+        <v>1465200</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="G4" t="n">
-        <v>6540</v>
+        <v>81420</v>
       </c>
       <c r="H4" t="n">
-        <v>210</v>
+        <v>8910</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>20220</v>
+        <v>193620</v>
       </c>
     </row>
     <row r="5">
@@ -9881,37 +9875,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>3895.47</v>
+        <v>29507.85</v>
       </c>
       <c r="C5" t="n">
-        <v>685440</v>
+        <v>4608576</v>
       </c>
       <c r="D5" t="n">
-        <v>538560</v>
+        <v>3621024</v>
       </c>
       <c r="E5" t="n">
-        <v>120600</v>
+        <v>1055700</v>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="G5" t="n">
-        <v>8670</v>
+        <v>86370</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>7440</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>20670</v>
+        <v>193410</v>
       </c>
     </row>
     <row r="6">
@@ -9919,37 +9913,37 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>4026.06</v>
+        <v>34814.34</v>
       </c>
       <c r="C6" t="n">
-        <v>422856</v>
+        <v>4942224</v>
       </c>
       <c r="D6" t="n">
-        <v>332244</v>
+        <v>3883176</v>
       </c>
       <c r="E6" t="n">
-        <v>65700</v>
+        <v>929700</v>
       </c>
       <c r="F6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G6" t="n">
-        <v>8370</v>
+        <v>84600</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>12210</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>23220</v>
+        <v>208590</v>
       </c>
     </row>
     <row r="7">
@@ -9957,37 +9951,37 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>2657.97</v>
+        <v>28593.63</v>
       </c>
       <c r="C7" t="n">
-        <v>223272</v>
+        <v>2469600</v>
       </c>
       <c r="D7" t="n">
-        <v>175428</v>
+        <v>1940400</v>
       </c>
       <c r="E7" t="n">
-        <v>37800</v>
+        <v>279900</v>
       </c>
       <c r="F7" t="n">
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>4770</v>
+        <v>66600</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>4470</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>10410</v>
+        <v>137550</v>
       </c>
     </row>
     <row r="8">
@@ -9995,37 +9989,37 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>1382.49</v>
+        <v>23748.66</v>
       </c>
       <c r="C8" t="n">
-        <v>76104</v>
+        <v>1741320</v>
       </c>
       <c r="D8" t="n">
-        <v>59796</v>
+        <v>1368180</v>
       </c>
       <c r="E8" t="n">
-        <v>12600</v>
+        <v>141300</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>2100</v>
+        <v>40050</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>3990</v>
+        <v>84030</v>
       </c>
     </row>
     <row r="9">
@@ -10033,22 +10027,22 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>655.11</v>
+        <v>14494.59</v>
       </c>
       <c r="C9" t="n">
-        <v>19656</v>
+        <v>937440</v>
       </c>
       <c r="D9" t="n">
-        <v>15444</v>
+        <v>736560</v>
       </c>
       <c r="E9" t="n">
-        <v>7200</v>
+        <v>53100</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>810</v>
+        <v>21750</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -10057,13 +10051,13 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>810</v>
+        <v>43200</v>
       </c>
     </row>
     <row r="10">
@@ -10071,22 +10065,22 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>394.47</v>
+        <v>1793.52</v>
       </c>
       <c r="C10" t="n">
-        <v>2016</v>
+        <v>145152</v>
       </c>
       <c r="D10" t="n">
-        <v>1584</v>
+        <v>114048</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>4500</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>420</v>
+        <v>2880</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -10101,7 +10095,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>600</v>
+        <v>10680</v>
       </c>
     </row>
     <row r="11">
@@ -10109,25 +10103,25 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>227.7</v>
+        <v>298.35</v>
       </c>
       <c r="C11" t="n">
-        <v>2520</v>
+        <v>28728</v>
       </c>
       <c r="D11" t="n">
-        <v>1980</v>
+        <v>22572</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>120</v>
+        <v>930</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -10139,7 +10133,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>300</v>
+        <v>4620</v>
       </c>
     </row>
     <row r="12">
@@ -10147,22 +10141,22 @@
         <v>400</v>
       </c>
       <c r="B12" t="n">
-        <v>156.51</v>
+        <v>192.51</v>
       </c>
       <c r="C12" t="n">
-        <v>1512</v>
+        <v>10584</v>
       </c>
       <c r="D12" t="n">
-        <v>1188</v>
+        <v>8316</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>120</v>
+        <v>240</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -10177,7 +10171,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>120</v>
+        <v>3450</v>
       </c>
     </row>
     <row r="13">
@@ -10185,13 +10179,13 @@
         <v>450</v>
       </c>
       <c r="B13" t="n">
-        <v>161.1</v>
+        <v>112.95</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>2520</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>1980</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -10200,7 +10194,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>120</v>
+        <v>240</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -10215,7 +10209,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>150</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="14">
@@ -10223,22 +10217,22 @@
         <v>500</v>
       </c>
       <c r="B14" t="n">
-        <v>61.38</v>
+        <v>13.68</v>
       </c>
       <c r="C14" t="n">
-        <v>504</v>
+        <v>2520</v>
       </c>
       <c r="D14" t="n">
-        <v>396</v>
+        <v>1980</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>450</v>
+        <v>60</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -10253,7 +10247,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>540</v>
+        <v>480</v>
       </c>
     </row>
     <row r="15">
@@ -10261,13 +10255,13 @@
         <v>550</v>
       </c>
       <c r="B15" t="n">
-        <v>4.77</v>
+        <v>17.46</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>1512</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>1188</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -10276,7 +10270,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -10291,7 +10285,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>390</v>
       </c>
     </row>
     <row r="16">
@@ -10299,13 +10293,13 @@
         <v>600</v>
       </c>
       <c r="B16" t="n">
-        <v>0.99</v>
+        <v>10.71</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>1512</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>1188</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -10314,7 +10308,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -10329,7 +10323,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
     </row>
     <row r="17">
@@ -10337,13 +10331,13 @@
         <v>650</v>
       </c>
       <c r="B17" t="n">
-        <v>1.26</v>
+        <v>5.13</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>504</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -10352,7 +10346,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -10367,7 +10361,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
     </row>
     <row r="18">
@@ -10375,13 +10369,13 @@
         <v>700</v>
       </c>
       <c r="B18" t="n">
-        <v>1.35</v>
+        <v>1.71</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>504</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -10390,7 +10384,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -10405,7 +10399,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>660</v>
       </c>
     </row>
     <row r="19">
@@ -10413,13 +10407,13 @@
         <v>750</v>
       </c>
       <c r="B19" t="n">
-        <v>0.18</v>
+        <v>0.09</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>3528</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>2772</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -10428,7 +10422,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>3690</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -10443,7 +10437,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
     </row>
     <row r="20">
@@ -10454,10 +10448,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>2016</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>1584</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -10530,10 +10524,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -10568,10 +10562,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>504</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -10606,10 +10600,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>3024</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>2376</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -11636,7 +11630,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Naushahro Feroze | Mode: Vul</t>
+          <t>Region: Qambar Shahdadkot | Mode: Vul</t>
         </is>
       </c>
     </row>
@@ -11745,37 +11739,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>1752.96</v>
+        <v>13278.53</v>
       </c>
       <c r="C5" t="n">
-        <v>376992</v>
+        <v>2534716.8</v>
       </c>
       <c r="D5" t="n">
-        <v>178263.36</v>
+        <v>1198558.94</v>
       </c>
       <c r="E5" t="n">
-        <v>13302.18</v>
+        <v>116443.71</v>
       </c>
       <c r="F5" t="n">
-        <v>0.06</v>
+        <v>0.42</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>2678.4</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>4340.7</v>
+        <v>40616.1</v>
       </c>
     </row>
     <row r="6">
@@ -11783,37 +11777,37 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>3220.85</v>
+        <v>27851.47</v>
       </c>
       <c r="C6" t="n">
-        <v>380570.4</v>
+        <v>4448001.6</v>
       </c>
       <c r="D6" t="n">
-        <v>168447.71</v>
+        <v>1968770.23</v>
       </c>
       <c r="E6" t="n">
-        <v>11103.3</v>
+        <v>157119.3</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="G6" t="n">
-        <v>418.5</v>
+        <v>4230</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>6959.7</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>8591.4</v>
+        <v>77178.3</v>
       </c>
     </row>
     <row r="7">
@@ -11821,37 +11815,37 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>2525.07</v>
+        <v>27163.95</v>
       </c>
       <c r="C7" t="n">
-        <v>223272</v>
+        <v>2469600</v>
       </c>
       <c r="D7" t="n">
-        <v>111923.06</v>
+        <v>1237975.2</v>
       </c>
       <c r="E7" t="n">
-        <v>8040.06</v>
+        <v>59534.73</v>
       </c>
       <c r="F7" t="n">
         <v>0.6</v>
       </c>
       <c r="G7" t="n">
-        <v>715.5</v>
+        <v>9990</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>3263.1</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>6246</v>
+        <v>82530</v>
       </c>
     </row>
     <row r="8">
@@ -11859,37 +11853,37 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>1382.49</v>
+        <v>23748.66</v>
       </c>
       <c r="C8" t="n">
-        <v>76104</v>
+        <v>1741320</v>
       </c>
       <c r="D8" t="n">
-        <v>44009.86</v>
+        <v>1006980.48</v>
       </c>
       <c r="E8" t="n">
-        <v>3090.78</v>
+        <v>34660.89</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>1365</v>
+        <v>26032.5</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>510</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>2832.9</v>
+        <v>59661.3</v>
       </c>
     </row>
     <row r="9">
@@ -11897,22 +11891,22 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>655.11</v>
+        <v>14494.59</v>
       </c>
       <c r="C9" t="n">
-        <v>19656</v>
+        <v>937440</v>
       </c>
       <c r="D9" t="n">
-        <v>12401.53</v>
+        <v>591457.6800000001</v>
       </c>
       <c r="E9" t="n">
-        <v>1927.44</v>
+        <v>14214.87</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>688.5</v>
+        <v>18487.5</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -11921,13 +11915,13 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>656.1</v>
+        <v>34992</v>
       </c>
     </row>
     <row r="10">
@@ -11935,22 +11929,22 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>394.47</v>
+        <v>1793.52</v>
       </c>
       <c r="C10" t="n">
-        <v>2016</v>
+        <v>145152</v>
       </c>
       <c r="D10" t="n">
-        <v>1378.08</v>
+        <v>99221.75999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>1305</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>420</v>
+        <v>2880</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -11965,7 +11959,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>534</v>
+        <v>9505.200000000001</v>
       </c>
     </row>
     <row r="11">
@@ -11973,25 +11967,25 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>227.7</v>
+        <v>298.35</v>
       </c>
       <c r="C11" t="n">
-        <v>2520</v>
+        <v>28728</v>
       </c>
       <c r="D11" t="n">
-        <v>1779.03</v>
+        <v>20280.94</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>368.82</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>120</v>
+        <v>930</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -12003,7 +11997,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>300</v>
+        <v>4620</v>
       </c>
     </row>
     <row r="12">
@@ -12011,22 +12005,22 @@
         <v>400</v>
       </c>
       <c r="B12" t="n">
-        <v>156.51</v>
+        <v>192.51</v>
       </c>
       <c r="C12" t="n">
-        <v>1512</v>
+        <v>10584</v>
       </c>
       <c r="D12" t="n">
-        <v>1101.28</v>
+        <v>7708.93</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>430.2</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>120</v>
+        <v>240</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -12041,7 +12035,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>120</v>
+        <v>3450</v>
       </c>
     </row>
     <row r="13">
@@ -12049,13 +12043,13 @@
         <v>450</v>
       </c>
       <c r="B13" t="n">
-        <v>161.1</v>
+        <v>112.95</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>2520</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>1880.01</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -12064,7 +12058,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>120</v>
+        <v>240</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -12079,7 +12073,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>150</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="14">
@@ -12087,22 +12081,22 @@
         <v>500</v>
       </c>
       <c r="B14" t="n">
-        <v>61.38</v>
+        <v>13.68</v>
       </c>
       <c r="C14" t="n">
-        <v>504</v>
+        <v>2520</v>
       </c>
       <c r="D14" t="n">
-        <v>384.91</v>
+        <v>1924.56</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>512.37</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>450</v>
+        <v>60</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -12117,7 +12111,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>540</v>
+        <v>480</v>
       </c>
     </row>
     <row r="15">
@@ -12125,13 +12119,13 @@
         <v>550</v>
       </c>
       <c r="B15" t="n">
-        <v>4.77</v>
+        <v>17.46</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>1512</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>1171.37</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -12140,7 +12134,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -12155,7 +12149,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>390</v>
       </c>
     </row>
     <row r="16">
@@ -12163,13 +12157,13 @@
         <v>600</v>
       </c>
       <c r="B16" t="n">
-        <v>0.99</v>
+        <v>10.71</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>1512</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>1188</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -12178,7 +12172,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -12193,7 +12187,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
     </row>
     <row r="17">
@@ -12201,13 +12195,13 @@
         <v>650</v>
       </c>
       <c r="B17" t="n">
-        <v>1.26</v>
+        <v>5.13</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>504</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -12216,7 +12210,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -12231,7 +12225,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
     </row>
     <row r="18">
@@ -12239,13 +12233,13 @@
         <v>700</v>
       </c>
       <c r="B18" t="n">
-        <v>1.35</v>
+        <v>1.71</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>504</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -12254,7 +12248,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -12269,7 +12263,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>660</v>
       </c>
     </row>
     <row r="19">
@@ -12277,13 +12271,13 @@
         <v>750</v>
       </c>
       <c r="B19" t="n">
-        <v>0.18</v>
+        <v>0.09</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>3528</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>2772</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -12292,7 +12286,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>3690</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -12307,7 +12301,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
     </row>
     <row r="20">
@@ -12318,10 +12312,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>2016</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>1584</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -12394,10 +12388,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -12432,10 +12426,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>504</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -12470,10 +12464,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>3024</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>2376</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -12568,7 +12562,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Naushahro Feroze | Mode: Dmg</t>
+          <t>Region: Qambar Shahdadkot | Mode: Dmg</t>
         </is>
       </c>
     </row>
@@ -12677,37 +12671,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>3856515.3</v>
+        <v>29212771.5</v>
       </c>
       <c r="C5" t="n">
-        <v>20734560</v>
+        <v>139409424</v>
       </c>
       <c r="D5" t="n">
-        <v>18063426.27</v>
+        <v>121449977.8</v>
       </c>
       <c r="E5" t="n">
-        <v>2450793.64</v>
+        <v>21453589.13</v>
       </c>
       <c r="F5" t="n">
-        <v>2500.02</v>
+        <v>17500.14</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>740979.36</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>192498.9</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>40889.39</v>
+        <v>382603.66</v>
       </c>
     </row>
     <row r="6">
@@ -12715,37 +12709,37 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>7085865.6</v>
+        <v>61273238.4</v>
       </c>
       <c r="C6" t="n">
-        <v>20931372</v>
+        <v>244640088</v>
       </c>
       <c r="D6" t="n">
-        <v>17068806.25</v>
+        <v>199495487.61</v>
       </c>
       <c r="E6" t="n">
-        <v>2045671.99</v>
+        <v>28947659.83</v>
       </c>
       <c r="F6" t="n">
-        <v>25000.2</v>
+        <v>16666.8</v>
       </c>
       <c r="G6" t="n">
-        <v>7742.25</v>
+        <v>78255</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1925401</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>58333</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>80930.99000000001</v>
+        <v>727019.59</v>
       </c>
     </row>
     <row r="7">
@@ -12753,37 +12747,37 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>5555157.3</v>
+        <v>59760686.7</v>
       </c>
       <c r="C7" t="n">
-        <v>12279960</v>
+        <v>135828000</v>
       </c>
       <c r="D7" t="n">
-        <v>11341164.08</v>
+        <v>125444027.02</v>
       </c>
       <c r="E7" t="n">
-        <v>1481300.65</v>
+        <v>10968678.66</v>
       </c>
       <c r="F7" t="n">
         <v>25000.2</v>
       </c>
       <c r="G7" t="n">
-        <v>13236.75</v>
+        <v>184815</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>902736.61</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>122499.3</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>58837.32</v>
+        <v>777432.6</v>
       </c>
     </row>
     <row r="8">
@@ -12791,37 +12785,37 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>3041478</v>
+        <v>52247052</v>
       </c>
       <c r="C8" t="n">
-        <v>4185720</v>
+        <v>95772600</v>
       </c>
       <c r="D8" t="n">
-        <v>4459518.71</v>
+        <v>102037332.04</v>
       </c>
       <c r="E8" t="n">
-        <v>569445.3100000001</v>
+        <v>6385922.37</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>25252.5</v>
+        <v>481601.25</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>141091.5</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>49583.05</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>26685.92</v>
+        <v>562009.45</v>
       </c>
     </row>
     <row r="9">
@@ -12829,22 +12823,22 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>1441242</v>
+        <v>31888098</v>
       </c>
       <c r="C9" t="n">
-        <v>1081080</v>
+        <v>51559200</v>
       </c>
       <c r="D9" t="n">
-        <v>1256647.24</v>
+        <v>59932406.71</v>
       </c>
       <c r="E9" t="n">
-        <v>355111.55</v>
+        <v>2618947.65</v>
       </c>
       <c r="F9" t="n">
-        <v>41667</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>12737.25</v>
+        <v>342018.75</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -12853,13 +12847,13 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>110832.7</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>6180.46</v>
+        <v>329624.64</v>
       </c>
     </row>
     <row r="10">
@@ -12867,22 +12861,22 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>867834</v>
+        <v>3945744</v>
       </c>
       <c r="C10" t="n">
-        <v>110880</v>
+        <v>7983360</v>
       </c>
       <c r="D10" t="n">
-        <v>139640.85</v>
+        <v>10054140.94</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>240433.2</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>7770</v>
+        <v>53280</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -12897,7 +12891,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>5030.28</v>
+        <v>89538.98</v>
       </c>
     </row>
     <row r="11">
@@ -12905,25 +12899,25 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>500940</v>
+        <v>656370</v>
       </c>
       <c r="C11" t="n">
-        <v>138600</v>
+        <v>1580040</v>
       </c>
       <c r="D11" t="n">
-        <v>180269.11</v>
+        <v>2055067.85</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>67951.39999999999</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>2220</v>
+        <v>17205</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>8299.5</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -12935,7 +12929,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>2826</v>
+        <v>43520.4</v>
       </c>
     </row>
     <row r="12">
@@ -12943,22 +12937,22 @@
         <v>400</v>
       </c>
       <c r="B12" t="n">
-        <v>344322</v>
+        <v>423522</v>
       </c>
       <c r="C12" t="n">
-        <v>83160</v>
+        <v>582120</v>
       </c>
       <c r="D12" t="n">
-        <v>111592.3</v>
+        <v>781146.08</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>79260.05</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>2220</v>
+        <v>4440</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -12973,7 +12967,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>1130.4</v>
+        <v>32499</v>
       </c>
     </row>
     <row r="13">
@@ -12981,13 +12975,13 @@
         <v>450</v>
       </c>
       <c r="B13" t="n">
-        <v>354420</v>
+        <v>248490</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>138600</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>190501.41</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -12996,7 +12990,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>2220</v>
+        <v>4440</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -13011,7 +13005,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1413</v>
+        <v>13564.8</v>
       </c>
     </row>
     <row r="14">
@@ -13019,22 +13013,22 @@
         <v>500</v>
       </c>
       <c r="B14" t="n">
-        <v>135036</v>
+        <v>30096</v>
       </c>
       <c r="C14" t="n">
-        <v>27720</v>
+        <v>138600</v>
       </c>
       <c r="D14" t="n">
-        <v>39003.13</v>
+        <v>195015.66</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>94399.05</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>8325</v>
+        <v>1110</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -13049,7 +13043,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>5086.8</v>
+        <v>4521.6</v>
       </c>
     </row>
     <row r="15">
@@ -13057,13 +13051,13 @@
         <v>550</v>
       </c>
       <c r="B15" t="n">
-        <v>10494</v>
+        <v>38412</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>83160</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>118694.72</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -13072,7 +13066,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>3330</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -13087,7 +13081,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>3673.8</v>
       </c>
     </row>
     <row r="16">
@@ -13095,13 +13089,13 @@
         <v>600</v>
       </c>
       <c r="B16" t="n">
-        <v>2178</v>
+        <v>23562</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>83160</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>120380.04</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -13110,7 +13104,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>1665</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -13125,7 +13119,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2826</v>
       </c>
     </row>
     <row r="17">
@@ -13133,13 +13127,13 @@
         <v>650</v>
       </c>
       <c r="B17" t="n">
-        <v>2772</v>
+        <v>11286</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>27720</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>40126.68</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -13148,7 +13142,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>2775</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -13163,7 +13157,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2826</v>
       </c>
     </row>
     <row r="18">
@@ -13171,13 +13165,13 @@
         <v>700</v>
       </c>
       <c r="B18" t="n">
-        <v>2970</v>
+        <v>3762</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>27720</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>40126.68</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -13186,7 +13180,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>3885</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -13201,7 +13195,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>6217.2</v>
       </c>
     </row>
     <row r="19">
@@ -13209,13 +13203,13 @@
         <v>750</v>
       </c>
       <c r="B19" t="n">
-        <v>396</v>
+        <v>198</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>194040</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>280886.76</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -13224,7 +13218,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>68265</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -13239,7 +13233,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1130.4</v>
       </c>
     </row>
     <row r="20">
@@ -13250,10 +13244,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>110880</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>160506.72</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -13326,10 +13320,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>55440</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>80253.36</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -13364,10 +13358,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>27720</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>40126.68</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -13402,10 +13396,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>166320</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>240760.08</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -13500,7 +13494,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Qambar Shahdadkot | Mode: Exp</t>
+          <t>Region: Shikarpur | Mode: Exp</t>
         </is>
       </c>
     </row>
@@ -13571,37 +13565,37 @@
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>27809.82</v>
+        <v>29688.12</v>
       </c>
       <c r="C4" t="n">
-        <v>5349456</v>
+        <v>2961000</v>
       </c>
       <c r="D4" t="n">
-        <v>4203144</v>
+        <v>2326500</v>
       </c>
       <c r="E4" t="n">
-        <v>1465200</v>
+        <v>919800</v>
       </c>
       <c r="F4" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G4" t="n">
-        <v>81420</v>
+        <v>88950</v>
       </c>
       <c r="H4" t="n">
-        <v>8910</v>
+        <v>10320</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>193620</v>
+        <v>287370</v>
       </c>
     </row>
     <row r="5">
@@ -13609,37 +13603,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>29507.85</v>
+        <v>8563.77</v>
       </c>
       <c r="C5" t="n">
-        <v>4608576</v>
+        <v>580104</v>
       </c>
       <c r="D5" t="n">
-        <v>3621024</v>
+        <v>455796</v>
       </c>
       <c r="E5" t="n">
-        <v>1055700</v>
+        <v>216000</v>
       </c>
       <c r="F5" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="G5" t="n">
-        <v>86370</v>
+        <v>20160</v>
       </c>
       <c r="H5" t="n">
-        <v>7440</v>
+        <v>2040</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>193410</v>
+        <v>85050</v>
       </c>
     </row>
     <row r="6">
@@ -13647,37 +13641,37 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>34814.34</v>
+        <v>757.98</v>
       </c>
       <c r="C6" t="n">
-        <v>4942224</v>
+        <v>65520</v>
       </c>
       <c r="D6" t="n">
-        <v>3883176</v>
+        <v>51480</v>
       </c>
       <c r="E6" t="n">
-        <v>929700</v>
+        <v>20700</v>
       </c>
       <c r="F6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>84600</v>
+        <v>2100</v>
       </c>
       <c r="H6" t="n">
-        <v>12210</v>
+        <v>300</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>208590</v>
+        <v>12780</v>
       </c>
     </row>
     <row r="7">
@@ -13685,37 +13679,37 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>28593.63</v>
+        <v>109.98</v>
       </c>
       <c r="C7" t="n">
-        <v>2469600</v>
+        <v>14112</v>
       </c>
       <c r="D7" t="n">
-        <v>1940400</v>
+        <v>11088</v>
       </c>
       <c r="E7" t="n">
-        <v>279900</v>
+        <v>2700</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>66600</v>
+        <v>60</v>
       </c>
       <c r="H7" t="n">
-        <v>4470</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>137550</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="8">
@@ -13723,37 +13717,37 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>23748.66</v>
+        <v>8.1</v>
       </c>
       <c r="C8" t="n">
-        <v>1741320</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>1368180</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>141300</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>40050</v>
+        <v>60</v>
       </c>
       <c r="H8" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>84030</v>
+        <v>210</v>
       </c>
     </row>
     <row r="9">
@@ -13761,22 +13755,22 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>14494.59</v>
+        <v>0.09</v>
       </c>
       <c r="C9" t="n">
-        <v>937440</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>736560</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>53100</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>21750</v>
+        <v>30</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -13785,13 +13779,13 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>43200</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10">
@@ -13799,22 +13793,22 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>1793.52</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>145152</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>114048</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>4500</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>2880</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -13829,7 +13823,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>10680</v>
+        <v>150</v>
       </c>
     </row>
     <row r="11">
@@ -13837,25 +13831,25 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>298.35</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>28728</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>22572</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>930</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -13867,7 +13861,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>4620</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12">
@@ -13875,22 +13869,22 @@
         <v>400</v>
       </c>
       <c r="B12" t="n">
-        <v>192.51</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10584</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>8316</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -13905,7 +13899,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>3450</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -13913,13 +13907,13 @@
         <v>450</v>
       </c>
       <c r="B13" t="n">
-        <v>112.95</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>2520</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>1980</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -13928,7 +13922,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -13943,7 +13937,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1440</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -13951,22 +13945,22 @@
         <v>500</v>
       </c>
       <c r="B14" t="n">
-        <v>13.68</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>2520</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>1980</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -13981,7 +13975,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>480</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -13989,13 +13983,13 @@
         <v>550</v>
       </c>
       <c r="B15" t="n">
-        <v>17.46</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>1512</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>1188</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -14004,7 +13998,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -14019,7 +14013,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>390</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -14027,13 +14021,13 @@
         <v>600</v>
       </c>
       <c r="B16" t="n">
-        <v>10.71</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>1512</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>1188</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -14042,7 +14036,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -14057,7 +14051,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -14065,13 +14059,13 @@
         <v>650</v>
       </c>
       <c r="B17" t="n">
-        <v>5.13</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -14080,7 +14074,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -14095,7 +14089,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -14103,13 +14097,13 @@
         <v>700</v>
       </c>
       <c r="B18" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -14118,7 +14112,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -14133,7 +14127,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>660</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -14141,13 +14135,13 @@
         <v>750</v>
       </c>
       <c r="B19" t="n">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>3528</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>2772</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -14156,7 +14150,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>3690</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -14171,7 +14165,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -14182,10 +14176,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>2016</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>1584</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -14258,10 +14252,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -14296,10 +14290,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -14334,10 +14328,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>3024</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>2376</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -14432,7 +14426,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Qambar Shahdadkot | Mode: Vul</t>
+          <t>Region: Shikarpur | Mode: Vul</t>
         </is>
       </c>
     </row>
@@ -14541,37 +14535,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>13278.53</v>
+        <v>3853.7</v>
       </c>
       <c r="C5" t="n">
-        <v>2534716.8</v>
+        <v>319057.2</v>
       </c>
       <c r="D5" t="n">
-        <v>1198558.94</v>
+        <v>150868.48</v>
       </c>
       <c r="E5" t="n">
-        <v>116443.71</v>
+        <v>23824.8</v>
       </c>
       <c r="F5" t="n">
-        <v>0.42</v>
+        <v>0.14</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>2678.4</v>
+        <v>734.4</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>40616.1</v>
+        <v>17860.5</v>
       </c>
     </row>
     <row r="6">
@@ -14579,37 +14573,37 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>27851.47</v>
+        <v>606.38</v>
       </c>
       <c r="C6" t="n">
-        <v>4448001.6</v>
+        <v>58968</v>
       </c>
       <c r="D6" t="n">
-        <v>1968770.23</v>
+        <v>26100.36</v>
       </c>
       <c r="E6" t="n">
-        <v>157119.3</v>
+        <v>3498.3</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>4230</v>
+        <v>105</v>
       </c>
       <c r="H6" t="n">
-        <v>6959.7</v>
+        <v>171</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>77178.3</v>
+        <v>4728.6</v>
       </c>
     </row>
     <row r="7">
@@ -14617,37 +14611,37 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>27163.95</v>
+        <v>104.48</v>
       </c>
       <c r="C7" t="n">
-        <v>2469600</v>
+        <v>14112</v>
       </c>
       <c r="D7" t="n">
-        <v>1237975.2</v>
+        <v>7074.14</v>
       </c>
       <c r="E7" t="n">
-        <v>59534.73</v>
+        <v>574.29</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>9990</v>
+        <v>9</v>
       </c>
       <c r="H7" t="n">
-        <v>3263.1</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>82530</v>
+        <v>738</v>
       </c>
     </row>
     <row r="8">
@@ -14655,37 +14649,37 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>23748.66</v>
+        <v>8.1</v>
       </c>
       <c r="C8" t="n">
-        <v>1741320</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>1006980.48</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>34660.89</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>26032.5</v>
+        <v>39</v>
       </c>
       <c r="H8" t="n">
-        <v>510</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0.85</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>59661.3</v>
+        <v>149.1</v>
       </c>
     </row>
     <row r="9">
@@ -14693,22 +14687,22 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>14494.59</v>
+        <v>0.09</v>
       </c>
       <c r="C9" t="n">
-        <v>937440</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>591457.6800000001</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>14214.87</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>18487.5</v>
+        <v>25.5</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -14717,13 +14711,13 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>34992</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="10">
@@ -14731,22 +14725,22 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>1793.52</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>145152</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>99221.75999999999</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>1305</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>2880</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -14761,7 +14755,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>9505.200000000001</v>
+        <v>133.5</v>
       </c>
     </row>
     <row r="11">
@@ -14769,25 +14763,25 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>298.35</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>28728</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>20280.94</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>368.82</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>930</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -14799,7 +14793,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>4620</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12">
@@ -14807,22 +14801,22 @@
         <v>400</v>
       </c>
       <c r="B12" t="n">
-        <v>192.51</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10584</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>7708.93</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>430.2</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -14837,7 +14831,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>3450</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -14845,13 +14839,13 @@
         <v>450</v>
       </c>
       <c r="B13" t="n">
-        <v>112.95</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>2520</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>1880.01</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -14860,7 +14854,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -14875,7 +14869,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1440</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -14883,22 +14877,22 @@
         <v>500</v>
       </c>
       <c r="B14" t="n">
-        <v>13.68</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>2520</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>1924.56</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>512.37</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -14913,7 +14907,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>480</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -14921,13 +14915,13 @@
         <v>550</v>
       </c>
       <c r="B15" t="n">
-        <v>17.46</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>1512</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>1171.37</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -14936,7 +14930,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -14951,7 +14945,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>390</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -14959,13 +14953,13 @@
         <v>600</v>
       </c>
       <c r="B16" t="n">
-        <v>10.71</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>1512</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>1188</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -14974,7 +14968,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -14989,7 +14983,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -14997,13 +14991,13 @@
         <v>650</v>
       </c>
       <c r="B17" t="n">
-        <v>5.13</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -15012,7 +15006,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -15027,7 +15021,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -15035,13 +15029,13 @@
         <v>700</v>
       </c>
       <c r="B18" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -15050,7 +15044,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -15065,7 +15059,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>660</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -15073,13 +15067,13 @@
         <v>750</v>
       </c>
       <c r="B19" t="n">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>3528</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>2772</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -15088,7 +15082,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>3690</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -15103,7 +15097,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -15114,10 +15108,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>2016</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>1584</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -15190,10 +15184,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -15228,10 +15222,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -15266,10 +15260,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>3024</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>2376</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -15364,7 +15358,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Qambar Shahdadkot | Mode: Dmg</t>
+          <t>Region: Shikarpur | Mode: Dmg</t>
         </is>
       </c>
     </row>
@@ -15473,37 +15467,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>29212771.5</v>
+        <v>8478132.300000001</v>
       </c>
       <c r="C5" t="n">
-        <v>139409424</v>
+        <v>17548146</v>
       </c>
       <c r="D5" t="n">
-        <v>121449977.8</v>
+        <v>15287502.67</v>
       </c>
       <c r="E5" t="n">
-        <v>21453589.13</v>
+        <v>4389481.15</v>
       </c>
       <c r="F5" t="n">
-        <v>17500.14</v>
+        <v>5833.38</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>740979.36</v>
+        <v>203171.76</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>192498.9</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>382603.66</v>
+        <v>168245.91</v>
       </c>
     </row>
     <row r="6">
@@ -15511,37 +15505,37 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>61273238.4</v>
+        <v>1334044.8</v>
       </c>
       <c r="C6" t="n">
-        <v>244640088</v>
+        <v>3243240</v>
       </c>
       <c r="D6" t="n">
-        <v>199495487.61</v>
+        <v>2644749.48</v>
       </c>
       <c r="E6" t="n">
-        <v>28947659.83</v>
+        <v>644526.79</v>
       </c>
       <c r="F6" t="n">
-        <v>16666.8</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>78255</v>
+        <v>1942.5</v>
       </c>
       <c r="H6" t="n">
-        <v>1925401</v>
+        <v>47307.15</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>58333</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>727019.59</v>
+        <v>44543.41</v>
       </c>
     </row>
     <row r="7">
@@ -15549,37 +15543,37 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>59760686.7</v>
+        <v>229858.2</v>
       </c>
       <c r="C7" t="n">
-        <v>135828000</v>
+        <v>776160</v>
       </c>
       <c r="D7" t="n">
-        <v>125444027.02</v>
+        <v>716823.01</v>
       </c>
       <c r="E7" t="n">
-        <v>10968678.66</v>
+        <v>105807.19</v>
       </c>
       <c r="F7" t="n">
-        <v>25000.2</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>184815</v>
+        <v>166.5</v>
       </c>
       <c r="H7" t="n">
-        <v>902736.61</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>122499.3</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>777432.6</v>
+        <v>6951.96</v>
       </c>
     </row>
     <row r="8">
@@ -15587,37 +15581,37 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>52247052</v>
+        <v>17820</v>
       </c>
       <c r="C8" t="n">
-        <v>95772600</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>102037332.04</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>6385922.37</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>481601.25</v>
+        <v>721.5</v>
       </c>
       <c r="H8" t="n">
-        <v>141091.5</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>49583.05</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>562009.45</v>
+        <v>1404.52</v>
       </c>
     </row>
     <row r="9">
@@ -15625,22 +15619,22 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>31888098</v>
+        <v>198</v>
       </c>
       <c r="C9" t="n">
-        <v>51559200</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>59932406.71</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>2618947.65</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>342018.75</v>
+        <v>471.75</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -15649,13 +15643,13 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>110832.7</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>329624.64</v>
+        <v>457.81</v>
       </c>
     </row>
     <row r="10">
@@ -15663,22 +15657,22 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>3945744</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>7983360</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>10054140.94</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>240433.2</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>53280</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -15693,7 +15687,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>89538.98</v>
+        <v>1257.57</v>
       </c>
     </row>
     <row r="11">
@@ -15701,25 +15695,25 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>656370</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>1580040</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>2055067.85</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>67951.39999999999</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>17205</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>8299.5</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -15731,4667 +15725,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>43520.4</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>423522</v>
-      </c>
-      <c r="C12" t="n">
-        <v>582120</v>
-      </c>
-      <c r="D12" t="n">
-        <v>781146.08</v>
-      </c>
-      <c r="E12" t="n">
-        <v>79260.05</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>4440</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>32499</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>248490</v>
-      </c>
-      <c r="C13" t="n">
-        <v>138600</v>
-      </c>
-      <c r="D13" t="n">
-        <v>190501.41</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>4440</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>13564.8</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>30096</v>
-      </c>
-      <c r="C14" t="n">
-        <v>138600</v>
-      </c>
-      <c r="D14" t="n">
-        <v>195015.66</v>
-      </c>
-      <c r="E14" t="n">
-        <v>94399.05</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>1110</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>4521.6</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>38412</v>
-      </c>
-      <c r="C15" t="n">
-        <v>83160</v>
-      </c>
-      <c r="D15" t="n">
-        <v>118694.72</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>3330</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>3673.8</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>23562</v>
-      </c>
-      <c r="C16" t="n">
-        <v>83160</v>
-      </c>
-      <c r="D16" t="n">
-        <v>120380.04</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>1665</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>2826</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>11286</v>
-      </c>
-      <c r="C17" t="n">
-        <v>27720</v>
-      </c>
-      <c r="D17" t="n">
-        <v>40126.68</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>2775</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>2826</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>3762</v>
-      </c>
-      <c r="C18" t="n">
-        <v>27720</v>
-      </c>
-      <c r="D18" t="n">
-        <v>40126.68</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>3885</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>6217.2</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>198</v>
-      </c>
-      <c r="C19" t="n">
-        <v>194040</v>
-      </c>
-      <c r="D19" t="n">
-        <v>280886.76</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>68265</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1130.4</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>110880</v>
-      </c>
-      <c r="D20" t="n">
-        <v>160506.72</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>55440</v>
-      </c>
-      <c r="D22" t="n">
-        <v>80253.36</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>27720</v>
-      </c>
-      <c r="D23" t="n">
-        <v>40126.68</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>166320</v>
-      </c>
-      <c r="D24" t="n">
-        <v>240760.08</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shaheed Benazirabad | Mode: Exp</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>4183.56</v>
-      </c>
-      <c r="C4" t="n">
-        <v>1111320</v>
-      </c>
-      <c r="D4" t="n">
-        <v>873180</v>
-      </c>
-      <c r="E4" t="n">
-        <v>338400</v>
-      </c>
-      <c r="F4" t="n">
-        <v>10</v>
-      </c>
-      <c r="G4" t="n">
-        <v>14910</v>
-      </c>
-      <c r="H4" t="n">
-        <v>3630</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>2</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>37050</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>5480.73</v>
-      </c>
-      <c r="C5" t="n">
-        <v>856800</v>
-      </c>
-      <c r="D5" t="n">
-        <v>673200</v>
-      </c>
-      <c r="E5" t="n">
-        <v>190800</v>
-      </c>
-      <c r="F5" t="n">
-        <v>8</v>
-      </c>
-      <c r="G5" t="n">
-        <v>17130</v>
-      </c>
-      <c r="H5" t="n">
-        <v>2490</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>34350</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>5154.93</v>
-      </c>
-      <c r="C6" t="n">
-        <v>543312</v>
-      </c>
-      <c r="D6" t="n">
-        <v>426888</v>
-      </c>
-      <c r="E6" t="n">
-        <v>105300</v>
-      </c>
-      <c r="F6" t="n">
-        <v>4</v>
-      </c>
-      <c r="G6" t="n">
-        <v>8430</v>
-      </c>
-      <c r="H6" t="n">
-        <v>930</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>21540</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>4817.52</v>
-      </c>
-      <c r="C7" t="n">
-        <v>288792</v>
-      </c>
-      <c r="D7" t="n">
-        <v>226908</v>
-      </c>
-      <c r="E7" t="n">
-        <v>54900</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>4890</v>
-      </c>
-      <c r="H7" t="n">
-        <v>30</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>14820</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>4319.37</v>
-      </c>
-      <c r="C8" t="n">
-        <v>221256</v>
-      </c>
-      <c r="D8" t="n">
-        <v>173844</v>
-      </c>
-      <c r="E8" t="n">
-        <v>31500</v>
-      </c>
-      <c r="F8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" t="n">
-        <v>4080</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>13590</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>2830.41</v>
-      </c>
-      <c r="C9" t="n">
-        <v>98280</v>
-      </c>
-      <c r="D9" t="n">
-        <v>77220</v>
-      </c>
-      <c r="E9" t="n">
-        <v>4500</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" t="n">
-        <v>3180</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>6960</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>2043.9</v>
-      </c>
-      <c r="C10" t="n">
-        <v>37296</v>
-      </c>
-      <c r="D10" t="n">
-        <v>29304</v>
-      </c>
-      <c r="E10" t="n">
-        <v>900</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>510</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1560</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>1087.83</v>
-      </c>
-      <c r="C11" t="n">
-        <v>10080</v>
-      </c>
-      <c r="D11" t="n">
-        <v>7920</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>300</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>674.64</v>
-      </c>
-      <c r="C12" t="n">
-        <v>4032</v>
-      </c>
-      <c r="D12" t="n">
-        <v>3168</v>
-      </c>
-      <c r="E12" t="n">
-        <v>900</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>413.01</v>
-      </c>
-      <c r="C13" t="n">
-        <v>2520</v>
-      </c>
-      <c r="D13" t="n">
-        <v>1980</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>361.8</v>
-      </c>
-      <c r="C14" t="n">
-        <v>2016</v>
-      </c>
-      <c r="D14" t="n">
-        <v>1584</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>333.72</v>
-      </c>
-      <c r="C15" t="n">
-        <v>1008</v>
-      </c>
-      <c r="D15" t="n">
-        <v>792</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>381.06</v>
-      </c>
-      <c r="C16" t="n">
-        <v>1008</v>
-      </c>
-      <c r="D16" t="n">
-        <v>792</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>127.17</v>
-      </c>
-      <c r="C17" t="n">
-        <v>1008</v>
-      </c>
-      <c r="D17" t="n">
-        <v>792</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>37.71</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>12.87</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shaheed Benazirabad | Mode: Vul</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>2466.33</v>
-      </c>
-      <c r="C5" t="n">
-        <v>471240</v>
-      </c>
-      <c r="D5" t="n">
-        <v>222829.2</v>
-      </c>
-      <c r="E5" t="n">
-        <v>21045.24</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>896.4</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>7213.5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>4123.94</v>
-      </c>
-      <c r="C6" t="n">
-        <v>488980.8</v>
-      </c>
-      <c r="D6" t="n">
-        <v>216432.22</v>
-      </c>
-      <c r="E6" t="n">
-        <v>17795.7</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G6" t="n">
-        <v>421.5</v>
-      </c>
-      <c r="H6" t="n">
-        <v>530.1</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>7969.8</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>4576.64</v>
-      </c>
-      <c r="C7" t="n">
-        <v>288792</v>
-      </c>
-      <c r="D7" t="n">
-        <v>144767.3</v>
-      </c>
-      <c r="E7" t="n">
-        <v>11677.23</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>733.5</v>
-      </c>
-      <c r="H7" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>8892</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>4319.37</v>
-      </c>
-      <c r="C8" t="n">
-        <v>221256</v>
-      </c>
-      <c r="D8" t="n">
-        <v>127949.18</v>
-      </c>
-      <c r="E8" t="n">
-        <v>7726.95</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="G8" t="n">
-        <v>2652</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>9648.9</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>2830.41</v>
-      </c>
-      <c r="C9" t="n">
-        <v>98280</v>
-      </c>
-      <c r="D9" t="n">
-        <v>62007.66</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1204.65</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" t="n">
-        <v>2703</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>5637.6</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>2043.9</v>
-      </c>
-      <c r="C10" t="n">
-        <v>37296</v>
-      </c>
-      <c r="D10" t="n">
-        <v>25494.48</v>
-      </c>
-      <c r="E10" t="n">
-        <v>261</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>510</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1388.4</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>1087.83</v>
-      </c>
-      <c r="C11" t="n">
-        <v>10080</v>
-      </c>
-      <c r="D11" t="n">
-        <v>7116.12</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>300</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>674.64</v>
-      </c>
-      <c r="C12" t="n">
-        <v>4032</v>
-      </c>
-      <c r="D12" t="n">
-        <v>2936.74</v>
-      </c>
-      <c r="E12" t="n">
-        <v>430.2</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>413.01</v>
-      </c>
-      <c r="C13" t="n">
-        <v>2520</v>
-      </c>
-      <c r="D13" t="n">
-        <v>1880.01</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>361.8</v>
-      </c>
-      <c r="C14" t="n">
-        <v>2016</v>
-      </c>
-      <c r="D14" t="n">
-        <v>1539.65</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>333.72</v>
-      </c>
-      <c r="C15" t="n">
-        <v>1008</v>
-      </c>
-      <c r="D15" t="n">
-        <v>780.91</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>381.06</v>
-      </c>
-      <c r="C16" t="n">
-        <v>1008</v>
-      </c>
-      <c r="D16" t="n">
-        <v>792</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>127.17</v>
-      </c>
-      <c r="C17" t="n">
-        <v>1008</v>
-      </c>
-      <c r="D17" t="n">
-        <v>792</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>37.71</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>12.87</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shaheed Benazirabad | Mode: Dmg</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>5425922.7</v>
-      </c>
-      <c r="C5" t="n">
-        <v>25918200</v>
-      </c>
-      <c r="D5" t="n">
-        <v>22579282.84</v>
-      </c>
-      <c r="E5" t="n">
-        <v>3877375.02</v>
-      </c>
-      <c r="F5" t="n">
-        <v>6666.72</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>247989.06</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>17499.9</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>67951.17</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>9072676.800000001</v>
-      </c>
-      <c r="C6" t="n">
-        <v>26893944</v>
-      </c>
-      <c r="D6" t="n">
-        <v>21931076.45</v>
-      </c>
-      <c r="E6" t="n">
-        <v>3278679.77</v>
-      </c>
-      <c r="F6" t="n">
-        <v>16666.8</v>
-      </c>
-      <c r="G6" t="n">
-        <v>7797.75</v>
-      </c>
-      <c r="H6" t="n">
-        <v>146652.16</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>75075.52</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>10068616.8</v>
-      </c>
-      <c r="C7" t="n">
-        <v>15883560</v>
-      </c>
-      <c r="D7" t="n">
-        <v>14669270.91</v>
-      </c>
-      <c r="E7" t="n">
-        <v>2151412.86</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>13569.75</v>
-      </c>
-      <c r="H7" t="n">
-        <v>6058.63</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>83762.64</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>9502614</v>
-      </c>
-      <c r="C8" t="n">
-        <v>12169080</v>
-      </c>
-      <c r="D8" t="n">
-        <v>12965090.81</v>
-      </c>
-      <c r="E8" t="n">
-        <v>1423613.27</v>
-      </c>
-      <c r="F8" t="n">
-        <v>39583.65</v>
-      </c>
-      <c r="G8" t="n">
-        <v>49062</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>90892.64</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>6226902</v>
-      </c>
-      <c r="C9" t="n">
-        <v>5405400</v>
-      </c>
-      <c r="D9" t="n">
-        <v>6283236.19</v>
-      </c>
-      <c r="E9" t="n">
-        <v>221944.72</v>
-      </c>
-      <c r="F9" t="n">
-        <v>41667</v>
-      </c>
-      <c r="G9" t="n">
-        <v>50005.5</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>53106.19</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>4496580</v>
-      </c>
-      <c r="C10" t="n">
-        <v>2051280</v>
-      </c>
-      <c r="D10" t="n">
-        <v>2583355.66</v>
-      </c>
-      <c r="E10" t="n">
-        <v>48086.64</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>9435</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>13078.73</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>2393226</v>
-      </c>
-      <c r="C11" t="n">
-        <v>554400</v>
-      </c>
-      <c r="D11" t="n">
-        <v>721076.4399999999</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>5550</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>3391.2</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>1484208</v>
-      </c>
-      <c r="C12" t="n">
-        <v>221760</v>
-      </c>
-      <c r="D12" t="n">
-        <v>297579.46</v>
-      </c>
-      <c r="E12" t="n">
-        <v>79260.05</v>
-      </c>
-      <c r="F12" t="n">
-        <v>41667</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>908622</v>
-      </c>
-      <c r="C13" t="n">
-        <v>138600</v>
-      </c>
-      <c r="D13" t="n">
-        <v>190501.41</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>795960</v>
-      </c>
-      <c r="C14" t="n">
-        <v>110880</v>
-      </c>
-      <c r="D14" t="n">
-        <v>156012.53</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>41667</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>734184</v>
-      </c>
-      <c r="C15" t="n">
-        <v>55440</v>
-      </c>
-      <c r="D15" t="n">
-        <v>79129.81</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>838332</v>
-      </c>
-      <c r="C16" t="n">
-        <v>55440</v>
-      </c>
-      <c r="D16" t="n">
-        <v>80253.36</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>279774</v>
-      </c>
-      <c r="C17" t="n">
-        <v>55440</v>
-      </c>
-      <c r="D17" t="n">
-        <v>80253.36</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>82962</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>28314</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shikarpur | Mode: Exp</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>29688.12</v>
-      </c>
-      <c r="C4" t="n">
-        <v>2961000</v>
-      </c>
-      <c r="D4" t="n">
-        <v>2326500</v>
-      </c>
-      <c r="E4" t="n">
-        <v>919800</v>
-      </c>
-      <c r="F4" t="n">
-        <v>33</v>
-      </c>
-      <c r="G4" t="n">
-        <v>88950</v>
-      </c>
-      <c r="H4" t="n">
-        <v>10320</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>4</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>287370</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>8563.77</v>
-      </c>
-      <c r="C5" t="n">
-        <v>580104</v>
-      </c>
-      <c r="D5" t="n">
-        <v>455796</v>
-      </c>
-      <c r="E5" t="n">
-        <v>216000</v>
-      </c>
-      <c r="F5" t="n">
-        <v>7</v>
-      </c>
-      <c r="G5" t="n">
-        <v>20160</v>
-      </c>
-      <c r="H5" t="n">
-        <v>2040</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>85050</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>757.98</v>
-      </c>
-      <c r="C6" t="n">
-        <v>65520</v>
-      </c>
-      <c r="D6" t="n">
-        <v>51480</v>
-      </c>
-      <c r="E6" t="n">
-        <v>20700</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>2100</v>
-      </c>
-      <c r="H6" t="n">
-        <v>300</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>12780</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>109.98</v>
-      </c>
-      <c r="C7" t="n">
-        <v>14112</v>
-      </c>
-      <c r="D7" t="n">
-        <v>11088</v>
-      </c>
-      <c r="E7" t="n">
-        <v>2700</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>60</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1230</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>60</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>30</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shikarpur | Mode: Vul</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>3853.7</v>
-      </c>
-      <c r="C5" t="n">
-        <v>319057.2</v>
-      </c>
-      <c r="D5" t="n">
-        <v>150868.48</v>
-      </c>
-      <c r="E5" t="n">
-        <v>23824.8</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>734.4</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>17860.5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>606.38</v>
-      </c>
-      <c r="C6" t="n">
-        <v>58968</v>
-      </c>
-      <c r="D6" t="n">
-        <v>26100.36</v>
-      </c>
-      <c r="E6" t="n">
-        <v>3498.3</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>105</v>
-      </c>
-      <c r="H6" t="n">
-        <v>171</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>4728.6</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>104.48</v>
-      </c>
-      <c r="C7" t="n">
-        <v>14112</v>
-      </c>
-      <c r="D7" t="n">
-        <v>7074.14</v>
-      </c>
-      <c r="E7" t="n">
-        <v>574.29</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>9</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>39</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>149.1</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>48.6</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>133.5</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>90</v>
+        <v>847.8</v>
       </c>
     </row>
     <row r="12">
@@ -21876,938 +17210,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shikarpur | Mode: Dmg</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>8478132.300000001</v>
-      </c>
-      <c r="C5" t="n">
-        <v>17548146</v>
-      </c>
-      <c r="D5" t="n">
-        <v>15287502.67</v>
-      </c>
-      <c r="E5" t="n">
-        <v>4389481.15</v>
-      </c>
-      <c r="F5" t="n">
-        <v>5833.38</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>203171.76</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>168245.91</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>1334044.8</v>
-      </c>
-      <c r="C6" t="n">
-        <v>3243240</v>
-      </c>
-      <c r="D6" t="n">
-        <v>2644749.48</v>
-      </c>
-      <c r="E6" t="n">
-        <v>644526.79</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1942.5</v>
-      </c>
-      <c r="H6" t="n">
-        <v>47307.15</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>44543.41</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>229858.2</v>
-      </c>
-      <c r="C7" t="n">
-        <v>776160</v>
-      </c>
-      <c r="D7" t="n">
-        <v>716823.01</v>
-      </c>
-      <c r="E7" t="n">
-        <v>105807.19</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>166.5</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>6951.96</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>17820</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>721.5</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1404.52</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>198</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>471.75</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>457.81</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1257.57</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>847.8</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/risk/Risk_Analysis_T3_50yrs_Present_Perfect.xlsx
+++ b/risk/Risk_Analysis_T3_50yrs_Present_Perfect.xlsx
@@ -538,7 +538,7 @@
         <v>68100</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J4" t="n">
         <v>40</v>
@@ -576,7 +576,7 @@
         <v>48750</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J5" t="n">
         <v>26</v>
@@ -614,7 +614,7 @@
         <v>56340</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
         <v>10</v>
@@ -652,7 +652,7 @@
         <v>30060</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J7" t="n">
         <v>14</v>
@@ -690,7 +690,7 @@
         <v>8040</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
         <v>5</v>
@@ -766,7 +766,7 @@
         <v>4890</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J10" t="n">
         <v>3</v>
@@ -880,7 +880,7 @@
         <v>840</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1622,7 +1622,7 @@
         <v>3750</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
         <v>1</v>
@@ -1698,7 +1698,7 @@
         <v>4530</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
@@ -1812,7 +1812,7 @@
         <v>840</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -2554,7 +2554,7 @@
         <v>3187.5</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>0.72</v>
       </c>
       <c r="J8" t="n">
         <v>0.85</v>
@@ -2630,7 +2630,7 @@
         <v>4530</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
@@ -2744,7 +2744,7 @@
         <v>840</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -3486,7 +3486,7 @@
         <v>881821.87</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>275997.6</v>
       </c>
       <c r="J8" t="n">
         <v>49583.05</v>
@@ -3562,7 +3562,7 @@
         <v>1253224.5</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>735993.6</v>
       </c>
       <c r="J10" t="n">
         <v>58333</v>
@@ -3676,7 +3676,7 @@
         <v>232386</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>383330</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -9858,7 +9858,7 @@
         <v>8910</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J4" t="n">
         <v>9</v>
@@ -9896,7 +9896,7 @@
         <v>7440</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J5" t="n">
         <v>11</v>
@@ -9934,7 +9934,7 @@
         <v>12210</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
         <v>2</v>
@@ -9972,7 +9972,7 @@
         <v>4470</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J7" t="n">
         <v>3</v>
@@ -10086,7 +10086,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -10828,7 +10828,7 @@
         <v>17550</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="J5" t="n">
         <v>7.8</v>
@@ -10866,7 +10866,7 @@
         <v>32113.8</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="J6" t="n">
         <v>5</v>
@@ -10904,7 +10904,7 @@
         <v>21943.8</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="J7" t="n">
         <v>9.800000000000001</v>
@@ -10942,7 +10942,7 @@
         <v>6834</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>0.72</v>
       </c>
       <c r="J8" t="n">
         <v>4.25</v>
@@ -11018,7 +11018,7 @@
         <v>4890</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="J10" t="n">
         <v>3</v>
@@ -11132,7 +11132,7 @@
         <v>840</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -11760,7 +11760,7 @@
         <v>2678.4</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="J5" t="n">
         <v>3.3</v>
@@ -11798,7 +11798,7 @@
         <v>6959.7</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -11836,7 +11836,7 @@
         <v>3263.1</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="J7" t="n">
         <v>2.1</v>
@@ -11950,7 +11950,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -12692,7 +12692,7 @@
         <v>740979.36</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>172498.5</v>
       </c>
       <c r="J5" t="n">
         <v>192498.9</v>
@@ -12730,7 +12730,7 @@
         <v>1925401</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>134165.5</v>
       </c>
       <c r="J6" t="n">
         <v>58333</v>
@@ -12768,7 +12768,7 @@
         <v>902736.61</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>632494.5</v>
       </c>
       <c r="J7" t="n">
         <v>122499.3</v>
@@ -12882,7 +12882,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>367996.8</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -13586,7 +13586,7 @@
         <v>10320</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>4</v>
@@ -16420,7 +16420,7 @@
         <v>4855207.5</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>172498.5</v>
       </c>
       <c r="J5" t="n">
         <v>454997.4</v>
@@ -16458,7 +16458,7 @@
         <v>8884282.77</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>134165.5</v>
       </c>
       <c r="J6" t="n">
         <v>291665</v>
@@ -16496,7 +16496,7 @@
         <v>6070752.27</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>843326</v>
       </c>
       <c r="J7" t="n">
         <v>571663.4</v>
@@ -16534,7 +16534,7 @@
         <v>1890626.1</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>275997.6</v>
       </c>
       <c r="J8" t="n">
         <v>247915.25</v>
@@ -16610,7 +16610,7 @@
         <v>1352818.5</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1103990.4</v>
       </c>
       <c r="J10" t="n">
         <v>174999</v>
@@ -16724,7 +16724,7 @@
         <v>232386</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>383330</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -17314,7 +17314,7 @@
         <v>8580</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J4" t="n">
         <v>2</v>
@@ -17428,7 +17428,7 @@
         <v>18450</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
         <v>9</v>
@@ -18360,7 +18360,7 @@
         <v>13468.5</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>0.55</v>
       </c>
       <c r="J7" t="n">
         <v>6.3</v>
@@ -19292,7 +19292,7 @@
         <v>3726060.52</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>210831.5</v>
       </c>
       <c r="J7" t="n">
         <v>367497.9</v>
@@ -20110,7 +20110,7 @@
         <v>24660</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J4" t="n">
         <v>12</v>

--- a/risk/Risk_Analysis_T3_50yrs_Present_Perfect.xlsx
+++ b/risk/Risk_Analysis_T3_50yrs_Present_Perfect.xlsx
@@ -544,7 +544,7 @@
         <v>40</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1023</v>
       </c>
       <c r="L4" t="n">
         <v>1353630</v>
@@ -582,7 +582,7 @@
         <v>26</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>577</v>
       </c>
       <c r="L5" t="n">
         <v>855360</v>
@@ -620,7 +620,7 @@
         <v>10</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>509</v>
       </c>
       <c r="L6" t="n">
         <v>636720</v>
@@ -658,7 +658,7 @@
         <v>14</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>394</v>
       </c>
       <c r="L7" t="n">
         <v>504690</v>
@@ -696,7 +696,7 @@
         <v>5</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>333</v>
       </c>
       <c r="L8" t="n">
         <v>398370</v>
@@ -734,7 +734,7 @@
         <v>9</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>267</v>
       </c>
       <c r="L9" t="n">
         <v>291570</v>
@@ -772,7 +772,7 @@
         <v>3</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>172</v>
       </c>
       <c r="L10" t="n">
         <v>178290</v>
@@ -810,7 +810,7 @@
         <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="L11" t="n">
         <v>162840</v>
@@ -848,7 +848,7 @@
         <v>3</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="L12" t="n">
         <v>97140</v>
@@ -886,7 +886,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="L13" t="n">
         <v>42900</v>
@@ -924,7 +924,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L14" t="n">
         <v>16410</v>
@@ -962,7 +962,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L15" t="n">
         <v>6780</v>
@@ -1000,7 +1000,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
         <v>2160</v>
@@ -1476,7 +1476,7 @@
         <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L4" t="n">
         <v>16980</v>
@@ -1514,7 +1514,7 @@
         <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="L5" t="n">
         <v>27090</v>
@@ -1552,7 +1552,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="L6" t="n">
         <v>30600</v>
@@ -1590,7 +1590,7 @@
         <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="L7" t="n">
         <v>38160</v>
@@ -1628,7 +1628,7 @@
         <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="L8" t="n">
         <v>49650</v>
@@ -1666,7 +1666,7 @@
         <v>4</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="L9" t="n">
         <v>44280</v>
@@ -1704,7 +1704,7 @@
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="L10" t="n">
         <v>59370</v>
@@ -1742,7 +1742,7 @@
         <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="L11" t="n">
         <v>93480</v>
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="L12" t="n">
         <v>64440</v>
@@ -1818,7 +1818,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="L13" t="n">
         <v>31230</v>
@@ -1856,7 +1856,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L14" t="n">
         <v>12780</v>
@@ -1894,7 +1894,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L15" t="n">
         <v>5400</v>
@@ -2446,7 +2446,7 @@
         <v>0.6</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>7.98</v>
       </c>
       <c r="L5" t="n">
         <v>5688.9</v>
@@ -2484,7 +2484,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>16.25</v>
       </c>
       <c r="L6" t="n">
         <v>11322</v>
@@ -2522,7 +2522,7 @@
         <v>0.7</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>18.04</v>
       </c>
       <c r="L7" t="n">
         <v>22896</v>
@@ -2560,7 +2560,7 @@
         <v>0.85</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>22.5</v>
       </c>
       <c r="L8" t="n">
         <v>35251.5</v>
@@ -2598,7 +2598,7 @@
         <v>3.8</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="L9" t="n">
         <v>35866.8</v>
@@ -2636,7 +2636,7 @@
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="L10" t="n">
         <v>52839.3</v>
@@ -2674,7 +2674,7 @@
         <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="L11" t="n">
         <v>93480</v>
@@ -2712,7 +2712,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="L12" t="n">
         <v>64440</v>
@@ -2750,7 +2750,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="L13" t="n">
         <v>31230</v>
@@ -2788,7 +2788,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L14" t="n">
         <v>12780</v>
@@ -2826,7 +2826,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L15" t="n">
         <v>5400</v>
@@ -3378,7 +3378,7 @@
         <v>34999.8</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>170245.32</v>
       </c>
       <c r="L5" t="n">
         <v>53589.44</v>
@@ -3416,7 +3416,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>346677.5</v>
       </c>
       <c r="L6" t="n">
         <v>106653.24</v>
@@ -3454,7 +3454,7 @@
         <v>40833.1</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>384865.36</v>
       </c>
       <c r="L7" t="n">
         <v>215680.32</v>
@@ -3492,7 +3492,7 @@
         <v>49583.05</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>480015</v>
       </c>
       <c r="L8" t="n">
         <v>332069.13</v>
@@ -3530,7 +3530,7 @@
         <v>221665.4</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>448014</v>
       </c>
       <c r="L9" t="n">
         <v>337865.26</v>
@@ -3568,7 +3568,7 @@
         <v>58333</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>661354</v>
       </c>
       <c r="L10" t="n">
         <v>497746.21</v>
@@ -3606,7 +3606,7 @@
         <v>58333</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>768024</v>
       </c>
       <c r="L11" t="n">
         <v>880581.6</v>
@@ -3644,7 +3644,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>746690</v>
       </c>
       <c r="L12" t="n">
         <v>607024.8</v>
@@ -3682,7 +3682,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>362678</v>
       </c>
       <c r="L13" t="n">
         <v>294186.6</v>
@@ -3720,7 +3720,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>213340</v>
       </c>
       <c r="L14" t="n">
         <v>120387.6</v>
@@ -3758,7 +3758,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>64002</v>
       </c>
       <c r="L15" t="n">
         <v>50868</v>
@@ -4272,7 +4272,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="L4" t="n">
         <v>126330</v>
@@ -4310,7 +4310,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="L5" t="n">
         <v>47250</v>
@@ -4348,7 +4348,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
         <v>9570</v>
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
         <v>2190</v>
@@ -5242,7 +5242,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>8.82</v>
       </c>
       <c r="L5" t="n">
         <v>9922.5</v>
@@ -5280,7 +5280,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>0.65</v>
       </c>
       <c r="L6" t="n">
         <v>3540.9</v>
@@ -5318,7 +5318,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>0.82</v>
       </c>
       <c r="L7" t="n">
         <v>1314</v>
@@ -6174,7 +6174,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>188165.88</v>
       </c>
       <c r="L5" t="n">
         <v>93469.95</v>
@@ -6212,7 +6212,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>13867.1</v>
       </c>
       <c r="L6" t="n">
         <v>33355.28</v>
@@ -6250,7 +6250,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>17493.88</v>
       </c>
       <c r="L7" t="n">
         <v>12377.88</v>
@@ -7068,7 +7068,7 @@
         <v>10</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>137</v>
       </c>
       <c r="L4" t="n">
         <v>107190</v>
@@ -7106,7 +7106,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="L5" t="n">
         <v>34710</v>
@@ -7144,7 +7144,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L6" t="n">
         <v>8700</v>
@@ -7182,7 +7182,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L7" t="n">
         <v>3210</v>
@@ -7220,7 +7220,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" t="n">
         <v>1320</v>
@@ -8038,7 +8038,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>11.34</v>
       </c>
       <c r="L5" t="n">
         <v>7289.1</v>
@@ -8076,7 +8076,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="L6" t="n">
         <v>3219</v>
@@ -8114,7 +8114,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="L7" t="n">
         <v>1926</v>
@@ -8152,7 +8152,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="L8" t="n">
         <v>937.2</v>
@@ -8970,7 +8970,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>241927.56</v>
       </c>
       <c r="L5" t="n">
         <v>68663.32000000001</v>
@@ -9008,7 +9008,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>110936.8</v>
       </c>
       <c r="L6" t="n">
         <v>30322.98</v>
@@ -9046,7 +9046,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>52481.64</v>
       </c>
       <c r="L7" t="n">
         <v>18142.92</v>
@@ -9084,7 +9084,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>19200.6</v>
       </c>
       <c r="L8" t="n">
         <v>8828.42</v>
@@ -9864,7 +9864,7 @@
         <v>9</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>230</v>
       </c>
       <c r="L4" t="n">
         <v>193620</v>
@@ -9902,7 +9902,7 @@
         <v>11</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>171</v>
       </c>
       <c r="L5" t="n">
         <v>193410</v>
@@ -9940,7 +9940,7 @@
         <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>219</v>
       </c>
       <c r="L6" t="n">
         <v>208590</v>
@@ -9978,7 +9978,7 @@
         <v>3</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>134</v>
       </c>
       <c r="L7" t="n">
         <v>137550</v>
@@ -10016,7 +10016,7 @@
         <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="L8" t="n">
         <v>84030</v>
@@ -10054,7 +10054,7 @@
         <v>2</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L9" t="n">
         <v>43200</v>
@@ -10092,7 +10092,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L10" t="n">
         <v>10680</v>
@@ -10130,7 +10130,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L11" t="n">
         <v>4620</v>
@@ -10834,7 +10834,7 @@
         <v>7.8</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>242.34</v>
       </c>
       <c r="L5" t="n">
         <v>179625.6</v>
@@ -10872,7 +10872,7 @@
         <v>5</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>330.85</v>
       </c>
       <c r="L6" t="n">
         <v>235586.4</v>
@@ -10910,7 +10910,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>323.08</v>
       </c>
       <c r="L7" t="n">
         <v>302814</v>
@@ -10948,7 +10948,7 @@
         <v>4.25</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>299.7</v>
       </c>
       <c r="L8" t="n">
         <v>282842.7</v>
@@ -10986,7 +10986,7 @@
         <v>8.550000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>267</v>
       </c>
       <c r="L9" t="n">
         <v>236171.7</v>
@@ -11024,7 +11024,7 @@
         <v>3</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>172</v>
       </c>
       <c r="L10" t="n">
         <v>158678.1</v>
@@ -11062,7 +11062,7 @@
         <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="L11" t="n">
         <v>162840</v>
@@ -11100,7 +11100,7 @@
         <v>3</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="L12" t="n">
         <v>97140</v>
@@ -11138,7 +11138,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="L13" t="n">
         <v>42900</v>
@@ -11176,7 +11176,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L14" t="n">
         <v>16410</v>
@@ -11214,7 +11214,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L15" t="n">
         <v>6780</v>
@@ -11252,7 +11252,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
         <v>2160</v>
@@ -11766,7 +11766,7 @@
         <v>3.3</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>71.81999999999999</v>
       </c>
       <c r="L5" t="n">
         <v>40616.1</v>
@@ -11804,7 +11804,7 @@
         <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>142.35</v>
       </c>
       <c r="L6" t="n">
         <v>77178.3</v>
@@ -11842,7 +11842,7 @@
         <v>2.1</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>109.88</v>
       </c>
       <c r="L7" t="n">
         <v>82530</v>
@@ -11880,7 +11880,7 @@
         <v>0.85</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>82.8</v>
       </c>
       <c r="L8" t="n">
         <v>59661.3</v>
@@ -11918,7 +11918,7 @@
         <v>1.9</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L9" t="n">
         <v>34992</v>
@@ -11956,7 +11956,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L10" t="n">
         <v>9505.200000000001</v>
@@ -11994,7 +11994,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L11" t="n">
         <v>4620</v>
@@ -12698,7 +12698,7 @@
         <v>192498.9</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1532207.88</v>
       </c>
       <c r="L5" t="n">
         <v>382603.66</v>
@@ -12736,7 +12736,7 @@
         <v>58333</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>3036894.9</v>
       </c>
       <c r="L6" t="n">
         <v>727019.59</v>
@@ -12774,7 +12774,7 @@
         <v>122499.3</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>2344179.92</v>
       </c>
       <c r="L7" t="n">
         <v>777432.6</v>
@@ -12812,7 +12812,7 @@
         <v>49583.05</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1766455.2</v>
       </c>
       <c r="L8" t="n">
         <v>562009.45</v>
@@ -12850,7 +12850,7 @@
         <v>110832.7</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1066700</v>
       </c>
       <c r="L9" t="n">
         <v>329624.64</v>
@@ -12888,7 +12888,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>170672</v>
       </c>
       <c r="L10" t="n">
         <v>89538.98</v>
@@ -12926,7 +12926,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>42668</v>
       </c>
       <c r="L11" t="n">
         <v>43520.4</v>
@@ -13592,7 +13592,7 @@
         <v>4</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="L4" t="n">
         <v>287370</v>
@@ -13630,7 +13630,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="L5" t="n">
         <v>85050</v>
@@ -14562,7 +14562,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="L5" t="n">
         <v>17860.5</v>
@@ -15494,7 +15494,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>179205.6</v>
       </c>
       <c r="L5" t="n">
         <v>168245.91</v>
@@ -16426,7 +16426,7 @@
         <v>454997.4</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>5170081.56</v>
       </c>
       <c r="L5" t="n">
         <v>1692073.15</v>
@@ -16464,7 +16464,7 @@
         <v>291665</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>7058353.9</v>
       </c>
       <c r="L6" t="n">
         <v>2219223.89</v>
@@ -16502,7 +16502,7 @@
         <v>571663.4</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>6892588.72</v>
       </c>
       <c r="L7" t="n">
         <v>2852507.88</v>
@@ -16540,7 +16540,7 @@
         <v>247915.25</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>6393799.8</v>
       </c>
       <c r="L8" t="n">
         <v>2664378.23</v>
@@ -16578,7 +16578,7 @@
         <v>498747.15</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>5696178</v>
       </c>
       <c r="L9" t="n">
         <v>2224737.41</v>
@@ -16616,7 +16616,7 @@
         <v>174999</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>3669448</v>
       </c>
       <c r="L10" t="n">
         <v>1494747.7</v>
@@ -16654,7 +16654,7 @@
         <v>174999</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>2218736</v>
       </c>
       <c r="L11" t="n">
         <v>1533952.8</v>
@@ -16692,7 +16692,7 @@
         <v>174999</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1408044</v>
       </c>
       <c r="L12" t="n">
         <v>915058.8</v>
@@ -16730,7 +16730,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>597352</v>
       </c>
       <c r="L13" t="n">
         <v>404118</v>
@@ -16768,7 +16768,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>234674</v>
       </c>
       <c r="L14" t="n">
         <v>154582.2</v>
@@ -16806,7 +16806,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>64002</v>
       </c>
       <c r="L15" t="n">
         <v>63867.6</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>21334</v>
       </c>
       <c r="L16" t="n">
         <v>20347.2</v>
@@ -17320,7 +17320,7 @@
         <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>138</v>
       </c>
       <c r="L4" t="n">
         <v>157980</v>
@@ -17358,7 +17358,7 @@
         <v>4</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>164</v>
       </c>
       <c r="L5" t="n">
         <v>189270</v>
@@ -17396,7 +17396,7 @@
         <v>5</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>161</v>
       </c>
       <c r="L6" t="n">
         <v>198630</v>
@@ -17434,7 +17434,7 @@
         <v>9</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="L7" t="n">
         <v>247980</v>
@@ -17472,7 +17472,7 @@
         <v>3</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="L8" t="n">
         <v>237390</v>
@@ -17510,7 +17510,7 @@
         <v>3</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>194</v>
       </c>
       <c r="L9" t="n">
         <v>193950</v>
@@ -17548,7 +17548,7 @@
         <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="L10" t="n">
         <v>104940</v>
@@ -17586,7 +17586,7 @@
         <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="L11" t="n">
         <v>63540</v>
@@ -17624,7 +17624,7 @@
         <v>3</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="L12" t="n">
         <v>29010</v>
@@ -17662,7 +17662,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L13" t="n">
         <v>10080</v>
@@ -17700,7 +17700,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" t="n">
         <v>2610</v>
@@ -17776,7 +17776,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
         <v>240</v>
@@ -18290,7 +18290,7 @@
         <v>1.2</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>68.88</v>
       </c>
       <c r="L5" t="n">
         <v>39746.7</v>
@@ -18328,7 +18328,7 @@
         <v>2.5</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>104.65</v>
       </c>
       <c r="L6" t="n">
         <v>73493.10000000001</v>
@@ -18366,7 +18366,7 @@
         <v>6.3</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>164</v>
       </c>
       <c r="L7" t="n">
         <v>148788</v>
@@ -18404,7 +18404,7 @@
         <v>2.55</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>189</v>
       </c>
       <c r="L8" t="n">
         <v>168546.9</v>
@@ -18442,7 +18442,7 @@
         <v>2.85</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>194</v>
       </c>
       <c r="L9" t="n">
         <v>157099.5</v>
@@ -18480,7 +18480,7 @@
         <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="L10" t="n">
         <v>93396.60000000001</v>
@@ -18518,7 +18518,7 @@
         <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="L11" t="n">
         <v>63540</v>
@@ -18556,7 +18556,7 @@
         <v>3</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="L12" t="n">
         <v>29010</v>
@@ -18594,7 +18594,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L13" t="n">
         <v>10080</v>
@@ -18632,7 +18632,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" t="n">
         <v>2610</v>
@@ -18708,7 +18708,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
         <v>240</v>
@@ -19222,7 +19222,7 @@
         <v>69999.60000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1469485.92</v>
       </c>
       <c r="L5" t="n">
         <v>374413.91</v>
@@ -19260,7 +19260,7 @@
         <v>145832.5</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>2232603.1</v>
       </c>
       <c r="L6" t="n">
         <v>692305</v>
@@ -19298,7 +19298,7 @@
         <v>367497.9</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>3498776</v>
       </c>
       <c r="L7" t="n">
         <v>1401582.96</v>
@@ -19336,7 +19336,7 @@
         <v>148749.15</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>4032126</v>
       </c>
       <c r="L8" t="n">
         <v>1587711.8</v>
@@ -19374,7 +19374,7 @@
         <v>166249.05</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>4138796</v>
       </c>
       <c r="L9" t="n">
         <v>1479877.29</v>
@@ -19412,7 +19412,7 @@
         <v>116666</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>2837422</v>
       </c>
       <c r="L10" t="n">
         <v>879795.97</v>
@@ -19450,7 +19450,7 @@
         <v>116666</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1408044</v>
       </c>
       <c r="L11" t="n">
         <v>598546.8</v>
@@ -19488,7 +19488,7 @@
         <v>174999</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>640020</v>
       </c>
       <c r="L12" t="n">
         <v>273274.2</v>
@@ -19526,7 +19526,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>234674</v>
       </c>
       <c r="L13" t="n">
         <v>94953.60000000001</v>
@@ -19564,7 +19564,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>21334</v>
       </c>
       <c r="L14" t="n">
         <v>24586.2</v>
@@ -19640,7 +19640,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>21334</v>
       </c>
       <c r="L16" t="n">
         <v>2260.8</v>
@@ -20116,7 +20116,7 @@
         <v>12</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>349</v>
       </c>
       <c r="L4" t="n">
         <v>402510</v>
@@ -20154,7 +20154,7 @@
         <v>7</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>153</v>
       </c>
       <c r="L5" t="n">
         <v>216060</v>
@@ -20192,7 +20192,7 @@
         <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="L6" t="n">
         <v>115050</v>
@@ -20230,7 +20230,7 @@
         <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="L7" t="n">
         <v>46320</v>
@@ -20268,7 +20268,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L8" t="n">
         <v>7020</v>
@@ -21086,7 +21086,7 @@
         <v>2.1</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>64.26000000000001</v>
       </c>
       <c r="L5" t="n">
         <v>45372.6</v>
@@ -21124,7 +21124,7 @@
         <v>1.5</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>60.45</v>
       </c>
       <c r="L6" t="n">
         <v>42568.5</v>
@@ -21162,7 +21162,7 @@
         <v>0.7</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>27.88</v>
       </c>
       <c r="L7" t="n">
         <v>27792</v>
@@ -21200,7 +21200,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="L8" t="n">
         <v>4984.2</v>
@@ -22018,7 +22018,7 @@
         <v>122499.3</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1370922.84</v>
       </c>
       <c r="L5" t="n">
         <v>427409.89</v>
@@ -22056,7 +22056,7 @@
         <v>87499.5</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1289640.3</v>
       </c>
       <c r="L6" t="n">
         <v>400995.27</v>
@@ -22094,7 +22094,7 @@
         <v>40833.1</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>594791.92</v>
       </c>
       <c r="L7" t="n">
         <v>261800.64</v>
@@ -22132,7 +22132,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>57601.8</v>
       </c>
       <c r="L8" t="n">
         <v>46951.16</v>

--- a/risk/Risk_Analysis_T3_50yrs_Present_Perfect.xlsx
+++ b/risk/Risk_Analysis_T3_50yrs_Present_Perfect.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,13 +511,18 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>162850.77</v>
+        <v>162694.71</v>
       </c>
       <c r="C4" t="n">
         <v>34102656</v>
@@ -529,10 +534,10 @@
         <v>8144100</v>
       </c>
       <c r="F4" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G4" t="n">
-        <v>515760</v>
+        <v>513270</v>
       </c>
       <c r="H4" t="n">
         <v>68100</v>
@@ -544,10 +549,13 @@
         <v>40</v>
       </c>
       <c r="K4" t="n">
-        <v>1023</v>
+        <v>1013</v>
       </c>
       <c r="L4" t="n">
-        <v>1353630</v>
+        <v>1350570</v>
+      </c>
+      <c r="M4" t="n">
+        <v>64800</v>
       </c>
     </row>
     <row r="5">
@@ -555,7 +563,7 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>110274.3</v>
+        <v>110112.39</v>
       </c>
       <c r="C5" t="n">
         <v>19405512</v>
@@ -570,7 +578,7 @@
         <v>86</v>
       </c>
       <c r="G5" t="n">
-        <v>338580</v>
+        <v>337110</v>
       </c>
       <c r="H5" t="n">
         <v>48750</v>
@@ -582,10 +590,13 @@
         <v>26</v>
       </c>
       <c r="K5" t="n">
-        <v>577</v>
+        <v>567</v>
       </c>
       <c r="L5" t="n">
-        <v>855360</v>
+        <v>853350</v>
+      </c>
+      <c r="M5" t="n">
+        <v>50490</v>
       </c>
     </row>
     <row r="6">
@@ -593,7 +604,7 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>86134.05</v>
+        <v>85995.17999999999</v>
       </c>
       <c r="C6" t="n">
         <v>14311080</v>
@@ -608,7 +619,7 @@
         <v>54</v>
       </c>
       <c r="G6" t="n">
-        <v>250050</v>
+        <v>249300</v>
       </c>
       <c r="H6" t="n">
         <v>56340</v>
@@ -620,10 +631,13 @@
         <v>10</v>
       </c>
       <c r="K6" t="n">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="L6" t="n">
-        <v>636720</v>
+        <v>634980</v>
+      </c>
+      <c r="M6" t="n">
+        <v>30630</v>
       </c>
     </row>
     <row r="7">
@@ -631,7 +645,7 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>72310.41</v>
+        <v>72264.14999999999</v>
       </c>
       <c r="C7" t="n">
         <v>8772624</v>
@@ -646,7 +660,7 @@
         <v>29</v>
       </c>
       <c r="G7" t="n">
-        <v>205200</v>
+        <v>204750</v>
       </c>
       <c r="H7" t="n">
         <v>30060</v>
@@ -661,7 +675,10 @@
         <v>394</v>
       </c>
       <c r="L7" t="n">
-        <v>504690</v>
+        <v>503700</v>
+      </c>
+      <c r="M7" t="n">
+        <v>20940</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +686,7 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>62453.61</v>
+        <v>62453.16</v>
       </c>
       <c r="C8" t="n">
         <v>7014672</v>
@@ -684,7 +701,7 @@
         <v>17</v>
       </c>
       <c r="G8" t="n">
-        <v>166020</v>
+        <v>165570</v>
       </c>
       <c r="H8" t="n">
         <v>8040</v>
@@ -699,7 +716,10 @@
         <v>333</v>
       </c>
       <c r="L8" t="n">
-        <v>398370</v>
+        <v>397650</v>
+      </c>
+      <c r="M8" t="n">
+        <v>13260</v>
       </c>
     </row>
     <row r="9">
@@ -722,7 +742,7 @@
         <v>18</v>
       </c>
       <c r="G9" t="n">
-        <v>136110</v>
+        <v>135780</v>
       </c>
       <c r="H9" t="n">
         <v>3870</v>
@@ -737,7 +757,10 @@
         <v>267</v>
       </c>
       <c r="L9" t="n">
-        <v>291570</v>
+        <v>291210</v>
+      </c>
+      <c r="M9" t="n">
+        <v>10440</v>
       </c>
     </row>
     <row r="10">
@@ -745,7 +768,7 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>31503.15</v>
+        <v>31502.88</v>
       </c>
       <c r="C10" t="n">
         <v>2778552</v>
@@ -775,7 +798,10 @@
         <v>172</v>
       </c>
       <c r="L10" t="n">
-        <v>178290</v>
+        <v>178200</v>
+      </c>
+      <c r="M10" t="n">
+        <v>6840</v>
       </c>
     </row>
     <row r="11">
@@ -783,7 +809,7 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>22911.84</v>
+        <v>22911.75</v>
       </c>
       <c r="C11" t="n">
         <v>1611288</v>
@@ -813,7 +839,10 @@
         <v>104</v>
       </c>
       <c r="L11" t="n">
-        <v>162840</v>
+        <v>162570</v>
+      </c>
+      <c r="M11" t="n">
+        <v>3660</v>
       </c>
     </row>
     <row r="12">
@@ -851,7 +880,10 @@
         <v>66</v>
       </c>
       <c r="L12" t="n">
-        <v>97140</v>
+        <v>96930</v>
+      </c>
+      <c r="M12" t="n">
+        <v>2850</v>
       </c>
     </row>
     <row r="13">
@@ -891,6 +923,9 @@
       <c r="L13" t="n">
         <v>42900</v>
       </c>
+      <c r="M13" t="n">
+        <v>1410</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -929,6 +964,9 @@
       <c r="L14" t="n">
         <v>16410</v>
       </c>
+      <c r="M14" t="n">
+        <v>300</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -967,6 +1005,9 @@
       <c r="L15" t="n">
         <v>6780</v>
       </c>
+      <c r="M15" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1005,6 +1046,9 @@
       <c r="L16" t="n">
         <v>2160</v>
       </c>
+      <c r="M16" t="n">
+        <v>210</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1043,6 +1087,9 @@
       <c r="L17" t="n">
         <v>1440</v>
       </c>
+      <c r="M17" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1081,6 +1128,9 @@
       <c r="L18" t="n">
         <v>1530</v>
       </c>
+      <c r="M18" t="n">
+        <v>120</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1119,6 +1169,9 @@
       <c r="L19" t="n">
         <v>780</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1157,6 +1210,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1195,6 +1251,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1233,6 +1292,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1271,6 +1333,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1309,6 +1374,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -1358,6 +1426,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -1372,7 +1444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1443,6 +1515,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1479,7 +1556,10 @@
         <v>11</v>
       </c>
       <c r="L4" t="n">
-        <v>16980</v>
+        <v>17040</v>
+      </c>
+      <c r="M4" t="n">
+        <v>5340</v>
       </c>
     </row>
     <row r="5">
@@ -1502,7 +1582,7 @@
         <v>7</v>
       </c>
       <c r="G5" t="n">
-        <v>8700</v>
+        <v>8730</v>
       </c>
       <c r="H5" t="n">
         <v>2370</v>
@@ -1517,7 +1597,10 @@
         <v>19</v>
       </c>
       <c r="L5" t="n">
-        <v>27090</v>
+        <v>27030</v>
+      </c>
+      <c r="M5" t="n">
+        <v>12780</v>
       </c>
     </row>
     <row r="6">
@@ -1525,7 +1608,7 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>3181.32</v>
+        <v>3181.23</v>
       </c>
       <c r="C6" t="n">
         <v>559440</v>
@@ -1540,7 +1623,7 @@
         <v>6</v>
       </c>
       <c r="G6" t="n">
-        <v>9090</v>
+        <v>9120</v>
       </c>
       <c r="H6" t="n">
         <v>2820</v>
@@ -1555,7 +1638,10 @@
         <v>25</v>
       </c>
       <c r="L6" t="n">
-        <v>30600</v>
+        <v>30780</v>
+      </c>
+      <c r="M6" t="n">
+        <v>10170</v>
       </c>
     </row>
     <row r="7">
@@ -1578,7 +1664,7 @@
         <v>6</v>
       </c>
       <c r="G7" t="n">
-        <v>16140</v>
+        <v>16230</v>
       </c>
       <c r="H7" t="n">
         <v>3450</v>
@@ -1593,7 +1679,10 @@
         <v>22</v>
       </c>
       <c r="L7" t="n">
-        <v>38160</v>
+        <v>38400</v>
+      </c>
+      <c r="M7" t="n">
+        <v>6660</v>
       </c>
     </row>
     <row r="8">
@@ -1616,7 +1705,7 @@
         <v>7</v>
       </c>
       <c r="G8" t="n">
-        <v>19710</v>
+        <v>19770</v>
       </c>
       <c r="H8" t="n">
         <v>3750</v>
@@ -1631,7 +1720,10 @@
         <v>25</v>
       </c>
       <c r="L8" t="n">
-        <v>49650</v>
+        <v>49770</v>
+      </c>
+      <c r="M8" t="n">
+        <v>3960</v>
       </c>
     </row>
     <row r="9">
@@ -1669,7 +1761,10 @@
         <v>21</v>
       </c>
       <c r="L9" t="n">
-        <v>44280</v>
+        <v>44310</v>
+      </c>
+      <c r="M9" t="n">
+        <v>3000</v>
       </c>
     </row>
     <row r="10">
@@ -1692,7 +1787,7 @@
         <v>9</v>
       </c>
       <c r="G10" t="n">
-        <v>20490</v>
+        <v>20550</v>
       </c>
       <c r="H10" t="n">
         <v>4530</v>
@@ -1707,7 +1802,10 @@
         <v>31</v>
       </c>
       <c r="L10" t="n">
-        <v>59370</v>
+        <v>59520</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1950</v>
       </c>
     </row>
     <row r="11">
@@ -1730,7 +1828,7 @@
         <v>9</v>
       </c>
       <c r="G11" t="n">
-        <v>32640</v>
+        <v>32610</v>
       </c>
       <c r="H11" t="n">
         <v>4500</v>
@@ -1745,7 +1843,10 @@
         <v>36</v>
       </c>
       <c r="L11" t="n">
-        <v>93480</v>
+        <v>93660</v>
+      </c>
+      <c r="M11" t="n">
+        <v>930</v>
       </c>
     </row>
     <row r="12">
@@ -1783,7 +1884,10 @@
         <v>35</v>
       </c>
       <c r="L12" t="n">
-        <v>64440</v>
+        <v>64500</v>
+      </c>
+      <c r="M12" t="n">
+        <v>300</v>
       </c>
     </row>
     <row r="13">
@@ -1806,7 +1910,7 @@
         <v>2</v>
       </c>
       <c r="G13" t="n">
-        <v>13680</v>
+        <v>13710</v>
       </c>
       <c r="H13" t="n">
         <v>840</v>
@@ -1821,7 +1925,10 @@
         <v>17</v>
       </c>
       <c r="L13" t="n">
-        <v>31230</v>
+        <v>31290</v>
+      </c>
+      <c r="M13" t="n">
+        <v>240</v>
       </c>
     </row>
     <row r="14">
@@ -1859,7 +1966,10 @@
         <v>10</v>
       </c>
       <c r="L14" t="n">
-        <v>12780</v>
+        <v>12810</v>
+      </c>
+      <c r="M14" t="n">
+        <v>150</v>
       </c>
     </row>
     <row r="15">
@@ -1899,6 +2009,9 @@
       <c r="L15" t="n">
         <v>5400</v>
       </c>
+      <c r="M15" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1937,6 +2050,9 @@
       <c r="L16" t="n">
         <v>1620</v>
       </c>
+      <c r="M16" t="n">
+        <v>120</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1975,6 +2091,9 @@
       <c r="L17" t="n">
         <v>930</v>
       </c>
+      <c r="M17" t="n">
+        <v>120</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2013,6 +2132,9 @@
       <c r="L18" t="n">
         <v>750</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2051,6 +2173,9 @@
       <c r="L19" t="n">
         <v>660</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2089,6 +2214,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2127,6 +2255,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2165,6 +2296,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2203,6 +2337,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2241,6 +2378,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -2290,6 +2430,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -2304,7 +2448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2375,6 +2519,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -2411,6 +2560,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2446,10 +2598,13 @@
         <v>0.6</v>
       </c>
       <c r="K5" t="n">
-        <v>7.98</v>
+        <v>6.29</v>
       </c>
       <c r="L5" t="n">
-        <v>5688.9</v>
+        <v>5676.3</v>
+      </c>
+      <c r="M5" t="n">
+        <v>255.6</v>
       </c>
     </row>
     <row r="6">
@@ -2457,7 +2612,7 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>2545.06</v>
+        <v>2544.98</v>
       </c>
       <c r="C6" t="n">
         <v>503496</v>
@@ -2472,7 +2627,7 @@
         <v>0.6</v>
       </c>
       <c r="G6" t="n">
-        <v>454.5</v>
+        <v>456</v>
       </c>
       <c r="H6" t="n">
         <v>1607.4</v>
@@ -2484,10 +2639,13 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>16.25</v>
+        <v>12.68</v>
       </c>
       <c r="L6" t="n">
-        <v>11322</v>
+        <v>11388.6</v>
+      </c>
+      <c r="M6" t="n">
+        <v>813.6</v>
       </c>
     </row>
     <row r="7">
@@ -2510,7 +2668,7 @@
         <v>3.6</v>
       </c>
       <c r="G7" t="n">
-        <v>2421</v>
+        <v>2434.5</v>
       </c>
       <c r="H7" t="n">
         <v>2518.5</v>
@@ -2522,10 +2680,13 @@
         <v>0.7</v>
       </c>
       <c r="K7" t="n">
-        <v>18.04</v>
+        <v>14.04</v>
       </c>
       <c r="L7" t="n">
-        <v>22896</v>
+        <v>23040</v>
+      </c>
+      <c r="M7" t="n">
+        <v>2331</v>
       </c>
     </row>
     <row r="8">
@@ -2548,22 +2709,25 @@
         <v>6.65</v>
       </c>
       <c r="G8" t="n">
-        <v>12811.5</v>
+        <v>12850.5</v>
       </c>
       <c r="H8" t="n">
         <v>3187.5</v>
       </c>
       <c r="I8" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="J8" t="n">
         <v>0.85</v>
       </c>
       <c r="K8" t="n">
-        <v>22.5</v>
+        <v>18.4</v>
       </c>
       <c r="L8" t="n">
-        <v>35251.5</v>
+        <v>35336.7</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2376</v>
       </c>
     </row>
     <row r="9">
@@ -2598,10 +2762,13 @@
         <v>3.8</v>
       </c>
       <c r="K9" t="n">
-        <v>21</v>
+        <v>16.86</v>
       </c>
       <c r="L9" t="n">
-        <v>35866.8</v>
+        <v>35891.1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>3000</v>
       </c>
     </row>
     <row r="10">
@@ -2624,22 +2791,25 @@
         <v>9</v>
       </c>
       <c r="G10" t="n">
-        <v>20490</v>
+        <v>20550</v>
       </c>
       <c r="H10" t="n">
         <v>4530</v>
       </c>
       <c r="I10" t="n">
-        <v>1.92</v>
+        <v>1.74</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>31</v>
+        <v>26.97</v>
       </c>
       <c r="L10" t="n">
-        <v>52839.3</v>
+        <v>52972.8</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1950</v>
       </c>
     </row>
     <row r="11">
@@ -2662,7 +2832,7 @@
         <v>9</v>
       </c>
       <c r="G11" t="n">
-        <v>32640</v>
+        <v>32610</v>
       </c>
       <c r="H11" t="n">
         <v>4500</v>
@@ -2674,10 +2844,13 @@
         <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>36</v>
+        <v>32.35</v>
       </c>
       <c r="L11" t="n">
-        <v>93480</v>
+        <v>93660</v>
+      </c>
+      <c r="M11" t="n">
+        <v>930</v>
       </c>
     </row>
     <row r="12">
@@ -2712,10 +2885,13 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>35</v>
+        <v>32.44</v>
       </c>
       <c r="L12" t="n">
-        <v>64440</v>
+        <v>64500</v>
+      </c>
+      <c r="M12" t="n">
+        <v>300</v>
       </c>
     </row>
     <row r="13">
@@ -2738,22 +2914,25 @@
         <v>2</v>
       </c>
       <c r="G13" t="n">
-        <v>13680</v>
+        <v>13710</v>
       </c>
       <c r="H13" t="n">
         <v>840</v>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>17</v>
+        <v>16.14</v>
       </c>
       <c r="L13" t="n">
-        <v>31230</v>
+        <v>31290</v>
+      </c>
+      <c r="M13" t="n">
+        <v>240</v>
       </c>
     </row>
     <row r="14">
@@ -2788,10 +2967,13 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>10</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>12780</v>
+        <v>12810</v>
+      </c>
+      <c r="M14" t="n">
+        <v>150</v>
       </c>
     </row>
     <row r="15">
@@ -2826,10 +3008,13 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="L15" t="n">
         <v>5400</v>
+      </c>
+      <c r="M15" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="16">
@@ -2869,6 +3054,9 @@
       <c r="L16" t="n">
         <v>1620</v>
       </c>
+      <c r="M16" t="n">
+        <v>120</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2907,6 +3095,9 @@
       <c r="L17" t="n">
         <v>930</v>
       </c>
+      <c r="M17" t="n">
+        <v>120</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2945,6 +3136,9 @@
       <c r="L18" t="n">
         <v>750</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2983,6 +3177,9 @@
       <c r="L19" t="n">
         <v>660</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3021,6 +3218,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3059,6 +3259,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3097,6 +3300,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3135,6 +3341,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3173,6 +3382,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -3222,6 +3434,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -3236,7 +3452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3307,6 +3523,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -3343,6 +3564,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3354,13 +3578,13 @@
         <v>1494741.6</v>
       </c>
       <c r="C5" t="n">
-        <v>15474690</v>
+        <v>11817036</v>
       </c>
       <c r="D5" t="n">
-        <v>13481160.05</v>
+        <v>25544090.88</v>
       </c>
       <c r="E5" t="n">
-        <v>6712248.26</v>
+        <v>12569071.05</v>
       </c>
       <c r="F5" t="n">
         <v>5833.38</v>
@@ -3369,19 +3593,22 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>236037.78</v>
+        <v>4863240</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>34999.8</v>
+        <v>14566.8</v>
       </c>
       <c r="K5" t="n">
-        <v>170245.32</v>
+        <v>305368.68</v>
       </c>
       <c r="L5" t="n">
-        <v>53589.44</v>
+        <v>1021734</v>
+      </c>
+      <c r="M5" t="n">
+        <v>76680</v>
       </c>
     </row>
     <row r="6">
@@ -3389,25 +3616,25 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>5599123.2</v>
+        <v>5598964.8</v>
       </c>
       <c r="C6" t="n">
-        <v>27692280</v>
+        <v>21146832</v>
       </c>
       <c r="D6" t="n">
-        <v>22582091.7</v>
+        <v>42788528.64</v>
       </c>
       <c r="E6" t="n">
-        <v>9723947.689999999</v>
+        <v>18208651.5</v>
       </c>
       <c r="F6" t="n">
         <v>25000.2</v>
       </c>
       <c r="G6" t="n">
-        <v>8408.25</v>
+        <v>24624</v>
       </c>
       <c r="H6" t="n">
-        <v>444687.21</v>
+        <v>9162180</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -3416,10 +3643,13 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>346677.5</v>
+        <v>615447.3</v>
       </c>
       <c r="L6" t="n">
-        <v>106653.24</v>
+        <v>2049948</v>
+      </c>
+      <c r="M6" t="n">
+        <v>244080</v>
       </c>
     </row>
     <row r="7">
@@ -3430,34 +3660,37 @@
         <v>9403495.199999999</v>
       </c>
       <c r="C7" t="n">
-        <v>34123320</v>
+        <v>26057808</v>
       </c>
       <c r="D7" t="n">
-        <v>31514611.69</v>
+        <v>59713860.1</v>
       </c>
       <c r="E7" t="n">
-        <v>15730002.19</v>
+        <v>29455334.1</v>
       </c>
       <c r="F7" t="n">
         <v>150001.2</v>
       </c>
       <c r="G7" t="n">
-        <v>44788.5</v>
+        <v>131463</v>
       </c>
       <c r="H7" t="n">
-        <v>696743.02</v>
+        <v>14355450</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>40833.1</v>
+        <v>16994.6</v>
       </c>
       <c r="K7" t="n">
-        <v>384865.36</v>
+        <v>681532.02</v>
       </c>
       <c r="L7" t="n">
-        <v>215680.32</v>
+        <v>4147200</v>
+      </c>
+      <c r="M7" t="n">
+        <v>699300</v>
       </c>
     </row>
     <row r="8">
@@ -3468,34 +3701,37 @@
         <v>10290456</v>
       </c>
       <c r="C8" t="n">
-        <v>42356160</v>
+        <v>32344704</v>
       </c>
       <c r="D8" t="n">
-        <v>45126785.34</v>
+        <v>85506195.45999999</v>
       </c>
       <c r="E8" t="n">
-        <v>19076417.79</v>
+        <v>35721689.85</v>
       </c>
       <c r="F8" t="n">
         <v>277085.55</v>
       </c>
       <c r="G8" t="n">
-        <v>237012.75</v>
+        <v>693927</v>
       </c>
       <c r="H8" t="n">
-        <v>881821.87</v>
+        <v>18168750</v>
       </c>
       <c r="I8" t="n">
-        <v>275997.6</v>
+        <v>142948.86</v>
       </c>
       <c r="J8" t="n">
-        <v>49583.05</v>
+        <v>20636.3</v>
       </c>
       <c r="K8" t="n">
-        <v>480015</v>
+        <v>893430.4</v>
       </c>
       <c r="L8" t="n">
-        <v>332069.13</v>
+        <v>6360606</v>
+      </c>
+      <c r="M8" t="n">
+        <v>712800</v>
       </c>
     </row>
     <row r="9">
@@ -3506,34 +3742,37 @@
         <v>10094040</v>
       </c>
       <c r="C9" t="n">
-        <v>34372800</v>
+        <v>26248320</v>
       </c>
       <c r="D9" t="n">
-        <v>39954937.81</v>
+        <v>75706583.04000001</v>
       </c>
       <c r="E9" t="n">
-        <v>12206959.38</v>
+        <v>22858233.75</v>
       </c>
       <c r="F9" t="n">
         <v>83334</v>
       </c>
       <c r="G9" t="n">
-        <v>293428.5</v>
+        <v>856494</v>
       </c>
       <c r="H9" t="n">
-        <v>921244.5</v>
+        <v>18981000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>221665.4</v>
+        <v>92256.39999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>448014</v>
+        <v>818799.83</v>
       </c>
       <c r="L9" t="n">
-        <v>337865.26</v>
+        <v>6460398</v>
+      </c>
+      <c r="M9" t="n">
+        <v>900000</v>
       </c>
     </row>
     <row r="10">
@@ -3544,34 +3783,37 @@
         <v>9364608</v>
       </c>
       <c r="C10" t="n">
-        <v>34234200</v>
+        <v>26142480</v>
       </c>
       <c r="D10" t="n">
-        <v>43114111.33</v>
+        <v>81692582.40000001</v>
       </c>
       <c r="E10" t="n">
-        <v>11444620.32</v>
+        <v>21430710</v>
       </c>
       <c r="F10" t="n">
         <v>375003</v>
       </c>
       <c r="G10" t="n">
-        <v>379065</v>
+        <v>1109700</v>
       </c>
       <c r="H10" t="n">
-        <v>1253224.5</v>
+        <v>25821000</v>
       </c>
       <c r="I10" t="n">
-        <v>735993.6</v>
+        <v>337949.76</v>
       </c>
       <c r="J10" t="n">
-        <v>58333</v>
+        <v>24278</v>
       </c>
       <c r="K10" t="n">
-        <v>661354</v>
+        <v>1309555.32</v>
       </c>
       <c r="L10" t="n">
-        <v>497746.21</v>
+        <v>9535104</v>
+      </c>
+      <c r="M10" t="n">
+        <v>585000</v>
       </c>
     </row>
     <row r="11">
@@ -3582,34 +3824,37 @@
         <v>13563396</v>
       </c>
       <c r="C11" t="n">
-        <v>34511400</v>
+        <v>26354160</v>
       </c>
       <c r="D11" t="n">
-        <v>44887008.37</v>
+        <v>85051866.23999999</v>
       </c>
       <c r="E11" t="n">
-        <v>10600417.9</v>
+        <v>19849892.4</v>
       </c>
       <c r="F11" t="n">
         <v>375003</v>
       </c>
       <c r="G11" t="n">
-        <v>603840</v>
+        <v>1760940</v>
       </c>
       <c r="H11" t="n">
-        <v>1244925</v>
+        <v>25650000</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>58333</v>
+        <v>24278</v>
       </c>
       <c r="K11" t="n">
-        <v>768024</v>
+        <v>1570592.38</v>
       </c>
       <c r="L11" t="n">
-        <v>880581.6</v>
+        <v>16858800</v>
+      </c>
+      <c r="M11" t="n">
+        <v>279000</v>
       </c>
     </row>
     <row r="12">
@@ -3620,22 +3865,22 @@
         <v>12879108</v>
       </c>
       <c r="C12" t="n">
-        <v>25613280</v>
+        <v>19559232</v>
       </c>
       <c r="D12" t="n">
-        <v>34370427.5</v>
+        <v>65125057.54</v>
       </c>
       <c r="E12" t="n">
-        <v>11492706.96</v>
+        <v>21520755</v>
       </c>
       <c r="F12" t="n">
         <v>333336</v>
       </c>
       <c r="G12" t="n">
-        <v>523365</v>
+        <v>1527660</v>
       </c>
       <c r="H12" t="n">
-        <v>340279.5</v>
+        <v>7011000</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -3644,10 +3889,13 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>746690</v>
+        <v>1575399.42</v>
       </c>
       <c r="L12" t="n">
-        <v>607024.8</v>
+        <v>11610000</v>
+      </c>
+      <c r="M12" t="n">
+        <v>90000</v>
       </c>
     </row>
     <row r="13">
@@ -3658,34 +3906,37 @@
         <v>6930594</v>
       </c>
       <c r="C13" t="n">
-        <v>14747040</v>
+        <v>11261376</v>
       </c>
       <c r="D13" t="n">
-        <v>20269350.38</v>
+        <v>38406348.29</v>
       </c>
       <c r="E13" t="n">
-        <v>5352739.46</v>
+        <v>10023312.6</v>
       </c>
       <c r="F13" t="n">
         <v>83334</v>
       </c>
       <c r="G13" t="n">
-        <v>253080</v>
+        <v>740340</v>
       </c>
       <c r="H13" t="n">
-        <v>232386</v>
+        <v>4788000</v>
       </c>
       <c r="I13" t="n">
-        <v>383330</v>
+        <v>184415.69</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>362678</v>
+        <v>783766.67</v>
       </c>
       <c r="L13" t="n">
-        <v>294186.6</v>
+        <v>5632200</v>
+      </c>
+      <c r="M13" t="n">
+        <v>72000</v>
       </c>
     </row>
     <row r="14">
@@ -3696,22 +3947,22 @@
         <v>2920896</v>
       </c>
       <c r="C14" t="n">
-        <v>7789320</v>
+        <v>5948208</v>
       </c>
       <c r="D14" t="n">
-        <v>10959880.36</v>
+        <v>20766772.22</v>
       </c>
       <c r="E14" t="n">
-        <v>3398365.76</v>
+        <v>6363635.4</v>
       </c>
       <c r="F14" t="n">
         <v>41667</v>
       </c>
       <c r="G14" t="n">
-        <v>77700</v>
+        <v>226800</v>
       </c>
       <c r="H14" t="n">
-        <v>66396</v>
+        <v>1368000</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -3720,10 +3971,13 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>213340</v>
+        <v>471964.32</v>
       </c>
       <c r="L14" t="n">
-        <v>120387.6</v>
+        <v>2305800</v>
+      </c>
+      <c r="M14" t="n">
+        <v>45000</v>
       </c>
     </row>
     <row r="15">
@@ -3734,22 +3988,22 @@
         <v>1976832</v>
       </c>
       <c r="C15" t="n">
-        <v>2522520</v>
+        <v>1926288</v>
       </c>
       <c r="D15" t="n">
-        <v>3600406.49</v>
+        <v>6822047.23</v>
       </c>
       <c r="E15" t="n">
-        <v>593256.48</v>
+        <v>1110906.9</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>56610</v>
+        <v>165240</v>
       </c>
       <c r="H15" t="n">
-        <v>24898.5</v>
+        <v>513000</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -3758,10 +4012,13 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>64002</v>
+        <v>143628.65</v>
       </c>
       <c r="L15" t="n">
-        <v>50868</v>
+        <v>972000</v>
+      </c>
+      <c r="M15" t="n">
+        <v>18000</v>
       </c>
     </row>
     <row r="16">
@@ -3772,22 +4029,22 @@
         <v>872190</v>
       </c>
       <c r="C16" t="n">
-        <v>443520</v>
+        <v>338688</v>
       </c>
       <c r="D16" t="n">
-        <v>642026.88</v>
+        <v>1216512</v>
       </c>
       <c r="E16" t="n">
-        <v>103353.11</v>
+        <v>193534.65</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>9435</v>
+        <v>27540</v>
       </c>
       <c r="H16" t="n">
-        <v>24898.5</v>
+        <v>513000</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -3799,7 +4056,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>15260.4</v>
+        <v>291600</v>
+      </c>
+      <c r="M16" t="n">
+        <v>36000</v>
       </c>
     </row>
     <row r="17">
@@ -3810,10 +4070,10 @@
         <v>372438</v>
       </c>
       <c r="C17" t="n">
-        <v>249480</v>
+        <v>190512</v>
       </c>
       <c r="D17" t="n">
-        <v>361140.12</v>
+        <v>684288</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -3822,10 +4082,10 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>1665</v>
+        <v>4860</v>
       </c>
       <c r="H17" t="n">
-        <v>16599</v>
+        <v>342000</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -3837,7 +4097,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>8760.6</v>
+        <v>167400</v>
+      </c>
+      <c r="M17" t="n">
+        <v>36000</v>
       </c>
     </row>
     <row r="18">
@@ -3848,10 +4111,10 @@
         <v>139590</v>
       </c>
       <c r="C18" t="n">
-        <v>27720</v>
+        <v>21168</v>
       </c>
       <c r="D18" t="n">
-        <v>40126.68</v>
+        <v>76032</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -3875,7 +4138,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>7065</v>
+        <v>135000</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3898,10 +4164,10 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>1110</v>
+        <v>3240</v>
       </c>
       <c r="H19" t="n">
-        <v>16599</v>
+        <v>342000</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -3913,7 +4179,10 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>6217.2</v>
+        <v>118800</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -3953,6 +4222,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3991,6 +4263,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -4029,6 +4304,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -4067,6 +4345,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -4105,6 +4386,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -4154,6 +4438,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -4168,7 +4456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4239,6 +4527,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -4260,7 +4553,7 @@
         <v>20</v>
       </c>
       <c r="G4" t="n">
-        <v>41580</v>
+        <v>41610</v>
       </c>
       <c r="H4" t="n">
         <v>4440</v>
@@ -4275,7 +4568,10 @@
         <v>55</v>
       </c>
       <c r="L4" t="n">
-        <v>126330</v>
+        <v>126180</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -4298,7 +4594,7 @@
         <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>14550</v>
+        <v>14610</v>
       </c>
       <c r="H5" t="n">
         <v>510</v>
@@ -4313,7 +4609,10 @@
         <v>21</v>
       </c>
       <c r="L5" t="n">
-        <v>47250</v>
+        <v>47730</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -4336,7 +4635,7 @@
         <v>4</v>
       </c>
       <c r="G6" t="n">
-        <v>1710</v>
+        <v>1740</v>
       </c>
       <c r="H6" t="n">
         <v>150</v>
@@ -4351,7 +4650,10 @@
         <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>9570</v>
+        <v>9540</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -4391,6 +4693,9 @@
       <c r="L7" t="n">
         <v>2190</v>
       </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -4429,6 +4734,9 @@
       <c r="L8" t="n">
         <v>420</v>
       </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -4467,6 +4775,9 @@
       <c r="L9" t="n">
         <v>150</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -4505,6 +4816,9 @@
       <c r="L10" t="n">
         <v>0</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -4543,6 +4857,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -4581,6 +4898,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -4619,6 +4939,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -4657,6 +4980,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -4695,6 +5021,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -4733,6 +5062,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -4771,6 +5103,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -4809,6 +5144,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -4847,6 +5185,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -4885,6 +5226,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -4923,6 +5267,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -4961,6 +5308,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -4999,6 +5349,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -5037,6 +5390,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -5086,6 +5442,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -5100,7 +5460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5171,6 +5531,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -5207,6 +5572,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5242,10 +5610,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>8.82</v>
+        <v>6.95</v>
       </c>
       <c r="L5" t="n">
-        <v>9922.5</v>
+        <v>10023.3</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -5268,7 +5639,7 @@
         <v>0.4</v>
       </c>
       <c r="G6" t="n">
-        <v>85.5</v>
+        <v>87</v>
       </c>
       <c r="H6" t="n">
         <v>85.5</v>
@@ -5280,10 +5651,13 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.65</v>
+        <v>0.51</v>
       </c>
       <c r="L6" t="n">
-        <v>3540.9</v>
+        <v>3529.8</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -5318,10 +5692,13 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.82</v>
+        <v>0.64</v>
       </c>
       <c r="L7" t="n">
         <v>1314</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -5361,6 +5738,9 @@
       <c r="L8" t="n">
         <v>298.2</v>
       </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -5399,6 +5779,9 @@
       <c r="L9" t="n">
         <v>121.5</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -5437,6 +5820,9 @@
       <c r="L10" t="n">
         <v>0</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -5475,6 +5861,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -5513,6 +5902,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -5551,6 +5943,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -5589,6 +5984,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -5627,6 +6025,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -5665,6 +6066,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -5703,6 +6107,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -5741,6 +6148,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -5779,6 +6189,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -5817,6 +6230,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -5855,6 +6271,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -5893,6 +6312,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -5931,6 +6353,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -5969,6 +6394,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -6018,6 +6446,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -6032,7 +6464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6103,6 +6535,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -6139,6 +6576,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6150,13 +6590,13 @@
         <v>4090759.2</v>
       </c>
       <c r="C5" t="n">
-        <v>16572402</v>
+        <v>12655288.8</v>
       </c>
       <c r="D5" t="n">
-        <v>14437459.08</v>
+        <v>27356085.5</v>
       </c>
       <c r="E5" t="n">
-        <v>2871452.25</v>
+        <v>5376959.55</v>
       </c>
       <c r="F5" t="n">
         <v>2500.02</v>
@@ -6165,7 +6605,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>50792.94</v>
+        <v>1046520</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -6174,10 +6614,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>188165.88</v>
+        <v>337512.76</v>
       </c>
       <c r="L5" t="n">
-        <v>93469.95</v>
+        <v>1804194</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -6188,22 +6631,22 @@
         <v>638827.2</v>
       </c>
       <c r="C6" t="n">
-        <v>4914756</v>
+        <v>3753086.4</v>
       </c>
       <c r="D6" t="n">
-        <v>4007812.67</v>
+        <v>7594000.13</v>
       </c>
       <c r="E6" t="n">
-        <v>1485213.91</v>
+        <v>2781148.5</v>
       </c>
       <c r="F6" t="n">
         <v>16666.8</v>
       </c>
       <c r="G6" t="n">
-        <v>1581.75</v>
+        <v>4698</v>
       </c>
       <c r="H6" t="n">
-        <v>23653.57</v>
+        <v>487350</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -6212,10 +6655,13 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>13867.1</v>
+        <v>24617.89</v>
       </c>
       <c r="L6" t="n">
-        <v>33355.28</v>
+        <v>635364</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -6226,19 +6672,19 @@
         <v>77873.39999999999</v>
       </c>
       <c r="C7" t="n">
-        <v>970200</v>
+        <v>740880</v>
       </c>
       <c r="D7" t="n">
-        <v>896028.76</v>
+        <v>1697794.56</v>
       </c>
       <c r="E7" t="n">
-        <v>105807.19</v>
+        <v>198130.05</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>1332</v>
+        <v>3888</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -6250,10 +6696,13 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>17493.88</v>
+        <v>30978.73</v>
       </c>
       <c r="L7" t="n">
-        <v>12377.88</v>
+        <v>236520</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -6264,10 +6713,10 @@
         <v>43758</v>
       </c>
       <c r="C8" t="n">
-        <v>110880</v>
+        <v>84672</v>
       </c>
       <c r="D8" t="n">
-        <v>118132.95</v>
+        <v>223838.21</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -6276,7 +6725,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>2164.5</v>
+        <v>6318</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -6291,7 +6740,10 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>2809.04</v>
+        <v>53676</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -6302,19 +6754,19 @@
         <v>21384</v>
       </c>
       <c r="C9" t="n">
-        <v>83160</v>
+        <v>63504</v>
       </c>
       <c r="D9" t="n">
-        <v>96665.17</v>
+        <v>183161.09</v>
       </c>
       <c r="E9" t="n">
-        <v>44388.94</v>
+        <v>83120.85000000001</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>471.75</v>
+        <v>1377</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -6329,7 +6781,10 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1144.53</v>
+        <v>21870</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -6369,6 +6824,9 @@
       <c r="L10" t="n">
         <v>0</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -6407,6 +6865,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -6445,6 +6906,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -6483,6 +6947,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -6521,6 +6988,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -6559,6 +7029,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -6597,6 +7070,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -6635,6 +7111,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -6673,6 +7152,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -6711,6 +7193,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -6749,6 +7234,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -6787,6 +7275,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -6825,6 +7316,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -6863,6 +7357,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -6901,6 +7398,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -6950,6 +7450,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -6964,7 +7468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7035,6 +7539,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -7056,7 +7565,7 @@
         <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>72120</v>
+        <v>72180</v>
       </c>
       <c r="H4" t="n">
         <v>4650</v>
@@ -7071,7 +7580,10 @@
         <v>137</v>
       </c>
       <c r="L4" t="n">
-        <v>107190</v>
+        <v>107280</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -7094,7 +7606,7 @@
         <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>19020</v>
+        <v>19050</v>
       </c>
       <c r="H5" t="n">
         <v>3060</v>
@@ -7110,6 +7622,9 @@
       </c>
       <c r="L5" t="n">
         <v>34710</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -7149,6 +7664,9 @@
       <c r="L6" t="n">
         <v>8700</v>
       </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -7187,6 +7705,9 @@
       <c r="L7" t="n">
         <v>3210</v>
       </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -7225,6 +7746,9 @@
       <c r="L8" t="n">
         <v>1320</v>
       </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -7263,6 +7787,9 @@
       <c r="L9" t="n">
         <v>0</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -7301,6 +7828,9 @@
       <c r="L10" t="n">
         <v>0</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -7339,6 +7869,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -7377,6 +7910,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -7415,6 +7951,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -7453,6 +7992,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -7491,6 +8033,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -7529,6 +8074,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -7567,6 +8115,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -7605,6 +8156,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -7643,6 +8197,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -7681,6 +8238,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -7719,6 +8279,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -7757,6 +8320,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -7795,6 +8361,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -7833,6 +8402,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -7882,6 +8454,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -7896,7 +8472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7967,6 +8543,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -8003,6 +8584,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8038,10 +8622,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>11.34</v>
+        <v>8.94</v>
       </c>
       <c r="L5" t="n">
         <v>7289.1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -8076,10 +8663,13 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>5.2</v>
+        <v>4.06</v>
       </c>
       <c r="L6" t="n">
         <v>3219</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -8114,10 +8704,13 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>2.46</v>
+        <v>1.91</v>
       </c>
       <c r="L7" t="n">
         <v>1926</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -8152,10 +8745,13 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.9</v>
+        <v>0.74</v>
       </c>
       <c r="L8" t="n">
         <v>937.2</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -8195,6 +8791,9 @@
       <c r="L9" t="n">
         <v>0</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -8233,6 +8832,9 @@
       <c r="L10" t="n">
         <v>0</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -8271,6 +8873,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -8309,6 +8914,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -8347,6 +8955,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -8385,6 +8996,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -8423,6 +9037,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -8461,6 +9078,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -8499,6 +9119,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -8537,6 +9160,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -8575,6 +9201,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -8613,6 +9242,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -8651,6 +9283,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -8689,6 +9324,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -8727,6 +9365,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -8765,6 +9406,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -8814,6 +9458,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -8828,7 +9476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8899,6 +9547,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -8935,6 +9588,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8946,13 +9602,13 @@
         <v>4854880.8</v>
       </c>
       <c r="C5" t="n">
-        <v>20216196</v>
+        <v>15437822.4</v>
       </c>
       <c r="D5" t="n">
-        <v>17611840.61</v>
+        <v>33370900.99</v>
       </c>
       <c r="E5" t="n">
-        <v>2341056.61</v>
+        <v>4383763.2</v>
       </c>
       <c r="F5" t="n">
         <v>2500.02</v>
@@ -8961,7 +9617,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>304757.64</v>
+        <v>6279120</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -8970,10 +9626,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>241927.56</v>
+        <v>433944.97</v>
       </c>
       <c r="L5" t="n">
-        <v>68663.32000000001</v>
+        <v>1312038</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -8984,22 +9643,22 @@
         <v>1237737.6</v>
       </c>
       <c r="C6" t="n">
-        <v>7833672</v>
+        <v>5982076.8</v>
       </c>
       <c r="D6" t="n">
-        <v>6388087.2</v>
+        <v>12104142.34</v>
       </c>
       <c r="E6" t="n">
-        <v>1204984.87</v>
+        <v>2256403.5</v>
       </c>
       <c r="F6" t="n">
         <v>8333.4</v>
       </c>
       <c r="G6" t="n">
-        <v>5799.75</v>
+        <v>16929</v>
       </c>
       <c r="H6" t="n">
-        <v>179767.17</v>
+        <v>3703860</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -9008,10 +9667,13 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>110936.8</v>
+        <v>196943.14</v>
       </c>
       <c r="L6" t="n">
-        <v>30322.98</v>
+        <v>579420</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -9022,22 +9684,22 @@
         <v>383159.7</v>
       </c>
       <c r="C7" t="n">
-        <v>3742200</v>
+        <v>2857680</v>
       </c>
       <c r="D7" t="n">
-        <v>3456110.95</v>
+        <v>6548636.16</v>
       </c>
       <c r="E7" t="n">
-        <v>529035.95</v>
+        <v>990650.25</v>
       </c>
       <c r="F7" t="n">
         <v>25000.2</v>
       </c>
       <c r="G7" t="n">
-        <v>5661</v>
+        <v>16524</v>
       </c>
       <c r="H7" t="n">
-        <v>36351.81</v>
+        <v>748980</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -9046,10 +9708,13 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>52481.64</v>
+        <v>92936.17999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>18142.92</v>
+        <v>346680</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -9060,19 +9725,19 @@
         <v>137214</v>
       </c>
       <c r="C8" t="n">
-        <v>748440</v>
+        <v>571536</v>
       </c>
       <c r="D8" t="n">
-        <v>797397.38</v>
+        <v>1510907.9</v>
       </c>
       <c r="E8" t="n">
-        <v>122023.99</v>
+        <v>228496.95</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>4689.75</v>
+        <v>13689</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -9084,10 +9749,13 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>19200.6</v>
+        <v>35737.22</v>
       </c>
       <c r="L8" t="n">
-        <v>8828.42</v>
+        <v>168696</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -9127,6 +9795,9 @@
       <c r="L9" t="n">
         <v>0</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -9165,6 +9836,9 @@
       <c r="L10" t="n">
         <v>0</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -9203,6 +9877,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -9241,6 +9918,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -9279,6 +9959,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -9317,6 +10000,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -9355,6 +10041,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -9393,6 +10082,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -9431,6 +10123,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -9469,6 +10164,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -9507,6 +10205,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -9545,6 +10246,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -9583,6 +10287,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -9621,6 +10328,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -9659,6 +10369,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -9697,6 +10410,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -9746,6 +10462,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -9760,7 +10480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9831,6 +10551,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -9852,10 +10577,10 @@
         <v>30</v>
       </c>
       <c r="G4" t="n">
-        <v>81420</v>
+        <v>81480</v>
       </c>
       <c r="H4" t="n">
-        <v>8910</v>
+        <v>8880</v>
       </c>
       <c r="I4" t="n">
         <v>5</v>
@@ -9867,7 +10592,10 @@
         <v>230</v>
       </c>
       <c r="L4" t="n">
-        <v>193620</v>
+        <v>194130</v>
+      </c>
+      <c r="M4" t="n">
+        <v>16830</v>
       </c>
     </row>
     <row r="5">
@@ -9890,7 +10618,7 @@
         <v>21</v>
       </c>
       <c r="G5" t="n">
-        <v>86370</v>
+        <v>86400</v>
       </c>
       <c r="H5" t="n">
         <v>7440</v>
@@ -9905,7 +10633,10 @@
         <v>171</v>
       </c>
       <c r="L5" t="n">
-        <v>193410</v>
+        <v>193380</v>
+      </c>
+      <c r="M5" t="n">
+        <v>18690</v>
       </c>
     </row>
     <row r="6">
@@ -9928,10 +10659,10 @@
         <v>4</v>
       </c>
       <c r="G6" t="n">
-        <v>84600</v>
+        <v>84660</v>
       </c>
       <c r="H6" t="n">
-        <v>12210</v>
+        <v>12180</v>
       </c>
       <c r="I6" t="n">
         <v>1</v>
@@ -9943,7 +10674,10 @@
         <v>219</v>
       </c>
       <c r="L6" t="n">
-        <v>208590</v>
+        <v>208650</v>
+      </c>
+      <c r="M6" t="n">
+        <v>11160</v>
       </c>
     </row>
     <row r="7">
@@ -9966,10 +10700,10 @@
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>66600</v>
+        <v>66630</v>
       </c>
       <c r="H7" t="n">
-        <v>4470</v>
+        <v>4500</v>
       </c>
       <c r="I7" t="n">
         <v>3</v>
@@ -9981,7 +10715,10 @@
         <v>134</v>
       </c>
       <c r="L7" t="n">
-        <v>137550</v>
+        <v>137640</v>
+      </c>
+      <c r="M7" t="n">
+        <v>6990</v>
       </c>
     </row>
     <row r="8">
@@ -10004,7 +10741,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>40050</v>
+        <v>40140</v>
       </c>
       <c r="H8" t="n">
         <v>600</v>
@@ -10019,7 +10756,10 @@
         <v>92</v>
       </c>
       <c r="L8" t="n">
-        <v>84030</v>
+        <v>84090</v>
+      </c>
+      <c r="M8" t="n">
+        <v>3690</v>
       </c>
     </row>
     <row r="9">
@@ -10054,10 +10794,13 @@
         <v>2</v>
       </c>
       <c r="K9" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L9" t="n">
         <v>43200</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2190</v>
       </c>
     </row>
     <row r="10">
@@ -10097,6 +10840,9 @@
       <c r="L10" t="n">
         <v>10680</v>
       </c>
+      <c r="M10" t="n">
+        <v>990</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -10135,6 +10881,9 @@
       <c r="L11" t="n">
         <v>4620</v>
       </c>
+      <c r="M11" t="n">
+        <v>330</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -10173,6 +10922,9 @@
       <c r="L12" t="n">
         <v>3450</v>
       </c>
+      <c r="M12" t="n">
+        <v>240</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -10211,6 +10963,9 @@
       <c r="L13" t="n">
         <v>1440</v>
       </c>
+      <c r="M13" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -10249,6 +11004,9 @@
       <c r="L14" t="n">
         <v>480</v>
       </c>
+      <c r="M14" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -10287,6 +11045,9 @@
       <c r="L15" t="n">
         <v>390</v>
       </c>
+      <c r="M15" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -10325,6 +11086,9 @@
       <c r="L16" t="n">
         <v>300</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -10363,6 +11127,9 @@
       <c r="L17" t="n">
         <v>300</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -10401,6 +11168,9 @@
       <c r="L18" t="n">
         <v>660</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -10439,6 +11209,9 @@
       <c r="L19" t="n">
         <v>120</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -10477,6 +11250,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -10515,6 +11291,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -10553,6 +11332,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -10591,6 +11373,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -10629,6 +11414,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -10678,6 +11466,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -10692,7 +11484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10763,6 +11555,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -10799,6 +11596,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10807,7 +11607,7 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>49623.44</v>
+        <v>49550.58</v>
       </c>
       <c r="C5" t="n">
         <v>10673031.6</v>
@@ -10828,16 +11628,19 @@
         <v>17550</v>
       </c>
       <c r="I5" t="n">
-        <v>0.45</v>
+        <v>0.99</v>
       </c>
       <c r="J5" t="n">
         <v>7.8</v>
       </c>
       <c r="K5" t="n">
-        <v>242.34</v>
+        <v>187.68</v>
       </c>
       <c r="L5" t="n">
-        <v>179625.6</v>
+        <v>179203.5</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1009.8</v>
       </c>
     </row>
     <row r="6">
@@ -10845,7 +11648,7 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>68907.24000000001</v>
+        <v>68796.14</v>
       </c>
       <c r="C6" t="n">
         <v>12879972</v>
@@ -10860,22 +11663,25 @@
         <v>5.4</v>
       </c>
       <c r="G6" t="n">
-        <v>12502.5</v>
+        <v>12465</v>
       </c>
       <c r="H6" t="n">
         <v>32113.8</v>
       </c>
       <c r="I6" t="n">
-        <v>0.35</v>
+        <v>0.51</v>
       </c>
       <c r="J6" t="n">
         <v>5</v>
       </c>
       <c r="K6" t="n">
-        <v>330.85</v>
+        <v>257.56</v>
       </c>
       <c r="L6" t="n">
-        <v>235586.4</v>
+        <v>234942.6</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2450.4</v>
       </c>
     </row>
     <row r="7">
@@ -10883,7 +11689,7 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>68694.89</v>
+        <v>68650.94</v>
       </c>
       <c r="C7" t="n">
         <v>8772624</v>
@@ -10898,22 +11704,25 @@
         <v>17.4</v>
       </c>
       <c r="G7" t="n">
-        <v>30780</v>
+        <v>30712.5</v>
       </c>
       <c r="H7" t="n">
         <v>21943.8</v>
       </c>
       <c r="I7" t="n">
-        <v>2.2</v>
+        <v>2.55</v>
       </c>
       <c r="J7" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>323.08</v>
+        <v>251.37</v>
       </c>
       <c r="L7" t="n">
-        <v>302814</v>
+        <v>302220</v>
+      </c>
+      <c r="M7" t="n">
+        <v>7329</v>
       </c>
     </row>
     <row r="8">
@@ -10921,7 +11730,7 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>62453.61</v>
+        <v>62453.16</v>
       </c>
       <c r="C8" t="n">
         <v>7014672</v>
@@ -10936,22 +11745,25 @@
         <v>16.15</v>
       </c>
       <c r="G8" t="n">
-        <v>107913</v>
+        <v>107620.5</v>
       </c>
       <c r="H8" t="n">
         <v>6834</v>
       </c>
       <c r="I8" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="J8" t="n">
         <v>4.25</v>
       </c>
       <c r="K8" t="n">
-        <v>299.7</v>
+        <v>245.09</v>
       </c>
       <c r="L8" t="n">
-        <v>282842.7</v>
+        <v>282331.5</v>
+      </c>
+      <c r="M8" t="n">
+        <v>7956</v>
       </c>
     </row>
     <row r="9">
@@ -10974,7 +11786,7 @@
         <v>18</v>
       </c>
       <c r="G9" t="n">
-        <v>115693.5</v>
+        <v>115413</v>
       </c>
       <c r="H9" t="n">
         <v>3870</v>
@@ -10986,10 +11798,13 @@
         <v>8.550000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>267</v>
+        <v>214.4</v>
       </c>
       <c r="L9" t="n">
-        <v>236171.7</v>
+        <v>235880.1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>10440</v>
       </c>
     </row>
     <row r="10">
@@ -10997,7 +11812,7 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>31503.15</v>
+        <v>31502.88</v>
       </c>
       <c r="C10" t="n">
         <v>2778552</v>
@@ -11018,16 +11833,19 @@
         <v>4890</v>
       </c>
       <c r="I10" t="n">
-        <v>2.88</v>
+        <v>2.61</v>
       </c>
       <c r="J10" t="n">
         <v>3</v>
       </c>
       <c r="K10" t="n">
-        <v>172</v>
+        <v>149.64</v>
       </c>
       <c r="L10" t="n">
-        <v>158678.1</v>
+        <v>158598</v>
+      </c>
+      <c r="M10" t="n">
+        <v>6840</v>
       </c>
     </row>
     <row r="11">
@@ -11035,7 +11853,7 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>22911.84</v>
+        <v>22911.75</v>
       </c>
       <c r="C11" t="n">
         <v>1611288</v>
@@ -11062,10 +11880,13 @@
         <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>104</v>
+        <v>93.44</v>
       </c>
       <c r="L11" t="n">
-        <v>162840</v>
+        <v>162570</v>
+      </c>
+      <c r="M11" t="n">
+        <v>3660</v>
       </c>
     </row>
     <row r="12">
@@ -11100,10 +11921,13 @@
         <v>3</v>
       </c>
       <c r="K12" t="n">
-        <v>66</v>
+        <v>61.18</v>
       </c>
       <c r="L12" t="n">
-        <v>97140</v>
+        <v>96930</v>
+      </c>
+      <c r="M12" t="n">
+        <v>2850</v>
       </c>
     </row>
     <row r="13">
@@ -11132,16 +11956,19 @@
         <v>840</v>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>28</v>
+        <v>26.59</v>
       </c>
       <c r="L13" t="n">
         <v>42900</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1410</v>
       </c>
     </row>
     <row r="14">
@@ -11176,10 +12003,13 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>11</v>
+        <v>10.69</v>
       </c>
       <c r="L14" t="n">
         <v>16410</v>
+      </c>
+      <c r="M14" t="n">
+        <v>300</v>
       </c>
     </row>
     <row r="15">
@@ -11214,10 +12044,13 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="L15" t="n">
         <v>6780</v>
+      </c>
+      <c r="M15" t="n">
+        <v>150</v>
       </c>
     </row>
     <row r="16">
@@ -11257,6 +12090,9 @@
       <c r="L16" t="n">
         <v>2160</v>
       </c>
+      <c r="M16" t="n">
+        <v>210</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -11295,6 +12131,9 @@
       <c r="L17" t="n">
         <v>1440</v>
       </c>
+      <c r="M17" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -11333,6 +12172,9 @@
       <c r="L18" t="n">
         <v>1530</v>
       </c>
+      <c r="M18" t="n">
+        <v>120</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -11371,6 +12213,9 @@
       <c r="L19" t="n">
         <v>780</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -11409,6 +12254,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -11447,6 +12295,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -11485,6 +12336,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -11523,6 +12377,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -11561,6 +12418,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -11610,6 +12470,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -11624,7 +12488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11695,6 +12559,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -11731,6 +12600,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11760,16 +12632,19 @@
         <v>2678.4</v>
       </c>
       <c r="I5" t="n">
-        <v>0.45</v>
+        <v>0.99</v>
       </c>
       <c r="J5" t="n">
         <v>3.3</v>
       </c>
       <c r="K5" t="n">
-        <v>71.81999999999999</v>
+        <v>56.6</v>
       </c>
       <c r="L5" t="n">
-        <v>40616.1</v>
+        <v>40609.8</v>
+      </c>
+      <c r="M5" t="n">
+        <v>373.8</v>
       </c>
     </row>
     <row r="6">
@@ -11792,22 +12667,25 @@
         <v>0.4</v>
       </c>
       <c r="G6" t="n">
-        <v>4230</v>
+        <v>4233</v>
       </c>
       <c r="H6" t="n">
-        <v>6959.7</v>
+        <v>6942.6</v>
       </c>
       <c r="I6" t="n">
-        <v>0.35</v>
+        <v>0.51</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>142.35</v>
+        <v>111.03</v>
       </c>
       <c r="L6" t="n">
-        <v>77178.3</v>
+        <v>77200.5</v>
+      </c>
+      <c r="M6" t="n">
+        <v>892.8</v>
       </c>
     </row>
     <row r="7">
@@ -11830,22 +12708,25 @@
         <v>0.6</v>
       </c>
       <c r="G7" t="n">
-        <v>9990</v>
+        <v>9994.5</v>
       </c>
       <c r="H7" t="n">
-        <v>3263.1</v>
+        <v>3285</v>
       </c>
       <c r="I7" t="n">
-        <v>1.65</v>
+        <v>1.91</v>
       </c>
       <c r="J7" t="n">
         <v>2.1</v>
       </c>
       <c r="K7" t="n">
-        <v>109.88</v>
+        <v>85.48999999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>82530</v>
+        <v>82584</v>
+      </c>
+      <c r="M7" t="n">
+        <v>2446.5</v>
       </c>
     </row>
     <row r="8">
@@ -11868,7 +12749,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>26032.5</v>
+        <v>26091</v>
       </c>
       <c r="H8" t="n">
         <v>510</v>
@@ -11880,10 +12761,13 @@
         <v>0.85</v>
       </c>
       <c r="K8" t="n">
-        <v>82.8</v>
+        <v>67.70999999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>59661.3</v>
+        <v>59703.9</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2214</v>
       </c>
     </row>
     <row r="9">
@@ -11918,10 +12802,13 @@
         <v>1.9</v>
       </c>
       <c r="K9" t="n">
-        <v>50</v>
+        <v>40.95</v>
       </c>
       <c r="L9" t="n">
         <v>34992</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2190</v>
       </c>
     </row>
     <row r="10">
@@ -11950,16 +12837,19 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0.96</v>
+        <v>0.87</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>8</v>
+        <v>6.96</v>
       </c>
       <c r="L10" t="n">
         <v>9505.200000000001</v>
+      </c>
+      <c r="M10" t="n">
+        <v>990</v>
       </c>
     </row>
     <row r="11">
@@ -11994,10 +12884,13 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="L11" t="n">
         <v>4620</v>
+      </c>
+      <c r="M11" t="n">
+        <v>330</v>
       </c>
     </row>
     <row r="12">
@@ -12037,6 +12930,9 @@
       <c r="L12" t="n">
         <v>3450</v>
       </c>
+      <c r="M12" t="n">
+        <v>240</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -12075,6 +12971,9 @@
       <c r="L13" t="n">
         <v>1440</v>
       </c>
+      <c r="M13" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -12113,6 +13012,9 @@
       <c r="L14" t="n">
         <v>480</v>
       </c>
+      <c r="M14" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -12151,6 +13053,9 @@
       <c r="L15" t="n">
         <v>390</v>
       </c>
+      <c r="M15" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -12189,6 +13094,9 @@
       <c r="L16" t="n">
         <v>300</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -12227,6 +13135,9 @@
       <c r="L17" t="n">
         <v>300</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -12265,6 +13176,9 @@
       <c r="L18" t="n">
         <v>660</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -12303,6 +13217,9 @@
       <c r="L19" t="n">
         <v>120</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -12341,6 +13258,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -12379,6 +13299,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -12417,6 +13340,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -12455,6 +13381,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -12493,6 +13422,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -12542,6 +13474,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -12556,7 +13492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12627,6 +13563,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -12663,6 +13604,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12674,13 +13618,13 @@
         <v>29212771.5</v>
       </c>
       <c r="C5" t="n">
-        <v>139409424</v>
+        <v>106458105.6</v>
       </c>
       <c r="D5" t="n">
-        <v>121449977.8</v>
+        <v>230123317.25</v>
       </c>
       <c r="E5" t="n">
-        <v>21453589.13</v>
+        <v>40173079.95</v>
       </c>
       <c r="F5" t="n">
         <v>17500.14</v>
@@ -12689,19 +13633,22 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>740979.36</v>
+        <v>15266880</v>
       </c>
       <c r="I5" t="n">
-        <v>172498.5</v>
+        <v>192864.43</v>
       </c>
       <c r="J5" t="n">
-        <v>192498.9</v>
+        <v>80117.39999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>1532207.88</v>
+        <v>2748318.16</v>
       </c>
       <c r="L5" t="n">
-        <v>382603.66</v>
+        <v>7309764</v>
+      </c>
+      <c r="M5" t="n">
+        <v>112140</v>
       </c>
     </row>
     <row r="6">
@@ -12712,34 +13659,37 @@
         <v>61273238.4</v>
       </c>
       <c r="C6" t="n">
-        <v>244640088</v>
+        <v>186816067.2</v>
       </c>
       <c r="D6" t="n">
-        <v>199495487.61</v>
+        <v>378003884.54</v>
       </c>
       <c r="E6" t="n">
-        <v>28947659.83</v>
+        <v>54206158.5</v>
       </c>
       <c r="F6" t="n">
         <v>16666.8</v>
       </c>
       <c r="G6" t="n">
-        <v>78255</v>
+        <v>228582</v>
       </c>
       <c r="H6" t="n">
-        <v>1925401</v>
+        <v>39572820</v>
       </c>
       <c r="I6" t="n">
-        <v>134165.5</v>
+        <v>98471.57000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>58333</v>
+        <v>24278</v>
       </c>
       <c r="K6" t="n">
-        <v>3036894.9</v>
+        <v>5391318.35</v>
       </c>
       <c r="L6" t="n">
-        <v>727019.59</v>
+        <v>13896090</v>
+      </c>
+      <c r="M6" t="n">
+        <v>267840</v>
       </c>
     </row>
     <row r="7">
@@ -12750,34 +13700,37 @@
         <v>59760686.7</v>
       </c>
       <c r="C7" t="n">
-        <v>135828000</v>
+        <v>103723200</v>
       </c>
       <c r="D7" t="n">
-        <v>125444027.02</v>
+        <v>237691238.4</v>
       </c>
       <c r="E7" t="n">
-        <v>10968678.66</v>
+        <v>20539481.85</v>
       </c>
       <c r="F7" t="n">
         <v>25000.2</v>
       </c>
       <c r="G7" t="n">
-        <v>184815</v>
+        <v>539703</v>
       </c>
       <c r="H7" t="n">
-        <v>902736.61</v>
+        <v>18724500</v>
       </c>
       <c r="I7" t="n">
-        <v>632494.5</v>
+        <v>371744.74</v>
       </c>
       <c r="J7" t="n">
-        <v>122499.3</v>
+        <v>50983.8</v>
       </c>
       <c r="K7" t="n">
-        <v>2344179.92</v>
+        <v>4151149.55</v>
       </c>
       <c r="L7" t="n">
-        <v>777432.6</v>
+        <v>14865120</v>
+      </c>
+      <c r="M7" t="n">
+        <v>733950</v>
       </c>
     </row>
     <row r="8">
@@ -12788,34 +13741,37 @@
         <v>52247052</v>
       </c>
       <c r="C8" t="n">
-        <v>95772600</v>
+        <v>73135440</v>
       </c>
       <c r="D8" t="n">
-        <v>102037332.04</v>
+        <v>193340252.16</v>
       </c>
       <c r="E8" t="n">
-        <v>6385922.37</v>
+        <v>11958007.05</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>481601.25</v>
+        <v>1408914</v>
       </c>
       <c r="H8" t="n">
-        <v>141091.5</v>
+        <v>2907000</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>49583.05</v>
+        <v>20636.3</v>
       </c>
       <c r="K8" t="n">
-        <v>1766455.2</v>
+        <v>3287823.87</v>
       </c>
       <c r="L8" t="n">
-        <v>562009.45</v>
+        <v>10746702</v>
+      </c>
+      <c r="M8" t="n">
+        <v>664200</v>
       </c>
     </row>
     <row r="9">
@@ -12826,19 +13782,19 @@
         <v>31888098</v>
       </c>
       <c r="C9" t="n">
-        <v>51559200</v>
+        <v>39372480</v>
       </c>
       <c r="D9" t="n">
-        <v>59932406.71</v>
+        <v>113559874.56</v>
       </c>
       <c r="E9" t="n">
-        <v>2618947.65</v>
+        <v>4904130.15</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>342018.75</v>
+        <v>998325</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -12847,13 +13803,16 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>110832.7</v>
+        <v>46128.2</v>
       </c>
       <c r="K9" t="n">
-        <v>1066700</v>
+        <v>1988513.87</v>
       </c>
       <c r="L9" t="n">
-        <v>329624.64</v>
+        <v>6298560</v>
+      </c>
+      <c r="M9" t="n">
+        <v>657000</v>
       </c>
     </row>
     <row r="10">
@@ -12864,34 +13823,37 @@
         <v>3945744</v>
       </c>
       <c r="C10" t="n">
-        <v>7983360</v>
+        <v>6096384</v>
       </c>
       <c r="D10" t="n">
-        <v>10054140.94</v>
+        <v>19050577.92</v>
       </c>
       <c r="E10" t="n">
-        <v>240433.2</v>
+        <v>450225</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>53280</v>
+        <v>155520</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>367996.8</v>
+        <v>168974.88</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>170672</v>
+        <v>337949.76</v>
       </c>
       <c r="L10" t="n">
-        <v>89538.98</v>
+        <v>1710936</v>
+      </c>
+      <c r="M10" t="n">
+        <v>297000</v>
       </c>
     </row>
     <row r="11">
@@ -12902,22 +13864,22 @@
         <v>656370</v>
       </c>
       <c r="C11" t="n">
-        <v>1580040</v>
+        <v>1206576</v>
       </c>
       <c r="D11" t="n">
-        <v>2055067.85</v>
+        <v>3893940.86</v>
       </c>
       <c r="E11" t="n">
-        <v>67951.39999999999</v>
+        <v>127242.9</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>17205</v>
+        <v>50220</v>
       </c>
       <c r="H11" t="n">
-        <v>8299.5</v>
+        <v>171000</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -12926,10 +13888,13 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>42668</v>
+        <v>87255.13</v>
       </c>
       <c r="L11" t="n">
-        <v>43520.4</v>
+        <v>831600</v>
+      </c>
+      <c r="M11" t="n">
+        <v>99000</v>
       </c>
     </row>
     <row r="12">
@@ -12940,19 +13905,19 @@
         <v>423522</v>
       </c>
       <c r="C12" t="n">
-        <v>582120</v>
+        <v>444528</v>
       </c>
       <c r="D12" t="n">
-        <v>781146.08</v>
+        <v>1480114.94</v>
       </c>
       <c r="E12" t="n">
-        <v>79260.05</v>
+        <v>148419</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>4440</v>
+        <v>12960</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -12967,7 +13932,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>32499</v>
+        <v>621000</v>
+      </c>
+      <c r="M12" t="n">
+        <v>72000</v>
       </c>
     </row>
     <row r="13">
@@ -12978,10 +13946,10 @@
         <v>248490</v>
       </c>
       <c r="C13" t="n">
-        <v>138600</v>
+        <v>105840</v>
       </c>
       <c r="D13" t="n">
-        <v>190501.41</v>
+        <v>360961.92</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -12990,7 +13958,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>4440</v>
+        <v>12960</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -13005,7 +13973,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>13564.8</v>
+        <v>259200</v>
+      </c>
+      <c r="M13" t="n">
+        <v>45000</v>
       </c>
     </row>
     <row r="14">
@@ -13016,19 +13987,19 @@
         <v>30096</v>
       </c>
       <c r="C14" t="n">
-        <v>138600</v>
+        <v>105840</v>
       </c>
       <c r="D14" t="n">
-        <v>195015.66</v>
+        <v>369515.52</v>
       </c>
       <c r="E14" t="n">
-        <v>94399.05</v>
+        <v>176767.65</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>1110</v>
+        <v>3240</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -13043,7 +14014,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>4521.6</v>
+        <v>86400</v>
+      </c>
+      <c r="M14" t="n">
+        <v>9000</v>
       </c>
     </row>
     <row r="15">
@@ -13054,10 +14028,10 @@
         <v>38412</v>
       </c>
       <c r="C15" t="n">
-        <v>83160</v>
+        <v>63504</v>
       </c>
       <c r="D15" t="n">
-        <v>118694.72</v>
+        <v>224902.66</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -13066,7 +14040,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>3330</v>
+        <v>9720</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -13081,7 +14055,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>3673.8</v>
+        <v>70200</v>
+      </c>
+      <c r="M15" t="n">
+        <v>9000</v>
       </c>
     </row>
     <row r="16">
@@ -13092,10 +14069,10 @@
         <v>23562</v>
       </c>
       <c r="C16" t="n">
-        <v>83160</v>
+        <v>63504</v>
       </c>
       <c r="D16" t="n">
-        <v>120380.04</v>
+        <v>228096</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -13104,7 +14081,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>1665</v>
+        <v>4860</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -13119,7 +14096,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>2826</v>
+        <v>54000</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -13130,10 +14110,10 @@
         <v>11286</v>
       </c>
       <c r="C17" t="n">
-        <v>27720</v>
+        <v>21168</v>
       </c>
       <c r="D17" t="n">
-        <v>40126.68</v>
+        <v>76032</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -13142,7 +14122,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>2775</v>
+        <v>8100</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -13157,7 +14137,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>2826</v>
+        <v>54000</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -13168,10 +14151,10 @@
         <v>3762</v>
       </c>
       <c r="C18" t="n">
-        <v>27720</v>
+        <v>21168</v>
       </c>
       <c r="D18" t="n">
-        <v>40126.68</v>
+        <v>76032</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -13180,7 +14163,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>3885</v>
+        <v>11340</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -13195,7 +14178,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>6217.2</v>
+        <v>118800</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -13206,10 +14192,10 @@
         <v>198</v>
       </c>
       <c r="C19" t="n">
-        <v>194040</v>
+        <v>148176</v>
       </c>
       <c r="D19" t="n">
-        <v>280886.76</v>
+        <v>532224</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -13218,7 +14204,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>68265</v>
+        <v>199260</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -13233,7 +14219,10 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>1130.4</v>
+        <v>21600</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -13244,10 +14233,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>110880</v>
+        <v>84672</v>
       </c>
       <c r="D20" t="n">
-        <v>160506.72</v>
+        <v>304128</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -13271,6 +14260,9 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13311,6 +14303,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -13320,10 +14315,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>55440</v>
+        <v>42336</v>
       </c>
       <c r="D22" t="n">
-        <v>80253.36</v>
+        <v>152064</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -13347,6 +14342,9 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13358,10 +14356,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>27720</v>
+        <v>21168</v>
       </c>
       <c r="D23" t="n">
-        <v>40126.68</v>
+        <v>76032</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -13385,6 +14383,9 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13396,10 +14397,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>166320</v>
+        <v>127008</v>
       </c>
       <c r="D24" t="n">
-        <v>240760.08</v>
+        <v>456192</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -13423,6 +14424,9 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13474,6 +14478,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -13488,7 +14496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13559,6 +14567,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -13580,7 +14593,7 @@
         <v>33</v>
       </c>
       <c r="G4" t="n">
-        <v>88950</v>
+        <v>89010</v>
       </c>
       <c r="H4" t="n">
         <v>10320</v>
@@ -13595,7 +14608,10 @@
         <v>102</v>
       </c>
       <c r="L4" t="n">
-        <v>287370</v>
+        <v>289500</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -13618,7 +14634,7 @@
         <v>7</v>
       </c>
       <c r="G5" t="n">
-        <v>20160</v>
+        <v>20280</v>
       </c>
       <c r="H5" t="n">
         <v>2040</v>
@@ -13633,7 +14649,10 @@
         <v>20</v>
       </c>
       <c r="L5" t="n">
-        <v>85050</v>
+        <v>85800</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -13656,7 +14675,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>2100</v>
+        <v>2130</v>
       </c>
       <c r="H6" t="n">
         <v>300</v>
@@ -13671,7 +14690,10 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>12780</v>
+        <v>12960</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -13711,6 +14733,9 @@
       <c r="L7" t="n">
         <v>1230</v>
       </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -13749,6 +14774,9 @@
       <c r="L8" t="n">
         <v>210</v>
       </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -13787,6 +14815,9 @@
       <c r="L9" t="n">
         <v>60</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -13825,6 +14856,9 @@
       <c r="L10" t="n">
         <v>150</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -13863,6 +14897,9 @@
       <c r="L11" t="n">
         <v>90</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -13901,6 +14938,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -13939,6 +14979,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -13977,6 +15020,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -14015,6 +15061,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -14053,6 +15102,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -14091,6 +15143,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -14129,6 +15184,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -14167,6 +15225,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -14205,6 +15266,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -14243,6 +15307,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -14281,6 +15348,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -14319,6 +15389,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -14357,6 +15430,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -14406,6 +15482,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -14420,7 +15500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14491,6 +15571,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -14527,6 +15612,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14562,10 +15650,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>8.4</v>
+        <v>6.62</v>
       </c>
       <c r="L5" t="n">
-        <v>17860.5</v>
+        <v>18018</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -14588,7 +15679,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>105</v>
+        <v>106.5</v>
       </c>
       <c r="H6" t="n">
         <v>171</v>
@@ -14603,7 +15694,10 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>4728.6</v>
+        <v>4795.2</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -14643,6 +15737,9 @@
       <c r="L7" t="n">
         <v>738</v>
       </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -14681,6 +15778,9 @@
       <c r="L8" t="n">
         <v>149.1</v>
       </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -14719,6 +15819,9 @@
       <c r="L9" t="n">
         <v>48.6</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -14757,6 +15860,9 @@
       <c r="L10" t="n">
         <v>133.5</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -14795,6 +15901,9 @@
       <c r="L11" t="n">
         <v>90</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -14833,6 +15942,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -14871,6 +15983,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -14909,6 +16024,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -14947,6 +16065,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -14985,6 +16106,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -15023,6 +16147,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -15061,6 +16188,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -15099,6 +16229,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -15137,6 +16270,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -15175,6 +16311,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -15213,6 +16352,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -15251,6 +16393,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -15289,6 +16434,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -15338,6 +16486,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -15352,7 +16504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15423,6 +16575,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -15459,6 +16616,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15470,13 +16630,13 @@
         <v>8478132.300000001</v>
       </c>
       <c r="C5" t="n">
-        <v>17548146</v>
+        <v>13400402.4</v>
       </c>
       <c r="D5" t="n">
-        <v>15287502.67</v>
+        <v>28966747.39</v>
       </c>
       <c r="E5" t="n">
-        <v>4389481.15</v>
+        <v>8219556</v>
       </c>
       <c r="F5" t="n">
         <v>5833.38</v>
@@ -15485,7 +16645,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>203171.76</v>
+        <v>4186080</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -15494,10 +16654,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>179205.6</v>
+        <v>321440.72</v>
       </c>
       <c r="L5" t="n">
-        <v>168245.91</v>
+        <v>3243240</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -15508,22 +16671,22 @@
         <v>1334044.8</v>
       </c>
       <c r="C6" t="n">
-        <v>3243240</v>
+        <v>2476656</v>
       </c>
       <c r="D6" t="n">
-        <v>2644749.48</v>
+        <v>5011269.12</v>
       </c>
       <c r="E6" t="n">
-        <v>644526.79</v>
+        <v>1206913.5</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>1942.5</v>
+        <v>5751</v>
       </c>
       <c r="H6" t="n">
-        <v>47307.15</v>
+        <v>974700</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -15535,7 +16698,10 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>44543.41</v>
+        <v>863136</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -15546,19 +16712,19 @@
         <v>229858.2</v>
       </c>
       <c r="C7" t="n">
-        <v>776160</v>
+        <v>592704</v>
       </c>
       <c r="D7" t="n">
-        <v>716823.01</v>
+        <v>1358235.65</v>
       </c>
       <c r="E7" t="n">
-        <v>105807.19</v>
+        <v>198130.05</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>166.5</v>
+        <v>486</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -15573,7 +16739,10 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>6951.96</v>
+        <v>132840</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -15596,7 +16765,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>721.5</v>
+        <v>2106</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -15611,7 +16780,10 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>1404.52</v>
+        <v>26838</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -15634,7 +16806,7 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>471.75</v>
+        <v>1377</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -15649,7 +16821,10 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>457.81</v>
+        <v>8748</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -15687,7 +16862,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>1257.57</v>
+        <v>24030</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -15725,7 +16903,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>847.8</v>
+        <v>16200</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -15765,6 +16946,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -15803,6 +16987,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -15841,6 +17028,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -15879,6 +17069,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -15917,6 +17110,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -15955,6 +17151,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -15993,6 +17192,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -16031,6 +17233,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -16069,6 +17274,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -16107,6 +17315,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -16145,6 +17356,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -16183,6 +17397,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -16221,6 +17438,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -16270,6 +17490,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -16284,7 +17508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16355,6 +17579,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -16391,6 +17620,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -16399,16 +17631,16 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>109171557</v>
+        <v>109011266.1</v>
       </c>
       <c r="C5" t="n">
-        <v>587016738</v>
+        <v>448267327.2</v>
       </c>
       <c r="D5" t="n">
-        <v>511394192.37</v>
+        <v>968989291.78</v>
       </c>
       <c r="E5" t="n">
-        <v>99275432.05</v>
+        <v>185898958.2</v>
       </c>
       <c r="F5" t="n">
         <v>71667.24000000001</v>
@@ -16417,19 +17649,22 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>4855207.5</v>
+        <v>100035000</v>
       </c>
       <c r="I5" t="n">
-        <v>172498.5</v>
+        <v>192864.43</v>
       </c>
       <c r="J5" t="n">
-        <v>454997.4</v>
+        <v>189368.4</v>
       </c>
       <c r="K5" t="n">
-        <v>5170081.56</v>
+        <v>9112844.41</v>
       </c>
       <c r="L5" t="n">
-        <v>1692073.15</v>
+        <v>32256630</v>
+      </c>
+      <c r="M5" t="n">
+        <v>302940</v>
       </c>
     </row>
     <row r="6">
@@ -16437,37 +17672,40 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>151595928</v>
+        <v>151351516.8</v>
       </c>
       <c r="C6" t="n">
-        <v>708398460</v>
+        <v>540958824</v>
       </c>
       <c r="D6" t="n">
-        <v>577674318.85</v>
+        <v>1094576820.48</v>
       </c>
       <c r="E6" t="n">
-        <v>113352646.68</v>
+        <v>212259352.5</v>
       </c>
       <c r="F6" t="n">
         <v>225001.8</v>
       </c>
       <c r="G6" t="n">
-        <v>231296.25</v>
+        <v>673110</v>
       </c>
       <c r="H6" t="n">
-        <v>8884282.77</v>
+        <v>183048660</v>
       </c>
       <c r="I6" t="n">
-        <v>134165.5</v>
+        <v>98471.57000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>291665</v>
+        <v>121390</v>
       </c>
       <c r="K6" t="n">
-        <v>7058353.9</v>
+        <v>12505889.14</v>
       </c>
       <c r="L6" t="n">
-        <v>2219223.89</v>
+        <v>42289668</v>
+      </c>
+      <c r="M6" t="n">
+        <v>735120</v>
       </c>
     </row>
     <row r="7">
@@ -16475,37 +17713,40 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>151128756.9</v>
+        <v>151032073.5</v>
       </c>
       <c r="C7" t="n">
-        <v>482494320</v>
+        <v>368450208</v>
       </c>
       <c r="D7" t="n">
-        <v>445607904.95</v>
+        <v>844337488.9</v>
       </c>
       <c r="E7" t="n">
-        <v>91981716.83</v>
+        <v>172241056.8</v>
       </c>
       <c r="F7" t="n">
         <v>725005.8</v>
       </c>
       <c r="G7" t="n">
-        <v>569430</v>
+        <v>1658475</v>
       </c>
       <c r="H7" t="n">
-        <v>6070752.27</v>
+        <v>125079660</v>
       </c>
       <c r="I7" t="n">
-        <v>843326</v>
+        <v>495659.65</v>
       </c>
       <c r="J7" t="n">
-        <v>571663.4</v>
+        <v>237924.4</v>
       </c>
       <c r="K7" t="n">
-        <v>6892588.72</v>
+        <v>12205618.83</v>
       </c>
       <c r="L7" t="n">
-        <v>2852507.88</v>
+        <v>54399600</v>
+      </c>
+      <c r="M7" t="n">
+        <v>2198700</v>
       </c>
     </row>
     <row r="8">
@@ -16513,37 +17754,40 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>137397942</v>
+        <v>137396952</v>
       </c>
       <c r="C8" t="n">
-        <v>385806960</v>
+        <v>294616224</v>
       </c>
       <c r="D8" t="n">
-        <v>411043585.33</v>
+        <v>778845044.74</v>
       </c>
       <c r="E8" t="n">
-        <v>84521953.45</v>
+        <v>158272220.7</v>
       </c>
       <c r="F8" t="n">
         <v>672922.05</v>
       </c>
       <c r="G8" t="n">
-        <v>1996390.5</v>
+        <v>5811507</v>
       </c>
       <c r="H8" t="n">
-        <v>1890626.1</v>
+        <v>38953800</v>
       </c>
       <c r="I8" t="n">
-        <v>275997.6</v>
+        <v>142948.86</v>
       </c>
       <c r="J8" t="n">
-        <v>247915.25</v>
+        <v>103181.5</v>
       </c>
       <c r="K8" t="n">
-        <v>6393799.8</v>
+        <v>11900492.93</v>
       </c>
       <c r="L8" t="n">
-        <v>2664378.23</v>
+        <v>50819670</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2386800</v>
       </c>
     </row>
     <row r="9">
@@ -16554,34 +17798,37 @@
         <v>113198382</v>
       </c>
       <c r="C9" t="n">
-        <v>294192360</v>
+        <v>224655984</v>
       </c>
       <c r="D9" t="n">
-        <v>341969157.24</v>
+        <v>647962875.65</v>
       </c>
       <c r="E9" t="n">
-        <v>60768463.24</v>
+        <v>113792443.65</v>
       </c>
       <c r="F9" t="n">
         <v>750006</v>
       </c>
       <c r="G9" t="n">
-        <v>2140329.75</v>
+        <v>6232302</v>
       </c>
       <c r="H9" t="n">
-        <v>1070635.5</v>
+        <v>22059000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>498747.15</v>
+        <v>207576.9</v>
       </c>
       <c r="K9" t="n">
-        <v>5696178</v>
+        <v>10410454.96</v>
       </c>
       <c r="L9" t="n">
-        <v>2224737.41</v>
+        <v>42458418</v>
+      </c>
+      <c r="M9" t="n">
+        <v>3132000</v>
       </c>
     </row>
     <row r="10">
@@ -16589,37 +17836,40 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>69306930</v>
+        <v>69306336</v>
       </c>
       <c r="C10" t="n">
-        <v>152820360</v>
+        <v>116699184</v>
       </c>
       <c r="D10" t="n">
-        <v>192459996.55</v>
+        <v>364673041.92</v>
       </c>
       <c r="E10" t="n">
-        <v>38902091.76</v>
+        <v>72846405</v>
       </c>
       <c r="F10" t="n">
         <v>1375011</v>
       </c>
       <c r="G10" t="n">
-        <v>1484070</v>
+        <v>4331880</v>
       </c>
       <c r="H10" t="n">
-        <v>1352818.5</v>
+        <v>27873000</v>
       </c>
       <c r="I10" t="n">
-        <v>1103990.4</v>
+        <v>506924.64</v>
       </c>
       <c r="J10" t="n">
-        <v>174999</v>
+        <v>72834</v>
       </c>
       <c r="K10" t="n">
-        <v>3669448</v>
+        <v>7265919.84</v>
       </c>
       <c r="L10" t="n">
-        <v>1494747.7</v>
+        <v>28547640</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2052000</v>
       </c>
     </row>
     <row r="11">
@@ -16627,37 +17877,40 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>50406048</v>
+        <v>50405850</v>
       </c>
       <c r="C11" t="n">
-        <v>88620840</v>
+        <v>67674096</v>
       </c>
       <c r="D11" t="n">
-        <v>115264068.87</v>
+        <v>218402262.14</v>
       </c>
       <c r="E11" t="n">
-        <v>27928024.08</v>
+        <v>52296831.9</v>
       </c>
       <c r="F11" t="n">
         <v>458337</v>
       </c>
       <c r="G11" t="n">
-        <v>1109445</v>
+        <v>3238380</v>
       </c>
       <c r="H11" t="n">
-        <v>1261524</v>
+        <v>25992000</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>174999</v>
+        <v>72834</v>
       </c>
       <c r="K11" t="n">
-        <v>2218736</v>
+        <v>4537266.86</v>
       </c>
       <c r="L11" t="n">
-        <v>1533952.8</v>
+        <v>29262600</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1098000</v>
       </c>
     </row>
     <row r="12">
@@ -16668,34 +17921,37 @@
         <v>34309638</v>
       </c>
       <c r="C12" t="n">
-        <v>48759480</v>
+        <v>37234512</v>
       </c>
       <c r="D12" t="n">
-        <v>65430283.52</v>
+        <v>123977246.98</v>
       </c>
       <c r="E12" t="n">
-        <v>16486089.98</v>
+        <v>30871152</v>
       </c>
       <c r="F12" t="n">
         <v>458337</v>
       </c>
       <c r="G12" t="n">
-        <v>880785</v>
+        <v>2570940</v>
       </c>
       <c r="H12" t="n">
-        <v>348579</v>
+        <v>7182000</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>174999</v>
+        <v>72834</v>
       </c>
       <c r="K12" t="n">
-        <v>1408044</v>
+        <v>2970753.19</v>
       </c>
       <c r="L12" t="n">
-        <v>915058.8</v>
+        <v>17447400</v>
+      </c>
+      <c r="M12" t="n">
+        <v>855000</v>
       </c>
     </row>
     <row r="13">
@@ -16706,34 +17962,37 @@
         <v>17379450</v>
       </c>
       <c r="C13" t="n">
-        <v>21178080</v>
+        <v>16172352</v>
       </c>
       <c r="D13" t="n">
-        <v>29108615.95</v>
+        <v>55154981.38</v>
       </c>
       <c r="E13" t="n">
-        <v>6405737.39</v>
+        <v>11995111.8</v>
       </c>
       <c r="F13" t="n">
         <v>125001</v>
       </c>
       <c r="G13" t="n">
-        <v>433455</v>
+        <v>1265220</v>
       </c>
       <c r="H13" t="n">
-        <v>232386</v>
+        <v>4788000</v>
       </c>
       <c r="I13" t="n">
-        <v>383330</v>
+        <v>184415.69</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>597352</v>
+        <v>1290909.82</v>
       </c>
       <c r="L13" t="n">
-        <v>404118</v>
+        <v>7722000</v>
+      </c>
+      <c r="M13" t="n">
+        <v>423000</v>
       </c>
     </row>
     <row r="14">
@@ -16744,22 +18003,22 @@
         <v>6799716</v>
       </c>
       <c r="C14" t="n">
-        <v>9702000</v>
+        <v>7408800</v>
       </c>
       <c r="D14" t="n">
-        <v>13651096.54</v>
+        <v>25866086.4</v>
       </c>
       <c r="E14" t="n">
-        <v>3681562.9</v>
+        <v>6893938.35</v>
       </c>
       <c r="F14" t="n">
         <v>166668</v>
       </c>
       <c r="G14" t="n">
-        <v>110445</v>
+        <v>322380</v>
       </c>
       <c r="H14" t="n">
-        <v>66396</v>
+        <v>1368000</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -16768,10 +18027,13 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>234674</v>
+        <v>519160.75</v>
       </c>
       <c r="L14" t="n">
-        <v>154582.2</v>
+        <v>2953800</v>
+      </c>
+      <c r="M14" t="n">
+        <v>90000</v>
       </c>
     </row>
     <row r="15">
@@ -16782,22 +18044,22 @@
         <v>3913074</v>
       </c>
       <c r="C15" t="n">
-        <v>3104640</v>
+        <v>2370816</v>
       </c>
       <c r="D15" t="n">
-        <v>4431269.53</v>
+        <v>8396365.82</v>
       </c>
       <c r="E15" t="n">
-        <v>692132.5699999999</v>
+        <v>1296058.05</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>74370</v>
+        <v>217080</v>
       </c>
       <c r="H15" t="n">
-        <v>24898.5</v>
+        <v>513000</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -16806,10 +18068,13 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>64002</v>
+        <v>143628.65</v>
       </c>
       <c r="L15" t="n">
-        <v>63867.6</v>
+        <v>1220400</v>
+      </c>
+      <c r="M15" t="n">
+        <v>45000</v>
       </c>
     </row>
     <row r="16">
@@ -16820,22 +18085,22 @@
         <v>2165724</v>
       </c>
       <c r="C16" t="n">
-        <v>665280</v>
+        <v>508032</v>
       </c>
       <c r="D16" t="n">
-        <v>963040.3199999999</v>
+        <v>1824768</v>
       </c>
       <c r="E16" t="n">
-        <v>206706.23</v>
+        <v>387069.3</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>21645</v>
+        <v>63180</v>
       </c>
       <c r="H16" t="n">
-        <v>24898.5</v>
+        <v>513000</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -16844,10 +18109,13 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>21334</v>
+        <v>48556</v>
       </c>
       <c r="L16" t="n">
-        <v>20347.2</v>
+        <v>388800</v>
+      </c>
+      <c r="M16" t="n">
+        <v>63000</v>
       </c>
     </row>
     <row r="17">
@@ -16858,10 +18126,10 @@
         <v>922680</v>
       </c>
       <c r="C17" t="n">
-        <v>415800</v>
+        <v>317520</v>
       </c>
       <c r="D17" t="n">
-        <v>601900.2</v>
+        <v>1140480</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -16870,10 +18138,10 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>4440</v>
+        <v>12960</v>
       </c>
       <c r="H17" t="n">
-        <v>16599</v>
+        <v>342000</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -16885,7 +18153,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>13564.8</v>
+        <v>259200</v>
+      </c>
+      <c r="M17" t="n">
+        <v>45000</v>
       </c>
     </row>
     <row r="18">
@@ -16896,10 +18167,10 @@
         <v>446490</v>
       </c>
       <c r="C18" t="n">
-        <v>83160</v>
+        <v>63504</v>
       </c>
       <c r="D18" t="n">
-        <v>120380.04</v>
+        <v>228096</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -16908,7 +18179,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>6105</v>
+        <v>17820</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -16923,7 +18194,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>14412.6</v>
+        <v>275400</v>
+      </c>
+      <c r="M18" t="n">
+        <v>36000</v>
       </c>
     </row>
     <row r="19">
@@ -16934,10 +18208,10 @@
         <v>188298</v>
       </c>
       <c r="C19" t="n">
-        <v>194040</v>
+        <v>148176</v>
       </c>
       <c r="D19" t="n">
-        <v>280886.76</v>
+        <v>532224</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -16946,10 +18220,10 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>69930</v>
+        <v>204120</v>
       </c>
       <c r="H19" t="n">
-        <v>16599</v>
+        <v>342000</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -16961,7 +18235,10 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>7347.6</v>
+        <v>140400</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -16972,10 +18249,10 @@
         <v>28908</v>
       </c>
       <c r="C20" t="n">
-        <v>138600</v>
+        <v>105840</v>
       </c>
       <c r="D20" t="n">
-        <v>200633.4</v>
+        <v>380160</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -16999,6 +18276,9 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -17039,6 +18319,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -17048,10 +18331,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>110880</v>
+        <v>84672</v>
       </c>
       <c r="D22" t="n">
-        <v>160506.72</v>
+        <v>304128</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -17075,6 +18358,9 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -17086,10 +18372,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>27720</v>
+        <v>21168</v>
       </c>
       <c r="D23" t="n">
-        <v>40126.68</v>
+        <v>76032</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -17113,6 +18399,9 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -17124,10 +18413,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>304920</v>
+        <v>232848</v>
       </c>
       <c r="D24" t="n">
-        <v>441393.48</v>
+        <v>836352</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -17151,6 +18440,9 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -17202,6 +18494,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -17216,7 +18512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17287,13 +18583,18 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>13022.37</v>
+        <v>12931.02</v>
       </c>
       <c r="C4" t="n">
         <v>3113712</v>
@@ -17308,7 +18609,7 @@
         <v>26</v>
       </c>
       <c r="G4" t="n">
-        <v>55650</v>
+        <v>53250</v>
       </c>
       <c r="H4" t="n">
         <v>8580</v>
@@ -17320,10 +18621,13 @@
         <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="L4" t="n">
-        <v>157980</v>
+        <v>155010</v>
+      </c>
+      <c r="M4" t="n">
+        <v>32760</v>
       </c>
     </row>
     <row r="5">
@@ -17331,7 +18635,7 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>20761.47</v>
+        <v>20698.47</v>
       </c>
       <c r="C5" t="n">
         <v>3471048</v>
@@ -17346,7 +18650,7 @@
         <v>15</v>
       </c>
       <c r="G5" t="n">
-        <v>68100</v>
+        <v>67170</v>
       </c>
       <c r="H5" t="n">
         <v>11520</v>
@@ -17358,10 +18662,13 @@
         <v>4</v>
       </c>
       <c r="K5" t="n">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="L5" t="n">
-        <v>189270</v>
+        <v>187860</v>
+      </c>
+      <c r="M5" t="n">
+        <v>13290</v>
       </c>
     </row>
     <row r="6">
@@ -17369,7 +18676,7 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>25763.04</v>
+        <v>25747.11</v>
       </c>
       <c r="C6" t="n">
         <v>3910536</v>
@@ -17384,10 +18691,10 @@
         <v>18</v>
       </c>
       <c r="G6" t="n">
-        <v>70800</v>
+        <v>70230</v>
       </c>
       <c r="H6" t="n">
-        <v>16650</v>
+        <v>16680</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -17396,10 +18703,13 @@
         <v>5</v>
       </c>
       <c r="K6" t="n">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="L6" t="n">
-        <v>198630</v>
+        <v>198090</v>
+      </c>
+      <c r="M6" t="n">
+        <v>6150</v>
       </c>
     </row>
     <row r="7">
@@ -17407,7 +18717,7 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>25677.36</v>
+        <v>25675.74</v>
       </c>
       <c r="C7" t="n">
         <v>3961944</v>
@@ -17422,7 +18732,7 @@
         <v>18</v>
       </c>
       <c r="G7" t="n">
-        <v>87630</v>
+        <v>87390</v>
       </c>
       <c r="H7" t="n">
         <v>18450</v>
@@ -17437,7 +18747,10 @@
         <v>200</v>
       </c>
       <c r="L7" t="n">
-        <v>247980</v>
+        <v>247020</v>
+      </c>
+      <c r="M7" t="n">
+        <v>5280</v>
       </c>
     </row>
     <row r="8">
@@ -17445,7 +18758,7 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>27913.5</v>
+        <v>27913.23</v>
       </c>
       <c r="C8" t="n">
         <v>4080384</v>
@@ -17460,7 +18773,7 @@
         <v>9</v>
       </c>
       <c r="G8" t="n">
-        <v>98250</v>
+        <v>97770</v>
       </c>
       <c r="H8" t="n">
         <v>3180</v>
@@ -17475,7 +18788,10 @@
         <v>210</v>
       </c>
       <c r="L8" t="n">
-        <v>237390</v>
+        <v>236730</v>
+      </c>
+      <c r="M8" t="n">
+        <v>4320</v>
       </c>
     </row>
     <row r="9">
@@ -17498,7 +18814,7 @@
         <v>14</v>
       </c>
       <c r="G9" t="n">
-        <v>91110</v>
+        <v>90810</v>
       </c>
       <c r="H9" t="n">
         <v>450</v>
@@ -17513,7 +18829,10 @@
         <v>194</v>
       </c>
       <c r="L9" t="n">
-        <v>193950</v>
+        <v>193650</v>
+      </c>
+      <c r="M9" t="n">
+        <v>4950</v>
       </c>
     </row>
     <row r="10">
@@ -17553,6 +18872,9 @@
       <c r="L10" t="n">
         <v>104940</v>
       </c>
+      <c r="M10" t="n">
+        <v>3600</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -17589,7 +18911,10 @@
         <v>66</v>
       </c>
       <c r="L11" t="n">
-        <v>63540</v>
+        <v>63240</v>
+      </c>
+      <c r="M11" t="n">
+        <v>2310</v>
       </c>
     </row>
     <row r="12">
@@ -17612,7 +18937,7 @@
         <v>2</v>
       </c>
       <c r="G12" t="n">
-        <v>18960</v>
+        <v>18990</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -17624,10 +18949,13 @@
         <v>3</v>
       </c>
       <c r="K12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L12" t="n">
-        <v>29010</v>
+        <v>28890</v>
+      </c>
+      <c r="M12" t="n">
+        <v>2220</v>
       </c>
     </row>
     <row r="13">
@@ -17667,6 +18995,9 @@
       <c r="L13" t="n">
         <v>10080</v>
       </c>
+      <c r="M13" t="n">
+        <v>1020</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -17705,6 +19036,9 @@
       <c r="L14" t="n">
         <v>2610</v>
       </c>
+      <c r="M14" t="n">
+        <v>120</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -17743,6 +19077,9 @@
       <c r="L15" t="n">
         <v>990</v>
       </c>
+      <c r="M15" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -17781,6 +19118,9 @@
       <c r="L16" t="n">
         <v>240</v>
       </c>
+      <c r="M16" t="n">
+        <v>90</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -17819,6 +19159,9 @@
       <c r="L17" t="n">
         <v>210</v>
       </c>
+      <c r="M17" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -17857,6 +19200,9 @@
       <c r="L18" t="n">
         <v>120</v>
       </c>
+      <c r="M18" t="n">
+        <v>120</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -17895,6 +19241,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -17933,6 +19282,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -17971,6 +19323,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -18009,6 +19364,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -18047,6 +19405,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -18085,6 +19446,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -18134,6 +19498,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -18148,7 +19516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18219,6 +19587,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -18255,6 +19628,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -18263,7 +19639,7 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>9342.66</v>
+        <v>9314.309999999999</v>
       </c>
       <c r="C5" t="n">
         <v>1909076.4</v>
@@ -18290,10 +19666,13 @@
         <v>1.2</v>
       </c>
       <c r="K5" t="n">
-        <v>68.88</v>
+        <v>50.97</v>
       </c>
       <c r="L5" t="n">
-        <v>39746.7</v>
+        <v>39450.6</v>
+      </c>
+      <c r="M5" t="n">
+        <v>265.8</v>
       </c>
     </row>
     <row r="6">
@@ -18301,7 +19680,7 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>20610.43</v>
+        <v>20597.69</v>
       </c>
       <c r="C6" t="n">
         <v>3519482.4</v>
@@ -18316,10 +19695,10 @@
         <v>1.8</v>
       </c>
       <c r="G6" t="n">
-        <v>3540</v>
+        <v>3511.5</v>
       </c>
       <c r="H6" t="n">
-        <v>9490.5</v>
+        <v>9507.6</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -18328,10 +19707,13 @@
         <v>2.5</v>
       </c>
       <c r="K6" t="n">
-        <v>104.65</v>
+        <v>81.12</v>
       </c>
       <c r="L6" t="n">
-        <v>73493.10000000001</v>
+        <v>73293.3</v>
+      </c>
+      <c r="M6" t="n">
+        <v>492</v>
       </c>
     </row>
     <row r="7">
@@ -18339,7 +19721,7 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>24393.49</v>
+        <v>24391.95</v>
       </c>
       <c r="C7" t="n">
         <v>3961944</v>
@@ -18354,22 +19736,25 @@
         <v>10.8</v>
       </c>
       <c r="G7" t="n">
-        <v>13144.5</v>
+        <v>13108.5</v>
       </c>
       <c r="H7" t="n">
         <v>13468.5</v>
       </c>
       <c r="I7" t="n">
-        <v>0.55</v>
+        <v>0.64</v>
       </c>
       <c r="J7" t="n">
         <v>6.3</v>
       </c>
       <c r="K7" t="n">
-        <v>164</v>
+        <v>127.6</v>
       </c>
       <c r="L7" t="n">
-        <v>148788</v>
+        <v>148212</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1848</v>
       </c>
     </row>
     <row r="8">
@@ -18377,7 +19762,7 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>27913.5</v>
+        <v>27913.23</v>
       </c>
       <c r="C8" t="n">
         <v>4080384</v>
@@ -18392,7 +19777,7 @@
         <v>8.550000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>63862.5</v>
+        <v>63550.5</v>
       </c>
       <c r="H8" t="n">
         <v>2703</v>
@@ -18404,10 +19789,13 @@
         <v>2.55</v>
       </c>
       <c r="K8" t="n">
-        <v>189</v>
+        <v>154.56</v>
       </c>
       <c r="L8" t="n">
-        <v>168546.9</v>
+        <v>168078.3</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2592</v>
       </c>
     </row>
     <row r="9">
@@ -18430,7 +19818,7 @@
         <v>14</v>
       </c>
       <c r="G9" t="n">
-        <v>77443.5</v>
+        <v>77188.5</v>
       </c>
       <c r="H9" t="n">
         <v>450</v>
@@ -18442,10 +19830,13 @@
         <v>2.85</v>
       </c>
       <c r="K9" t="n">
-        <v>194</v>
+        <v>155.78</v>
       </c>
       <c r="L9" t="n">
-        <v>157099.5</v>
+        <v>156856.5</v>
+      </c>
+      <c r="M9" t="n">
+        <v>4950</v>
       </c>
     </row>
     <row r="10">
@@ -18480,10 +19871,13 @@
         <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>133</v>
+        <v>115.71</v>
       </c>
       <c r="L10" t="n">
         <v>93396.60000000001</v>
+      </c>
+      <c r="M10" t="n">
+        <v>3600</v>
       </c>
     </row>
     <row r="11">
@@ -18518,10 +19912,13 @@
         <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>66</v>
+        <v>59.3</v>
       </c>
       <c r="L11" t="n">
-        <v>63540</v>
+        <v>63240</v>
+      </c>
+      <c r="M11" t="n">
+        <v>2310</v>
       </c>
     </row>
     <row r="12">
@@ -18544,7 +19941,7 @@
         <v>2</v>
       </c>
       <c r="G12" t="n">
-        <v>18960</v>
+        <v>18990</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -18556,10 +19953,13 @@
         <v>3</v>
       </c>
       <c r="K12" t="n">
-        <v>30</v>
+        <v>28.74</v>
       </c>
       <c r="L12" t="n">
-        <v>29010</v>
+        <v>28890</v>
+      </c>
+      <c r="M12" t="n">
+        <v>2220</v>
       </c>
     </row>
     <row r="13">
@@ -18594,10 +19994,13 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>11</v>
+        <v>10.44</v>
       </c>
       <c r="L13" t="n">
         <v>10080</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1020</v>
       </c>
     </row>
     <row r="14">
@@ -18632,10 +20035,13 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L14" t="n">
         <v>2610</v>
+      </c>
+      <c r="M14" t="n">
+        <v>120</v>
       </c>
     </row>
     <row r="15">
@@ -18675,6 +20081,9 @@
       <c r="L15" t="n">
         <v>990</v>
       </c>
+      <c r="M15" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -18713,6 +20122,9 @@
       <c r="L16" t="n">
         <v>240</v>
       </c>
+      <c r="M16" t="n">
+        <v>90</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -18751,6 +20163,9 @@
       <c r="L17" t="n">
         <v>210</v>
       </c>
+      <c r="M17" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -18789,6 +20204,9 @@
       <c r="L18" t="n">
         <v>120</v>
       </c>
+      <c r="M18" t="n">
+        <v>120</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -18827,6 +20245,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -18865,6 +20286,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -18903,6 +20327,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -18941,6 +20368,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -18979,6 +20409,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -19017,6 +20450,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -19066,6 +20502,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -19080,7 +20520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19151,6 +20591,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -19187,6 +20632,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -19195,16 +20643,16 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>20553855.3</v>
+        <v>20491485.3</v>
       </c>
       <c r="C5" t="n">
-        <v>104999202</v>
+        <v>80181208.8</v>
       </c>
       <c r="D5" t="n">
-        <v>91472659.34999999</v>
+        <v>173322319.1</v>
       </c>
       <c r="E5" t="n">
-        <v>38481118.1</v>
+        <v>72058107.59999999</v>
       </c>
       <c r="F5" t="n">
         <v>12500.1</v>
@@ -19213,19 +20661,22 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1147322.88</v>
+        <v>23639040</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>69999.60000000001</v>
+        <v>29133.6</v>
       </c>
       <c r="K5" t="n">
-        <v>1469485.92</v>
+        <v>2475093.54</v>
       </c>
       <c r="L5" t="n">
-        <v>374413.91</v>
+        <v>7101108</v>
+      </c>
+      <c r="M5" t="n">
+        <v>79740</v>
       </c>
     </row>
     <row r="6">
@@ -19233,37 +20684,40 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>45342950.4</v>
+        <v>45314913.6</v>
       </c>
       <c r="C6" t="n">
-        <v>193571532</v>
+        <v>147818260.8</v>
       </c>
       <c r="D6" t="n">
-        <v>157850855.43</v>
+        <v>299095670.02</v>
       </c>
       <c r="E6" t="n">
-        <v>54420479.57</v>
+        <v>101905479</v>
       </c>
       <c r="F6" t="n">
         <v>75000.60000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>65490</v>
+        <v>189621</v>
       </c>
       <c r="H6" t="n">
-        <v>2625546.82</v>
+        <v>54193320</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>145832.5</v>
+        <v>60695</v>
       </c>
       <c r="K6" t="n">
-        <v>2232603.1</v>
+        <v>3938862.72</v>
       </c>
       <c r="L6" t="n">
-        <v>692305</v>
+        <v>13192794</v>
+      </c>
+      <c r="M6" t="n">
+        <v>147600</v>
       </c>
     </row>
     <row r="7">
@@ -19271,37 +20725,40 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>53665682.4</v>
+        <v>53662296.6</v>
       </c>
       <c r="C7" t="n">
-        <v>217906920</v>
+        <v>166401648</v>
       </c>
       <c r="D7" t="n">
-        <v>201248060.48</v>
+        <v>381324658.18</v>
       </c>
       <c r="E7" t="n">
-        <v>56571577.37</v>
+        <v>105933533.4</v>
       </c>
       <c r="F7" t="n">
         <v>450003.6</v>
       </c>
       <c r="G7" t="n">
-        <v>243173.25</v>
+        <v>707859</v>
       </c>
       <c r="H7" t="n">
-        <v>3726060.52</v>
+        <v>76770450</v>
       </c>
       <c r="I7" t="n">
-        <v>210831.5</v>
+        <v>123914.91</v>
       </c>
       <c r="J7" t="n">
-        <v>367497.9</v>
+        <v>152951.4</v>
       </c>
       <c r="K7" t="n">
-        <v>3498776</v>
+        <v>6195745.6</v>
       </c>
       <c r="L7" t="n">
-        <v>1401582.96</v>
+        <v>26678160</v>
+      </c>
+      <c r="M7" t="n">
+        <v>554400</v>
       </c>
     </row>
     <row r="8">
@@ -19309,37 +20766,40 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>61409700</v>
+        <v>61409106</v>
       </c>
       <c r="C8" t="n">
-        <v>224421120</v>
+        <v>171376128</v>
       </c>
       <c r="D8" t="n">
-        <v>239101082.54</v>
+        <v>453048532.99</v>
       </c>
       <c r="E8" t="n">
-        <v>56415760.08</v>
+        <v>105641756.55</v>
       </c>
       <c r="F8" t="n">
         <v>356252.85</v>
       </c>
       <c r="G8" t="n">
-        <v>1181456.25</v>
+        <v>3431727</v>
       </c>
       <c r="H8" t="n">
-        <v>747784.95</v>
+        <v>15407100</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>148749.15</v>
+        <v>61908.9</v>
       </c>
       <c r="K8" t="n">
-        <v>4032126</v>
+        <v>7504815.36</v>
       </c>
       <c r="L8" t="n">
-        <v>1587711.8</v>
+        <v>30254094</v>
+      </c>
+      <c r="M8" t="n">
+        <v>777600</v>
       </c>
     </row>
     <row r="9">
@@ -19350,34 +20810,37 @@
         <v>63409896</v>
       </c>
       <c r="C9" t="n">
-        <v>200970000</v>
+        <v>153468000</v>
       </c>
       <c r="D9" t="n">
-        <v>233607499.29</v>
+        <v>442639296</v>
       </c>
       <c r="E9" t="n">
-        <v>45187944.18</v>
+        <v>84617025.3</v>
       </c>
       <c r="F9" t="n">
         <v>583338</v>
       </c>
       <c r="G9" t="n">
-        <v>1432704.75</v>
+        <v>4168179</v>
       </c>
       <c r="H9" t="n">
-        <v>124492.5</v>
+        <v>2565000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>166249.05</v>
+        <v>69192.3</v>
       </c>
       <c r="K9" t="n">
-        <v>4138796</v>
+        <v>7564150.79</v>
       </c>
       <c r="L9" t="n">
-        <v>1479877.29</v>
+        <v>28234170</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1485000</v>
       </c>
     </row>
     <row r="10">
@@ -19388,34 +20851,37 @@
         <v>50569596</v>
       </c>
       <c r="C10" t="n">
-        <v>108163440</v>
+        <v>82597536</v>
       </c>
       <c r="D10" t="n">
-        <v>136219645.66</v>
+        <v>258108871.68</v>
       </c>
       <c r="E10" t="n">
-        <v>27168951.6</v>
+        <v>50875425</v>
       </c>
       <c r="F10" t="n">
         <v>1000008</v>
       </c>
       <c r="G10" t="n">
-        <v>1034520</v>
+        <v>3019680</v>
       </c>
       <c r="H10" t="n">
-        <v>82995</v>
+        <v>1710000</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>116666</v>
+        <v>48556</v>
       </c>
       <c r="K10" t="n">
-        <v>2837422</v>
+        <v>5618414.76</v>
       </c>
       <c r="L10" t="n">
-        <v>879795.97</v>
+        <v>16811388</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1080000</v>
       </c>
     </row>
     <row r="11">
@@ -19426,34 +20892,37 @@
         <v>33279246</v>
       </c>
       <c r="C11" t="n">
-        <v>51780960</v>
+        <v>39541824</v>
       </c>
       <c r="D11" t="n">
-        <v>67348539.45999999</v>
+        <v>127611956.74</v>
       </c>
       <c r="E11" t="n">
-        <v>17259654.79</v>
+        <v>32319696.6</v>
       </c>
       <c r="F11" t="n">
         <v>83334</v>
       </c>
       <c r="G11" t="n">
-        <v>480630</v>
+        <v>1402920</v>
       </c>
       <c r="H11" t="n">
-        <v>8299.5</v>
+        <v>171000</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>116666</v>
+        <v>48556</v>
       </c>
       <c r="K11" t="n">
-        <v>1408044</v>
+        <v>2879419.36</v>
       </c>
       <c r="L11" t="n">
-        <v>598546.8</v>
+        <v>11383200</v>
+      </c>
+      <c r="M11" t="n">
+        <v>693000</v>
       </c>
     </row>
     <row r="12">
@@ -19464,19 +20933,19 @@
         <v>19177092</v>
       </c>
       <c r="C12" t="n">
-        <v>22259160</v>
+        <v>16997904</v>
       </c>
       <c r="D12" t="n">
-        <v>29869538.19</v>
+        <v>56596776.19</v>
       </c>
       <c r="E12" t="n">
-        <v>4834862.93</v>
+        <v>9053559</v>
       </c>
       <c r="F12" t="n">
         <v>83334</v>
       </c>
       <c r="G12" t="n">
-        <v>350760</v>
+        <v>1025460</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -19485,13 +20954,16 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>174999</v>
+        <v>72834</v>
       </c>
       <c r="K12" t="n">
-        <v>640020</v>
+        <v>1395353.77</v>
       </c>
       <c r="L12" t="n">
-        <v>273274.2</v>
+        <v>5200200</v>
+      </c>
+      <c r="M12" t="n">
+        <v>666000</v>
       </c>
     </row>
     <row r="13">
@@ -19502,19 +20974,19 @@
         <v>8936730</v>
       </c>
       <c r="C13" t="n">
-        <v>6153840</v>
+        <v>4699296</v>
       </c>
       <c r="D13" t="n">
-        <v>8458262.75</v>
+        <v>16026709.25</v>
       </c>
       <c r="E13" t="n">
-        <v>1052997.93</v>
+        <v>1971799.2</v>
       </c>
       <c r="F13" t="n">
         <v>41667</v>
       </c>
       <c r="G13" t="n">
-        <v>173715</v>
+        <v>507060</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -19526,10 +20998,13 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>234674</v>
+        <v>507143.14</v>
       </c>
       <c r="L13" t="n">
-        <v>94953.60000000001</v>
+        <v>1814400</v>
+      </c>
+      <c r="M13" t="n">
+        <v>306000</v>
       </c>
     </row>
     <row r="14">
@@ -19540,19 +21015,19 @@
         <v>2917728</v>
       </c>
       <c r="C14" t="n">
-        <v>1635480</v>
+        <v>1248912</v>
       </c>
       <c r="D14" t="n">
-        <v>2301184.84</v>
+        <v>4360283.14</v>
       </c>
       <c r="E14" t="n">
-        <v>188798.1</v>
+        <v>353535.3</v>
       </c>
       <c r="F14" t="n">
         <v>83334</v>
       </c>
       <c r="G14" t="n">
-        <v>23310</v>
+        <v>68040</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -19564,10 +21039,13 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>21334</v>
+        <v>47196.43</v>
       </c>
       <c r="L14" t="n">
-        <v>24586.2</v>
+        <v>469800</v>
+      </c>
+      <c r="M14" t="n">
+        <v>36000</v>
       </c>
     </row>
     <row r="15">
@@ -19578,19 +21056,19 @@
         <v>1153152</v>
       </c>
       <c r="C15" t="n">
-        <v>443520</v>
+        <v>338688</v>
       </c>
       <c r="D15" t="n">
-        <v>633038.5</v>
+        <v>1199480.83</v>
       </c>
       <c r="E15" t="n">
-        <v>98876.08</v>
+        <v>185151.15</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>14430</v>
+        <v>42120</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -19605,7 +21083,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>9325.799999999999</v>
+        <v>178200</v>
+      </c>
+      <c r="M15" t="n">
+        <v>18000</v>
       </c>
     </row>
     <row r="16">
@@ -19616,19 +21097,19 @@
         <v>429462</v>
       </c>
       <c r="C16" t="n">
-        <v>83160</v>
+        <v>63504</v>
       </c>
       <c r="D16" t="n">
-        <v>120380.04</v>
+        <v>228096</v>
       </c>
       <c r="E16" t="n">
-        <v>103353.11</v>
+        <v>193534.65</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>10545</v>
+        <v>30780</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -19640,10 +21121,13 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>21334</v>
+        <v>48556</v>
       </c>
       <c r="L16" t="n">
-        <v>2260.8</v>
+        <v>43200</v>
+      </c>
+      <c r="M16" t="n">
+        <v>27000</v>
       </c>
     </row>
     <row r="17">
@@ -19654,10 +21138,10 @@
         <v>256410</v>
       </c>
       <c r="C17" t="n">
-        <v>83160</v>
+        <v>63504</v>
       </c>
       <c r="D17" t="n">
-        <v>120380.04</v>
+        <v>228096</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -19681,7 +21165,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>1978.2</v>
+        <v>37800</v>
+      </c>
+      <c r="M17" t="n">
+        <v>9000</v>
       </c>
     </row>
     <row r="18">
@@ -19692,10 +21179,10 @@
         <v>217206</v>
       </c>
       <c r="C18" t="n">
-        <v>27720</v>
+        <v>21168</v>
       </c>
       <c r="D18" t="n">
-        <v>40126.68</v>
+        <v>76032</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -19704,7 +21191,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>2220</v>
+        <v>6480</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -19719,7 +21206,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>1130.4</v>
+        <v>21600</v>
+      </c>
+      <c r="M18" t="n">
+        <v>36000</v>
       </c>
     </row>
     <row r="19">
@@ -19742,7 +21232,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>555</v>
+        <v>1620</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -19757,6 +21247,9 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -19768,10 +21261,10 @@
         <v>16632</v>
       </c>
       <c r="C20" t="n">
-        <v>27720</v>
+        <v>21168</v>
       </c>
       <c r="D20" t="n">
-        <v>40126.68</v>
+        <v>76032</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -19795,6 +21288,9 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -19835,6 +21331,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -19844,10 +21343,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>55440</v>
+        <v>42336</v>
       </c>
       <c r="D22" t="n">
-        <v>80253.36</v>
+        <v>152064</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -19871,6 +21370,9 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -19911,6 +21413,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -19920,10 +21425,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>138600</v>
+        <v>105840</v>
       </c>
       <c r="D24" t="n">
-        <v>200633.4</v>
+        <v>380160</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -19947,6 +21452,9 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -19998,6 +21506,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -20012,7 +21524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20083,6 +21595,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -20104,10 +21621,10 @@
         <v>19</v>
       </c>
       <c r="G4" t="n">
-        <v>140850</v>
+        <v>141120</v>
       </c>
       <c r="H4" t="n">
-        <v>24660</v>
+        <v>24750</v>
       </c>
       <c r="I4" t="n">
         <v>2</v>
@@ -20116,10 +21633,13 @@
         <v>12</v>
       </c>
       <c r="K4" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L4" t="n">
-        <v>402510</v>
+        <v>401340</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -20142,10 +21662,10 @@
         <v>15</v>
       </c>
       <c r="G5" t="n">
-        <v>87510</v>
+        <v>87660</v>
       </c>
       <c r="H5" t="n">
-        <v>18840</v>
+        <v>18870</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -20157,7 +21677,10 @@
         <v>153</v>
       </c>
       <c r="L5" t="n">
-        <v>216060</v>
+        <v>216030</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -20180,10 +21703,10 @@
         <v>5</v>
       </c>
       <c r="G6" t="n">
-        <v>53490</v>
+        <v>53730</v>
       </c>
       <c r="H6" t="n">
-        <v>21060</v>
+        <v>21000</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -20195,7 +21718,10 @@
         <v>93</v>
       </c>
       <c r="L6" t="n">
-        <v>115050</v>
+        <v>115230</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -20221,7 +21747,7 @@
         <v>19260</v>
       </c>
       <c r="H7" t="n">
-        <v>3060</v>
+        <v>3150</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -20233,7 +21759,10 @@
         <v>34</v>
       </c>
       <c r="L7" t="n">
-        <v>46320</v>
+        <v>46380</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -20273,6 +21802,9 @@
       <c r="L8" t="n">
         <v>7020</v>
       </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -20294,7 +21826,7 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="H9" t="n">
         <v>90</v>
@@ -20309,7 +21841,10 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1800</v>
+        <v>1770</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -20349,6 +21884,9 @@
       <c r="L10" t="n">
         <v>420</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -20387,6 +21925,9 @@
       <c r="L11" t="n">
         <v>150</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -20425,6 +21966,9 @@
       <c r="L12" t="n">
         <v>30</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -20463,6 +22007,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -20501,6 +22048,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -20539,6 +22089,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -20577,6 +22130,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -20615,6 +22171,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -20653,6 +22212,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -20691,6 +22253,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -20729,6 +22294,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -20767,6 +22335,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -20805,6 +22376,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -20843,6 +22417,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -20881,6 +22458,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -20930,6 +22510,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -20944,7 +22528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21015,6 +22599,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -21051,6 +22640,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -21077,7 +22669,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>6782.4</v>
+        <v>6793.2</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -21086,10 +22678,13 @@
         <v>2.1</v>
       </c>
       <c r="K5" t="n">
-        <v>64.26000000000001</v>
+        <v>50.64</v>
       </c>
       <c r="L5" t="n">
-        <v>45372.6</v>
+        <v>45366.3</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -21112,10 +22707,10 @@
         <v>0.5</v>
       </c>
       <c r="G6" t="n">
-        <v>2674.5</v>
+        <v>2686.5</v>
       </c>
       <c r="H6" t="n">
-        <v>12004.2</v>
+        <v>11970</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -21124,10 +22719,13 @@
         <v>1.5</v>
       </c>
       <c r="K6" t="n">
-        <v>60.45</v>
+        <v>47.15</v>
       </c>
       <c r="L6" t="n">
-        <v>42568.5</v>
+        <v>42635.1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -21153,7 +22751,7 @@
         <v>2889</v>
       </c>
       <c r="H7" t="n">
-        <v>2233.8</v>
+        <v>2299.5</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -21162,10 +22760,13 @@
         <v>0.7</v>
       </c>
       <c r="K7" t="n">
-        <v>27.88</v>
+        <v>21.69</v>
       </c>
       <c r="L7" t="n">
-        <v>27792</v>
+        <v>27828</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -21200,10 +22801,13 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>2.7</v>
+        <v>2.21</v>
       </c>
       <c r="L8" t="n">
         <v>4984.2</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -21226,7 +22830,7 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>102</v>
+        <v>127.5</v>
       </c>
       <c r="H9" t="n">
         <v>90</v>
@@ -21241,7 +22845,10 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1458</v>
+        <v>1433.7</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -21281,6 +22888,9 @@
       <c r="L10" t="n">
         <v>373.8</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -21319,6 +22929,9 @@
       <c r="L11" t="n">
         <v>150</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -21357,6 +22970,9 @@
       <c r="L12" t="n">
         <v>30</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -21395,6 +23011,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -21433,6 +23052,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -21471,6 +23093,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -21509,6 +23134,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -21547,6 +23175,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -21585,6 +23216,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -21623,6 +23257,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -21661,6 +23298,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -21699,6 +23339,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -21737,6 +23380,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -21775,6 +23421,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -21813,6 +23462,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -21862,6 +23514,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -21876,7 +23532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21947,6 +23603,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -21983,6 +23644,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -21994,13 +23658,13 @@
         <v>31184198.1</v>
       </c>
       <c r="C5" t="n">
-        <v>95943078</v>
+        <v>73265623.2</v>
       </c>
       <c r="D5" t="n">
-        <v>83583192.29000001</v>
+        <v>158373363.46</v>
       </c>
       <c r="E5" t="n">
-        <v>6895143.31</v>
+        <v>12911552.55</v>
       </c>
       <c r="F5" t="n">
         <v>12500.1</v>
@@ -22009,19 +23673,22 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1876350.96</v>
+        <v>38721240</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>122499.3</v>
+        <v>50983.8</v>
       </c>
       <c r="K5" t="n">
-        <v>1370922.84</v>
+        <v>2459021.51</v>
       </c>
       <c r="L5" t="n">
-        <v>427409.89</v>
+        <v>8165934</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -22032,34 +23699,37 @@
         <v>20010038.4</v>
       </c>
       <c r="C6" t="n">
-        <v>74369988</v>
+        <v>56791627.2</v>
       </c>
       <c r="D6" t="n">
-        <v>60646139.97</v>
+        <v>114912255.74</v>
       </c>
       <c r="E6" t="n">
-        <v>4287504.31</v>
+        <v>8028598.5</v>
       </c>
       <c r="F6" t="n">
         <v>20833.5</v>
       </c>
       <c r="G6" t="n">
-        <v>49478.25</v>
+        <v>145071</v>
       </c>
       <c r="H6" t="n">
-        <v>3320961.93</v>
+        <v>68229000</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>87499.5</v>
+        <v>36417</v>
       </c>
       <c r="K6" t="n">
-        <v>1289640.3</v>
+        <v>2289463.96</v>
       </c>
       <c r="L6" t="n">
-        <v>400995.27</v>
+        <v>7674318</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -22070,34 +23740,37 @@
         <v>11984227.2</v>
       </c>
       <c r="C7" t="n">
-        <v>31406760</v>
+        <v>23983344</v>
       </c>
       <c r="D7" t="n">
-        <v>29005731.14</v>
+        <v>54960035.33</v>
       </c>
       <c r="E7" t="n">
-        <v>1763453.16</v>
+        <v>3302167.5</v>
       </c>
       <c r="F7" t="n">
         <v>25000.2</v>
       </c>
       <c r="G7" t="n">
-        <v>53446.5</v>
+        <v>156006</v>
       </c>
       <c r="H7" t="n">
-        <v>617980.77</v>
+        <v>13107150</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>40833.1</v>
+        <v>16994.6</v>
       </c>
       <c r="K7" t="n">
-        <v>594791.92</v>
+        <v>1053276.75</v>
       </c>
       <c r="L7" t="n">
-        <v>261800.64</v>
+        <v>5009040</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -22108,22 +23781,22 @@
         <v>707850</v>
       </c>
       <c r="C8" t="n">
-        <v>3548160</v>
+        <v>2709504</v>
       </c>
       <c r="D8" t="n">
-        <v>3780254.27</v>
+        <v>7162822.66</v>
       </c>
       <c r="E8" t="n">
-        <v>325397.32</v>
+        <v>609325.2</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>8297.25</v>
+        <v>24219</v>
       </c>
       <c r="H8" t="n">
-        <v>119927.78</v>
+        <v>2470950</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -22132,10 +23805,13 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>57601.8</v>
+        <v>107211.65</v>
       </c>
       <c r="L8" t="n">
-        <v>46951.16</v>
+        <v>897156</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -22146,10 +23822,10 @@
         <v>111078</v>
       </c>
       <c r="C9" t="n">
-        <v>498960</v>
+        <v>381024</v>
       </c>
       <c r="D9" t="n">
-        <v>579991.03</v>
+        <v>1098966.53</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -22158,10 +23834,10 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>1887</v>
+        <v>6885</v>
       </c>
       <c r="H9" t="n">
-        <v>24898.5</v>
+        <v>513000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -22173,7 +23849,10 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>13734.36</v>
+        <v>258066</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -22184,10 +23863,10 @@
         <v>53460</v>
       </c>
       <c r="C10" t="n">
-        <v>83160</v>
+        <v>63504</v>
       </c>
       <c r="D10" t="n">
-        <v>104730.63</v>
+        <v>198443.52</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -22199,7 +23878,7 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>16599</v>
+        <v>342000</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -22211,7 +23890,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>3521.2</v>
+        <v>67284</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -22249,7 +23931,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>1413</v>
+        <v>27000</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -22275,7 +23960,7 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>8299.5</v>
+        <v>171000</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -22287,7 +23972,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>282.6</v>
+        <v>5400</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -22327,6 +24015,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -22365,6 +24056,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -22403,6 +24097,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -22441,6 +24138,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -22479,6 +24179,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -22517,6 +24220,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -22555,6 +24261,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -22593,6 +24302,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -22631,6 +24343,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -22669,6 +24384,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -22707,6 +24425,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -22745,6 +24466,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -22794,6 +24518,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>

--- a/risk/Risk_Analysis_T3_50yrs_Present_Perfect.xlsx
+++ b/risk/Risk_Analysis_T3_50yrs_Present_Perfect.xlsx
@@ -549,7 +549,7 @@
         <v>40</v>
       </c>
       <c r="K4" t="n">
-        <v>1013</v>
+        <v>392</v>
       </c>
       <c r="L4" t="n">
         <v>1350570</v>
@@ -590,7 +590,7 @@
         <v>26</v>
       </c>
       <c r="K5" t="n">
-        <v>567</v>
+        <v>232</v>
       </c>
       <c r="L5" t="n">
         <v>853350</v>
@@ -631,7 +631,7 @@
         <v>10</v>
       </c>
       <c r="K6" t="n">
-        <v>508</v>
+        <v>173</v>
       </c>
       <c r="L6" t="n">
         <v>634980</v>
@@ -672,7 +672,7 @@
         <v>14</v>
       </c>
       <c r="K7" t="n">
-        <v>394</v>
+        <v>110</v>
       </c>
       <c r="L7" t="n">
         <v>503700</v>
@@ -713,7 +713,7 @@
         <v>5</v>
       </c>
       <c r="K8" t="n">
-        <v>333</v>
+        <v>104</v>
       </c>
       <c r="L8" t="n">
         <v>397650</v>
@@ -754,7 +754,7 @@
         <v>9</v>
       </c>
       <c r="K9" t="n">
-        <v>267</v>
+        <v>65</v>
       </c>
       <c r="L9" t="n">
         <v>291210</v>
@@ -795,7 +795,7 @@
         <v>3</v>
       </c>
       <c r="K10" t="n">
-        <v>172</v>
+        <v>39</v>
       </c>
       <c r="L10" t="n">
         <v>178200</v>
@@ -836,7 +836,7 @@
         <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>104</v>
+        <v>15</v>
       </c>
       <c r="L11" t="n">
         <v>162570</v>
@@ -877,7 +877,7 @@
         <v>3</v>
       </c>
       <c r="K12" t="n">
-        <v>66</v>
+        <v>7</v>
       </c>
       <c r="L12" t="n">
         <v>96930</v>
@@ -918,7 +918,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>42900</v>
@@ -959,7 +959,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>16410</v>
@@ -1000,7 +1000,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>6780</v>
@@ -1041,7 +1041,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>2160</v>
@@ -1553,7 +1553,7 @@
         <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="L4" t="n">
         <v>17040</v>
@@ -1594,7 +1594,7 @@
         <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="L5" t="n">
         <v>27030</v>
@@ -1635,7 +1635,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="L6" t="n">
         <v>30780</v>
@@ -1676,7 +1676,7 @@
         <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="L7" t="n">
         <v>38400</v>
@@ -1717,7 +1717,7 @@
         <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="L8" t="n">
         <v>49770</v>
@@ -1758,7 +1758,7 @@
         <v>4</v>
       </c>
       <c r="K9" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="L9" t="n">
         <v>44310</v>
@@ -1799,7 +1799,7 @@
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="L10" t="n">
         <v>59520</v>
@@ -1840,7 +1840,7 @@
         <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="L11" t="n">
         <v>93660</v>
@@ -1881,7 +1881,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="L12" t="n">
         <v>64500</v>
@@ -1922,7 +1922,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>31290</v>
@@ -1963,7 +1963,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>12810</v>
@@ -2004,7 +2004,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>5400</v>
@@ -2598,7 +2598,7 @@
         <v>0.6</v>
       </c>
       <c r="K5" t="n">
-        <v>6.29</v>
+        <v>2.98</v>
       </c>
       <c r="L5" t="n">
         <v>5676.3</v>
@@ -2639,7 +2639,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>12.68</v>
+        <v>5.58</v>
       </c>
       <c r="L6" t="n">
         <v>11388.6</v>
@@ -2680,7 +2680,7 @@
         <v>0.7</v>
       </c>
       <c r="K7" t="n">
-        <v>14.04</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="L7" t="n">
         <v>23040</v>
@@ -2721,7 +2721,7 @@
         <v>0.85</v>
       </c>
       <c r="K8" t="n">
-        <v>18.4</v>
+        <v>6.62</v>
       </c>
       <c r="L8" t="n">
         <v>35336.7</v>
@@ -2762,7 +2762,7 @@
         <v>3.8</v>
       </c>
       <c r="K9" t="n">
-        <v>16.86</v>
+        <v>2.41</v>
       </c>
       <c r="L9" t="n">
         <v>35891.1</v>
@@ -2803,7 +2803,7 @@
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>26.97</v>
+        <v>3.48</v>
       </c>
       <c r="L10" t="n">
         <v>52972.8</v>
@@ -2844,7 +2844,7 @@
         <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>32.35</v>
+        <v>3.59</v>
       </c>
       <c r="L11" t="n">
         <v>93660</v>
@@ -2885,7 +2885,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>32.44</v>
+        <v>5.56</v>
       </c>
       <c r="L12" t="n">
         <v>64500</v>
@@ -2926,7 +2926,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>16.14</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>31290</v>
@@ -2967,7 +2967,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>9.720000000000001</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>12810</v>
@@ -3008,7 +3008,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>5400</v>
@@ -3602,7 +3602,7 @@
         <v>14566.8</v>
       </c>
       <c r="K5" t="n">
-        <v>305368.68</v>
+        <v>144648.32</v>
       </c>
       <c r="L5" t="n">
         <v>1021734</v>
@@ -3643,7 +3643,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>615447.3</v>
+        <v>270796.81</v>
       </c>
       <c r="L6" t="n">
         <v>2049948</v>
@@ -3684,7 +3684,7 @@
         <v>16994.6</v>
       </c>
       <c r="K7" t="n">
-        <v>681532.02</v>
+        <v>402723.46</v>
       </c>
       <c r="L7" t="n">
         <v>4147200</v>
@@ -3725,7 +3725,7 @@
         <v>20636.3</v>
       </c>
       <c r="K8" t="n">
-        <v>893430.4</v>
+        <v>321634.94</v>
       </c>
       <c r="L8" t="n">
         <v>6360606</v>
@@ -3766,7 +3766,7 @@
         <v>92256.39999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>818799.83</v>
+        <v>116971.4</v>
       </c>
       <c r="L9" t="n">
         <v>6460398</v>
@@ -3807,7 +3807,7 @@
         <v>24278</v>
       </c>
       <c r="K10" t="n">
-        <v>1309555.32</v>
+        <v>168974.88</v>
       </c>
       <c r="L10" t="n">
         <v>9535104</v>
@@ -3848,7 +3848,7 @@
         <v>24278</v>
       </c>
       <c r="K11" t="n">
-        <v>1570592.38</v>
+        <v>174510.26</v>
       </c>
       <c r="L11" t="n">
         <v>16858800</v>
@@ -3889,7 +3889,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>1575399.42</v>
+        <v>270068.47</v>
       </c>
       <c r="L12" t="n">
         <v>11610000</v>
@@ -3930,7 +3930,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>783766.67</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>5632200</v>
@@ -3971,7 +3971,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>471964.32</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>2305800</v>
@@ -4012,7 +4012,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>143628.65</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>972000</v>
@@ -4565,7 +4565,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="L4" t="n">
         <v>126180</v>
@@ -4606,7 +4606,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="L5" t="n">
         <v>47730</v>
@@ -4647,7 +4647,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>9540</v>
@@ -5610,7 +5610,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>6.95</v>
+        <v>3.31</v>
       </c>
       <c r="L5" t="n">
         <v>10023.3</v>
@@ -5651,7 +5651,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.51</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>3529.8</v>
@@ -6614,7 +6614,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>337512.76</v>
+        <v>160720.36</v>
       </c>
       <c r="L5" t="n">
         <v>1804194</v>
@@ -6655,7 +6655,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>24617.89</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>635364</v>
@@ -7577,7 +7577,7 @@
         <v>10</v>
       </c>
       <c r="K4" t="n">
-        <v>137</v>
+        <v>26</v>
       </c>
       <c r="L4" t="n">
         <v>107280</v>
@@ -7618,7 +7618,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="L5" t="n">
         <v>34710</v>
@@ -7659,7 +7659,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>8700</v>
@@ -7700,7 +7700,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>3210</v>
@@ -7741,7 +7741,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>1320</v>
@@ -8622,7 +8622,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>8.94</v>
+        <v>1.66</v>
       </c>
       <c r="L5" t="n">
         <v>7289.1</v>
@@ -8663,7 +8663,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>3219</v>
@@ -8704,7 +8704,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>1926</v>
@@ -8745,7 +8745,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.74</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>937.2</v>
@@ -9626,7 +9626,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>433944.97</v>
+        <v>80360.17999999999</v>
       </c>
       <c r="L5" t="n">
         <v>1312038</v>
@@ -9667,7 +9667,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>196943.14</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>579420</v>
@@ -9708,7 +9708,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>92936.17999999999</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>346680</v>
@@ -9749,7 +9749,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>35737.22</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>168696</v>
@@ -10589,7 +10589,7 @@
         <v>9</v>
       </c>
       <c r="K4" t="n">
-        <v>230</v>
+        <v>133</v>
       </c>
       <c r="L4" t="n">
         <v>194130</v>
@@ -10630,7 +10630,7 @@
         <v>11</v>
       </c>
       <c r="K5" t="n">
-        <v>171</v>
+        <v>87</v>
       </c>
       <c r="L5" t="n">
         <v>193380</v>
@@ -10671,7 +10671,7 @@
         <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>219</v>
+        <v>84</v>
       </c>
       <c r="L6" t="n">
         <v>208650</v>
@@ -10712,7 +10712,7 @@
         <v>3</v>
       </c>
       <c r="K7" t="n">
-        <v>134</v>
+        <v>43</v>
       </c>
       <c r="L7" t="n">
         <v>137640</v>
@@ -10753,7 +10753,7 @@
         <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>92</v>
+        <v>33</v>
       </c>
       <c r="L8" t="n">
         <v>84090</v>
@@ -10794,7 +10794,7 @@
         <v>2</v>
       </c>
       <c r="K9" t="n">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="L9" t="n">
         <v>43200</v>
@@ -10835,7 +10835,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="L10" t="n">
         <v>10680</v>
@@ -11634,7 +11634,7 @@
         <v>7.8</v>
       </c>
       <c r="K5" t="n">
-        <v>187.68</v>
+        <v>76.79000000000001</v>
       </c>
       <c r="L5" t="n">
         <v>179203.5</v>
@@ -11675,7 +11675,7 @@
         <v>5</v>
       </c>
       <c r="K6" t="n">
-        <v>257.56</v>
+        <v>87.70999999999999</v>
       </c>
       <c r="L6" t="n">
         <v>234942.6</v>
@@ -11716,7 +11716,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>251.37</v>
+        <v>70.18000000000001</v>
       </c>
       <c r="L7" t="n">
         <v>302220</v>
@@ -11757,7 +11757,7 @@
         <v>4.25</v>
       </c>
       <c r="K8" t="n">
-        <v>245.09</v>
+        <v>76.54000000000001</v>
       </c>
       <c r="L8" t="n">
         <v>282331.5</v>
@@ -11798,7 +11798,7 @@
         <v>8.550000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>214.4</v>
+        <v>52.2</v>
       </c>
       <c r="L9" t="n">
         <v>235880.1</v>
@@ -11839,7 +11839,7 @@
         <v>3</v>
       </c>
       <c r="K10" t="n">
-        <v>149.64</v>
+        <v>33.93</v>
       </c>
       <c r="L10" t="n">
         <v>158598</v>
@@ -11880,7 +11880,7 @@
         <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>93.44</v>
+        <v>13.48</v>
       </c>
       <c r="L11" t="n">
         <v>162570</v>
@@ -11921,7 +11921,7 @@
         <v>3</v>
       </c>
       <c r="K12" t="n">
-        <v>61.18</v>
+        <v>6.49</v>
       </c>
       <c r="L12" t="n">
         <v>96930</v>
@@ -11962,7 +11962,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>26.59</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>42900</v>
@@ -12003,7 +12003,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>10.69</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>16410</v>
@@ -12044,7 +12044,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>6780</v>
@@ -12085,7 +12085,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>2160</v>
@@ -12638,7 +12638,7 @@
         <v>3.3</v>
       </c>
       <c r="K5" t="n">
-        <v>56.6</v>
+        <v>28.8</v>
       </c>
       <c r="L5" t="n">
         <v>40609.8</v>
@@ -12679,7 +12679,7 @@
         <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>111.03</v>
+        <v>42.59</v>
       </c>
       <c r="L6" t="n">
         <v>77200.5</v>
@@ -12720,7 +12720,7 @@
         <v>2.1</v>
       </c>
       <c r="K7" t="n">
-        <v>85.48999999999999</v>
+        <v>27.43</v>
       </c>
       <c r="L7" t="n">
         <v>82584</v>
@@ -12761,7 +12761,7 @@
         <v>0.85</v>
       </c>
       <c r="K8" t="n">
-        <v>67.70999999999999</v>
+        <v>24.29</v>
       </c>
       <c r="L8" t="n">
         <v>59703.9</v>
@@ -12802,7 +12802,7 @@
         <v>1.9</v>
       </c>
       <c r="K9" t="n">
-        <v>40.95</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="L9" t="n">
         <v>34992</v>
@@ -12843,7 +12843,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>6.96</v>
+        <v>1.74</v>
       </c>
       <c r="L10" t="n">
         <v>9505.200000000001</v>
@@ -13642,7 +13642,7 @@
         <v>80117.39999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>2748318.16</v>
+        <v>1398267.13</v>
       </c>
       <c r="L5" t="n">
         <v>7309764</v>
@@ -13683,7 +13683,7 @@
         <v>24278</v>
       </c>
       <c r="K6" t="n">
-        <v>5391318.35</v>
+        <v>2067902.93</v>
       </c>
       <c r="L6" t="n">
         <v>13896090</v>
@@ -13724,7 +13724,7 @@
         <v>50983.8</v>
       </c>
       <c r="K7" t="n">
-        <v>4151149.55</v>
+        <v>1332085.3</v>
       </c>
       <c r="L7" t="n">
         <v>14865120</v>
@@ -13765,7 +13765,7 @@
         <v>20636.3</v>
       </c>
       <c r="K8" t="n">
-        <v>3287823.87</v>
+        <v>1179328.13</v>
       </c>
       <c r="L8" t="n">
         <v>10746702</v>
@@ -13806,7 +13806,7 @@
         <v>46128.2</v>
       </c>
       <c r="K9" t="n">
-        <v>1988513.87</v>
+        <v>389904.68</v>
       </c>
       <c r="L9" t="n">
         <v>6298560</v>
@@ -13847,7 +13847,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>337949.76</v>
+        <v>84487.44</v>
       </c>
       <c r="L10" t="n">
         <v>1710936</v>
@@ -14605,7 +14605,7 @@
         <v>4</v>
       </c>
       <c r="K4" t="n">
-        <v>102</v>
+        <v>39</v>
       </c>
       <c r="L4" t="n">
         <v>289500</v>
@@ -14646,7 +14646,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="L5" t="n">
         <v>85800</v>
@@ -15650,7 +15650,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>6.62</v>
+        <v>3.64</v>
       </c>
       <c r="L5" t="n">
         <v>18018</v>
@@ -16654,7 +16654,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>321440.72</v>
+        <v>176792.4</v>
       </c>
       <c r="L5" t="n">
         <v>3243240</v>
@@ -17658,7 +17658,7 @@
         <v>189368.4</v>
       </c>
       <c r="K5" t="n">
-        <v>9112844.41</v>
+        <v>3728712.35</v>
       </c>
       <c r="L5" t="n">
         <v>32256630</v>
@@ -17699,7 +17699,7 @@
         <v>121390</v>
       </c>
       <c r="K6" t="n">
-        <v>12505889.14</v>
+        <v>4258895.32</v>
       </c>
       <c r="L6" t="n">
         <v>42289668</v>
@@ -17740,7 +17740,7 @@
         <v>237924.4</v>
       </c>
       <c r="K7" t="n">
-        <v>12205618.83</v>
+        <v>3407660.08</v>
       </c>
       <c r="L7" t="n">
         <v>54399600</v>
@@ -17781,7 +17781,7 @@
         <v>103181.5</v>
       </c>
       <c r="K8" t="n">
-        <v>11900492.93</v>
+        <v>3716670.46</v>
       </c>
       <c r="L8" t="n">
         <v>50819670</v>
@@ -17822,7 +17822,7 @@
         <v>207576.9</v>
       </c>
       <c r="K9" t="n">
-        <v>10410454.96</v>
+        <v>2534380.42</v>
       </c>
       <c r="L9" t="n">
         <v>42458418</v>
@@ -17863,7 +17863,7 @@
         <v>72834</v>
       </c>
       <c r="K10" t="n">
-        <v>7265919.84</v>
+        <v>1647505.08</v>
       </c>
       <c r="L10" t="n">
         <v>28547640</v>
@@ -17904,7 +17904,7 @@
         <v>72834</v>
       </c>
       <c r="K11" t="n">
-        <v>4537266.86</v>
+        <v>654413.49</v>
       </c>
       <c r="L11" t="n">
         <v>29262600</v>
@@ -17945,7 +17945,7 @@
         <v>72834</v>
       </c>
       <c r="K12" t="n">
-        <v>2970753.19</v>
+        <v>315079.88</v>
       </c>
       <c r="L12" t="n">
         <v>17447400</v>
@@ -17986,7 +17986,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>1290909.82</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>7722000</v>
@@ -18027,7 +18027,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>519160.75</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>2953800</v>
@@ -18068,7 +18068,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>143628.65</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>1220400</v>
@@ -18109,7 +18109,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>48556</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>388800</v>
@@ -18621,7 +18621,7 @@
         <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>128</v>
+        <v>66</v>
       </c>
       <c r="L4" t="n">
         <v>155010</v>
@@ -18662,7 +18662,7 @@
         <v>4</v>
       </c>
       <c r="K5" t="n">
-        <v>154</v>
+        <v>61</v>
       </c>
       <c r="L5" t="n">
         <v>187860</v>
@@ -18703,7 +18703,7 @@
         <v>5</v>
       </c>
       <c r="K6" t="n">
-        <v>160</v>
+        <v>59</v>
       </c>
       <c r="L6" t="n">
         <v>198090</v>
@@ -18744,7 +18744,7 @@
         <v>9</v>
       </c>
       <c r="K7" t="n">
-        <v>200</v>
+        <v>48</v>
       </c>
       <c r="L7" t="n">
         <v>247020</v>
@@ -18785,7 +18785,7 @@
         <v>3</v>
       </c>
       <c r="K8" t="n">
-        <v>210</v>
+        <v>62</v>
       </c>
       <c r="L8" t="n">
         <v>236730</v>
@@ -18826,7 +18826,7 @@
         <v>3</v>
       </c>
       <c r="K9" t="n">
-        <v>194</v>
+        <v>51</v>
       </c>
       <c r="L9" t="n">
         <v>193650</v>
@@ -18867,7 +18867,7 @@
         <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>133</v>
+        <v>33</v>
       </c>
       <c r="L10" t="n">
         <v>104940</v>
@@ -18908,7 +18908,7 @@
         <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>66</v>
+        <v>9</v>
       </c>
       <c r="L11" t="n">
         <v>63240</v>
@@ -18949,7 +18949,7 @@
         <v>3</v>
       </c>
       <c r="K12" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
         <v>28890</v>
@@ -18990,7 +18990,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>10080</v>
@@ -19031,7 +19031,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>2610</v>
@@ -19113,7 +19113,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>240</v>
@@ -19666,7 +19666,7 @@
         <v>1.2</v>
       </c>
       <c r="K5" t="n">
-        <v>50.97</v>
+        <v>20.19</v>
       </c>
       <c r="L5" t="n">
         <v>39450.6</v>
@@ -19707,7 +19707,7 @@
         <v>2.5</v>
       </c>
       <c r="K6" t="n">
-        <v>81.12</v>
+        <v>29.91</v>
       </c>
       <c r="L6" t="n">
         <v>73293.3</v>
@@ -19748,7 +19748,7 @@
         <v>6.3</v>
       </c>
       <c r="K7" t="n">
-        <v>127.6</v>
+        <v>30.62</v>
       </c>
       <c r="L7" t="n">
         <v>148212</v>
@@ -19789,7 +19789,7 @@
         <v>2.55</v>
       </c>
       <c r="K8" t="n">
-        <v>154.56</v>
+        <v>45.63</v>
       </c>
       <c r="L8" t="n">
         <v>168078.3</v>
@@ -19830,7 +19830,7 @@
         <v>2.85</v>
       </c>
       <c r="K9" t="n">
-        <v>155.78</v>
+        <v>40.95</v>
       </c>
       <c r="L9" t="n">
         <v>156856.5</v>
@@ -19871,7 +19871,7 @@
         <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>115.71</v>
+        <v>28.71</v>
       </c>
       <c r="L10" t="n">
         <v>93396.60000000001</v>
@@ -19912,7 +19912,7 @@
         <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>59.3</v>
+        <v>8.09</v>
       </c>
       <c r="L11" t="n">
         <v>63240</v>
@@ -19953,7 +19953,7 @@
         <v>3</v>
       </c>
       <c r="K12" t="n">
-        <v>28.74</v>
+        <v>0.93</v>
       </c>
       <c r="L12" t="n">
         <v>28890</v>
@@ -19994,7 +19994,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>10.44</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>10080</v>
@@ -20035,7 +20035,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0.97</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>2610</v>
@@ -20117,7 +20117,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>240</v>
@@ -20670,7 +20670,7 @@
         <v>29133.6</v>
       </c>
       <c r="K5" t="n">
-        <v>2475093.54</v>
+        <v>980394.2</v>
       </c>
       <c r="L5" t="n">
         <v>7101108</v>
@@ -20711,7 +20711,7 @@
         <v>60695</v>
       </c>
       <c r="K6" t="n">
-        <v>3938862.72</v>
+        <v>1452455.63</v>
       </c>
       <c r="L6" t="n">
         <v>13192794</v>
@@ -20752,7 +20752,7 @@
         <v>152951.4</v>
       </c>
       <c r="K7" t="n">
-        <v>6195745.6</v>
+        <v>1486978.94</v>
       </c>
       <c r="L7" t="n">
         <v>26678160</v>
@@ -20793,7 +20793,7 @@
         <v>61908.9</v>
       </c>
       <c r="K8" t="n">
-        <v>7504815.36</v>
+        <v>2215707.39</v>
       </c>
       <c r="L8" t="n">
         <v>30254094</v>
@@ -20834,7 +20834,7 @@
         <v>69192.3</v>
       </c>
       <c r="K9" t="n">
-        <v>7564150.79</v>
+        <v>1988513.87</v>
       </c>
       <c r="L9" t="n">
         <v>28234170</v>
@@ -20875,7 +20875,7 @@
         <v>48556</v>
       </c>
       <c r="K10" t="n">
-        <v>5618414.76</v>
+        <v>1394042.76</v>
       </c>
       <c r="L10" t="n">
         <v>16811388</v>
@@ -20916,7 +20916,7 @@
         <v>48556</v>
       </c>
       <c r="K11" t="n">
-        <v>2879419.36</v>
+        <v>392648.09</v>
       </c>
       <c r="L11" t="n">
         <v>11383200</v>
@@ -20957,7 +20957,7 @@
         <v>72834</v>
       </c>
       <c r="K12" t="n">
-        <v>1395353.77</v>
+        <v>45011.41</v>
       </c>
       <c r="L12" t="n">
         <v>5200200</v>
@@ -20998,7 +20998,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>507143.14</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>1814400</v>
@@ -21039,7 +21039,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>47196.43</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>469800</v>
@@ -21121,7 +21121,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>48556</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>43200</v>
@@ -21633,7 +21633,7 @@
         <v>12</v>
       </c>
       <c r="K4" t="n">
-        <v>350</v>
+        <v>89</v>
       </c>
       <c r="L4" t="n">
         <v>401340</v>
@@ -21674,7 +21674,7 @@
         <v>7</v>
       </c>
       <c r="K5" t="n">
-        <v>153</v>
+        <v>49</v>
       </c>
       <c r="L5" t="n">
         <v>216030</v>
@@ -21715,7 +21715,7 @@
         <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>93</v>
+        <v>19</v>
       </c>
       <c r="L6" t="n">
         <v>115230</v>
@@ -21756,7 +21756,7 @@
         <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="L7" t="n">
         <v>46380</v>
@@ -21797,7 +21797,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>7020</v>
@@ -22678,7 +22678,7 @@
         <v>2.1</v>
       </c>
       <c r="K5" t="n">
-        <v>50.64</v>
+        <v>16.22</v>
       </c>
       <c r="L5" t="n">
         <v>45366.3</v>
@@ -22719,7 +22719,7 @@
         <v>1.5</v>
       </c>
       <c r="K6" t="n">
-        <v>47.15</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="L6" t="n">
         <v>42635.1</v>
@@ -22760,7 +22760,7 @@
         <v>0.7</v>
       </c>
       <c r="K7" t="n">
-        <v>21.69</v>
+        <v>3.19</v>
       </c>
       <c r="L7" t="n">
         <v>27828</v>
@@ -22801,7 +22801,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>4984.2</v>
@@ -23682,7 +23682,7 @@
         <v>50983.8</v>
       </c>
       <c r="K5" t="n">
-        <v>2459021.51</v>
+        <v>787529.76</v>
       </c>
       <c r="L5" t="n">
         <v>8165934</v>
@@ -23723,7 +23723,7 @@
         <v>36417</v>
       </c>
       <c r="K6" t="n">
-        <v>2289463.96</v>
+        <v>467739.95</v>
       </c>
       <c r="L6" t="n">
         <v>7674318</v>
@@ -23764,7 +23764,7 @@
         <v>16994.6</v>
       </c>
       <c r="K7" t="n">
-        <v>1053276.75</v>
+        <v>154893.64</v>
       </c>
       <c r="L7" t="n">
         <v>5009040</v>
@@ -23805,7 +23805,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>107211.65</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>897156</v>

--- a/risk/Risk_Analysis_T3_50yrs_Present_Perfect.xlsx
+++ b/risk/Risk_Analysis_T3_50yrs_Present_Perfect.xlsx
@@ -560,7 +560,7 @@
         <v>513270</v>
       </c>
       <c r="H4" t="n">
-        <v>68100</v>
+        <v>73560</v>
       </c>
       <c r="I4" t="n">
         <v>10</v>
@@ -572,22 +572,22 @@
         <v>392</v>
       </c>
       <c r="L4" t="n">
-        <v>1350570</v>
+        <v>1451490</v>
       </c>
       <c r="M4" t="n">
-        <v>64800</v>
+        <v>49560</v>
       </c>
       <c r="N4" t="n">
-        <v>77010</v>
+        <v>77670</v>
       </c>
       <c r="O4" t="n">
-        <v>227940</v>
+        <v>234060</v>
       </c>
       <c r="P4" t="n">
-        <v>46680</v>
+        <v>17610</v>
       </c>
       <c r="Q4" t="n">
-        <v>201741.44</v>
+        <v>2090627.02</v>
       </c>
     </row>
     <row r="5">
@@ -613,7 +613,7 @@
         <v>337110</v>
       </c>
       <c r="H5" t="n">
-        <v>48750</v>
+        <v>56220</v>
       </c>
       <c r="I5" t="n">
         <v>3</v>
@@ -625,22 +625,22 @@
         <v>232</v>
       </c>
       <c r="L5" t="n">
-        <v>853350</v>
+        <v>895200</v>
       </c>
       <c r="M5" t="n">
-        <v>50490</v>
+        <v>32130</v>
       </c>
       <c r="N5" t="n">
-        <v>60840</v>
+        <v>74610</v>
       </c>
       <c r="O5" t="n">
-        <v>167820</v>
+        <v>193020</v>
       </c>
       <c r="P5" t="n">
-        <v>59250</v>
+        <v>38130</v>
       </c>
       <c r="Q5" t="n">
-        <v>136539.36</v>
+        <v>1414944.21</v>
       </c>
     </row>
     <row r="6">
@@ -666,7 +666,7 @@
         <v>249300</v>
       </c>
       <c r="H6" t="n">
-        <v>56340</v>
+        <v>56550</v>
       </c>
       <c r="I6" t="n">
         <v>1</v>
@@ -678,22 +678,22 @@
         <v>173</v>
       </c>
       <c r="L6" t="n">
-        <v>634980</v>
+        <v>636720</v>
       </c>
       <c r="M6" t="n">
-        <v>30630</v>
+        <v>26400</v>
       </c>
       <c r="N6" t="n">
-        <v>15630</v>
+        <v>25260</v>
       </c>
       <c r="O6" t="n">
-        <v>109290</v>
+        <v>117840</v>
       </c>
       <c r="P6" t="n">
-        <v>59970</v>
+        <v>43410</v>
       </c>
       <c r="Q6" t="n">
-        <v>106634.02</v>
+        <v>1105038.06</v>
       </c>
     </row>
     <row r="7">
@@ -719,7 +719,7 @@
         <v>204750</v>
       </c>
       <c r="H7" t="n">
-        <v>30060</v>
+        <v>31890</v>
       </c>
       <c r="I7" t="n">
         <v>4</v>
@@ -731,22 +731,22 @@
         <v>110</v>
       </c>
       <c r="L7" t="n">
-        <v>503700</v>
+        <v>508650</v>
       </c>
       <c r="M7" t="n">
-        <v>20940</v>
+        <v>27270</v>
       </c>
       <c r="N7" t="n">
-        <v>3780</v>
+        <v>7770</v>
       </c>
       <c r="O7" t="n">
-        <v>73650</v>
+        <v>82740</v>
       </c>
       <c r="P7" t="n">
-        <v>70260</v>
+        <v>53760</v>
       </c>
       <c r="Q7" t="n">
-        <v>89607.55</v>
+        <v>928594.33</v>
       </c>
     </row>
     <row r="8">
@@ -772,7 +772,7 @@
         <v>165570</v>
       </c>
       <c r="H8" t="n">
-        <v>8040</v>
+        <v>10800</v>
       </c>
       <c r="I8" t="n">
         <v>1</v>
@@ -784,22 +784,22 @@
         <v>104</v>
       </c>
       <c r="L8" t="n">
-        <v>397650</v>
+        <v>413340</v>
       </c>
       <c r="M8" t="n">
-        <v>13260</v>
+        <v>31260</v>
       </c>
       <c r="N8" t="n">
-        <v>90</v>
+        <v>420</v>
       </c>
       <c r="O8" t="n">
-        <v>61980</v>
+        <v>69210</v>
       </c>
       <c r="P8" t="n">
-        <v>69480</v>
+        <v>64080</v>
       </c>
       <c r="Q8" t="n">
-        <v>77441.92</v>
+        <v>802523.11</v>
       </c>
     </row>
     <row r="9">
@@ -825,7 +825,7 @@
         <v>135780</v>
       </c>
       <c r="H9" t="n">
-        <v>3870</v>
+        <v>4230</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -837,22 +837,22 @@
         <v>65</v>
       </c>
       <c r="L9" t="n">
-        <v>291210</v>
+        <v>325620</v>
       </c>
       <c r="M9" t="n">
-        <v>10440</v>
+        <v>30990</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>38100</v>
+        <v>53700</v>
       </c>
       <c r="P9" t="n">
-        <v>72690</v>
+        <v>70140</v>
       </c>
       <c r="Q9" t="n">
-        <v>63802.72</v>
+        <v>661181.46</v>
       </c>
     </row>
     <row r="10">
@@ -878,7 +878,7 @@
         <v>80220</v>
       </c>
       <c r="H10" t="n">
-        <v>4890</v>
+        <v>4620</v>
       </c>
       <c r="I10" t="n">
         <v>3</v>
@@ -890,22 +890,22 @@
         <v>39</v>
       </c>
       <c r="L10" t="n">
-        <v>178200</v>
+        <v>209460</v>
       </c>
       <c r="M10" t="n">
-        <v>6840</v>
+        <v>26130</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>12450</v>
+        <v>23550</v>
       </c>
       <c r="P10" t="n">
-        <v>81720</v>
+        <v>90870</v>
       </c>
       <c r="Q10" t="n">
-        <v>39063.57</v>
+        <v>404812.01</v>
       </c>
     </row>
     <row r="11">
@@ -931,7 +931,7 @@
         <v>59970</v>
       </c>
       <c r="H11" t="n">
-        <v>4560</v>
+        <v>5490</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -943,22 +943,22 @@
         <v>15</v>
       </c>
       <c r="L11" t="n">
-        <v>162570</v>
+        <v>207420</v>
       </c>
       <c r="M11" t="n">
-        <v>3660</v>
+        <v>26400</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>5130</v>
+        <v>14940</v>
       </c>
       <c r="P11" t="n">
-        <v>66060</v>
+        <v>102420</v>
       </c>
       <c r="Q11" t="n">
-        <v>28410.57</v>
+        <v>294415.99</v>
       </c>
     </row>
     <row r="12">
@@ -984,7 +984,7 @@
         <v>47610</v>
       </c>
       <c r="H12" t="n">
-        <v>1260</v>
+        <v>1830</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -996,22 +996,22 @@
         <v>7</v>
       </c>
       <c r="L12" t="n">
-        <v>96930</v>
+        <v>143130</v>
       </c>
       <c r="M12" t="n">
-        <v>2850</v>
+        <v>16350</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>2370</v>
+        <v>3930</v>
       </c>
       <c r="P12" t="n">
-        <v>48030</v>
+        <v>81780</v>
       </c>
       <c r="Q12" t="n">
-        <v>19338.16</v>
+        <v>200399.48</v>
       </c>
     </row>
     <row r="13">
@@ -1037,7 +1037,7 @@
         <v>23430</v>
       </c>
       <c r="H13" t="n">
-        <v>840</v>
+        <v>780</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
@@ -1049,10 +1049,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>42900</v>
+        <v>64980</v>
       </c>
       <c r="M13" t="n">
-        <v>1410</v>
+        <v>20580</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>3600</v>
       </c>
       <c r="P13" t="n">
-        <v>33420</v>
+        <v>52200</v>
       </c>
       <c r="Q13" t="n">
-        <v>9795.690000000001</v>
+        <v>101511.79</v>
       </c>
     </row>
     <row r="14">
@@ -1090,7 +1090,7 @@
         <v>5970</v>
       </c>
       <c r="H14" t="n">
-        <v>240</v>
+        <v>480</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -1102,22 +1102,22 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>16410</v>
+        <v>30450</v>
       </c>
       <c r="M14" t="n">
-        <v>300</v>
+        <v>6540</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>630</v>
+        <v>990</v>
       </c>
       <c r="P14" t="n">
-        <v>28770</v>
+        <v>29790</v>
       </c>
       <c r="Q14" t="n">
-        <v>3832.57</v>
+        <v>39716.52</v>
       </c>
     </row>
     <row r="15">
@@ -1143,7 +1143,7 @@
         <v>4020</v>
       </c>
       <c r="H15" t="n">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -1155,22 +1155,22 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>6780</v>
+        <v>23370</v>
       </c>
       <c r="M15" t="n">
+        <v>3180</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
         <v>150</v>
       </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>30</v>
-      </c>
       <c r="P15" t="n">
-        <v>38970</v>
+        <v>55170</v>
       </c>
       <c r="Q15" t="n">
-        <v>2205.55</v>
+        <v>22855.91</v>
       </c>
     </row>
     <row r="16">
@@ -1196,7 +1196,7 @@
         <v>1170</v>
       </c>
       <c r="H16" t="n">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -1208,10 +1208,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>2160</v>
+        <v>9450</v>
       </c>
       <c r="M16" t="n">
-        <v>210</v>
+        <v>1530</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -1220,10 +1220,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>25500</v>
+        <v>42780</v>
       </c>
       <c r="Q16" t="n">
-        <v>1220.68</v>
+        <v>12649.8</v>
       </c>
     </row>
     <row r="17">
@@ -1249,7 +1249,7 @@
         <v>240</v>
       </c>
       <c r="H17" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -1261,10 +1261,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>1440</v>
+        <v>6210</v>
       </c>
       <c r="M17" t="n">
-        <v>150</v>
+        <v>990</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -1273,10 +1273,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>17010</v>
+        <v>23460</v>
       </c>
       <c r="Q17" t="n">
-        <v>520.0599999999999</v>
+        <v>5389.29</v>
       </c>
     </row>
     <row r="18">
@@ -1314,22 +1314,22 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>1530</v>
+        <v>4920</v>
       </c>
       <c r="M18" t="n">
-        <v>120</v>
+        <v>1320</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="P18" t="n">
-        <v>18120</v>
+        <v>24090</v>
       </c>
       <c r="Q18" t="n">
-        <v>251.66</v>
+        <v>2607.91</v>
       </c>
     </row>
     <row r="19">
@@ -1355,7 +1355,7 @@
         <v>3780</v>
       </c>
       <c r="H19" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -1367,10 +1367,10 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>780</v>
+        <v>2790</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>1530</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -1379,10 +1379,10 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>6870</v>
+        <v>18030</v>
       </c>
       <c r="Q19" t="n">
-        <v>106.13</v>
+        <v>1099.83</v>
       </c>
     </row>
     <row r="20">
@@ -1420,7 +1420,7 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -1432,10 +1432,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="Q20" t="n">
-        <v>16.29</v>
+        <v>168.85</v>
       </c>
     </row>
     <row r="21">
@@ -1473,7 +1473,7 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -1488,7 +1488,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.79</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="22">
@@ -1852,7 +1852,7 @@
         <v>7680</v>
       </c>
       <c r="H4" t="n">
-        <v>2670</v>
+        <v>3000</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -1864,22 +1864,22 @@
         <v>6</v>
       </c>
       <c r="L4" t="n">
-        <v>17040</v>
+        <v>15240</v>
       </c>
       <c r="M4" t="n">
-        <v>5340</v>
+        <v>2340</v>
       </c>
       <c r="N4" t="n">
-        <v>1050</v>
+        <v>600</v>
       </c>
       <c r="O4" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>203.58</v>
+        <v>23072.4</v>
       </c>
     </row>
     <row r="5">
@@ -1905,7 +1905,7 @@
         <v>8730</v>
       </c>
       <c r="H5" t="n">
-        <v>2370</v>
+        <v>3510</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -1917,22 +1917,22 @@
         <v>9</v>
       </c>
       <c r="L5" t="n">
-        <v>27030</v>
+        <v>20460</v>
       </c>
       <c r="M5" t="n">
-        <v>12780</v>
+        <v>5940</v>
       </c>
       <c r="N5" t="n">
-        <v>150</v>
+        <v>630</v>
       </c>
       <c r="O5" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>452.95</v>
+        <v>51334.56</v>
       </c>
     </row>
     <row r="6">
@@ -1958,7 +1958,7 @@
         <v>9120</v>
       </c>
       <c r="H6" t="n">
-        <v>2820</v>
+        <v>2640</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -1970,22 +1970,22 @@
         <v>11</v>
       </c>
       <c r="L6" t="n">
-        <v>30780</v>
+        <v>23280</v>
       </c>
       <c r="M6" t="n">
-        <v>10170</v>
+        <v>5790</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="O6" t="n">
-        <v>930</v>
+        <v>810</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>954.37</v>
+        <v>108161.82</v>
       </c>
     </row>
     <row r="7">
@@ -2011,7 +2011,7 @@
         <v>16230</v>
       </c>
       <c r="H7" t="n">
-        <v>3450</v>
+        <v>2490</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -2023,22 +2023,22 @@
         <v>13</v>
       </c>
       <c r="L7" t="n">
-        <v>38400</v>
+        <v>33780</v>
       </c>
       <c r="M7" t="n">
-        <v>6660</v>
+        <v>2910</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>420</v>
+        <v>480</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1349.78</v>
+        <v>152975.52</v>
       </c>
     </row>
     <row r="8">
@@ -2064,7 +2064,7 @@
         <v>19770</v>
       </c>
       <c r="H8" t="n">
-        <v>3750</v>
+        <v>5010</v>
       </c>
       <c r="I8" t="n">
         <v>1</v>
@@ -2076,22 +2076,22 @@
         <v>9</v>
       </c>
       <c r="L8" t="n">
-        <v>49770</v>
+        <v>47070</v>
       </c>
       <c r="M8" t="n">
-        <v>3960</v>
+        <v>3180</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1403.24</v>
+        <v>159034.32</v>
       </c>
     </row>
     <row r="9">
@@ -2117,7 +2117,7 @@
         <v>18660</v>
       </c>
       <c r="H9" t="n">
-        <v>3330</v>
+        <v>3240</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -2129,22 +2129,22 @@
         <v>3</v>
       </c>
       <c r="L9" t="n">
-        <v>44310</v>
+        <v>45840</v>
       </c>
       <c r="M9" t="n">
-        <v>3000</v>
+        <v>1560</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1376.46</v>
+        <v>155998.8</v>
       </c>
     </row>
     <row r="10">
@@ -2170,7 +2170,7 @@
         <v>20550</v>
       </c>
       <c r="H10" t="n">
-        <v>4530</v>
+        <v>4080</v>
       </c>
       <c r="I10" t="n">
         <v>2</v>
@@ -2182,22 +2182,22 @@
         <v>4</v>
       </c>
       <c r="L10" t="n">
-        <v>59520</v>
+        <v>56280</v>
       </c>
       <c r="M10" t="n">
-        <v>1950</v>
+        <v>3630</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1276.99</v>
+        <v>144725.76</v>
       </c>
     </row>
     <row r="11">
@@ -2223,7 +2223,7 @@
         <v>32610</v>
       </c>
       <c r="H11" t="n">
-        <v>4500</v>
+        <v>5100</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -2235,22 +2235,22 @@
         <v>4</v>
       </c>
       <c r="L11" t="n">
-        <v>93660</v>
+        <v>96540</v>
       </c>
       <c r="M11" t="n">
-        <v>930</v>
+        <v>4530</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>150</v>
+        <v>240</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1849.55</v>
+        <v>209616.12</v>
       </c>
     </row>
     <row r="12">
@@ -2276,7 +2276,7 @@
         <v>28290</v>
       </c>
       <c r="H12" t="n">
-        <v>1230</v>
+        <v>1590</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -2288,10 +2288,10 @@
         <v>6</v>
       </c>
       <c r="L12" t="n">
-        <v>64500</v>
+        <v>75690</v>
       </c>
       <c r="M12" t="n">
-        <v>300</v>
+        <v>3600</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -2303,7 +2303,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1756.24</v>
+        <v>199040.76</v>
       </c>
     </row>
     <row r="13">
@@ -2329,7 +2329,7 @@
         <v>13710</v>
       </c>
       <c r="H13" t="n">
-        <v>840</v>
+        <v>780</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
@@ -2341,10 +2341,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>31290</v>
+        <v>37500</v>
       </c>
       <c r="M13" t="n">
-        <v>240</v>
+        <v>3840</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -2356,7 +2356,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>945.08</v>
+        <v>107109.18</v>
       </c>
     </row>
     <row r="14">
@@ -2382,7 +2382,7 @@
         <v>4200</v>
       </c>
       <c r="H14" t="n">
-        <v>240</v>
+        <v>480</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -2394,10 +2394,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>12810</v>
+        <v>18270</v>
       </c>
       <c r="M14" t="n">
-        <v>150</v>
+        <v>3390</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -2409,7 +2409,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>398.3</v>
+        <v>45141.12</v>
       </c>
     </row>
     <row r="15">
@@ -2435,7 +2435,7 @@
         <v>3060</v>
       </c>
       <c r="H15" t="n">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -2447,10 +2447,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>5400</v>
+        <v>11580</v>
       </c>
       <c r="M15" t="n">
-        <v>60</v>
+        <v>1830</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2462,7 +2462,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>269.57</v>
+        <v>30551.04</v>
       </c>
     </row>
     <row r="16">
@@ -2488,7 +2488,7 @@
         <v>510</v>
       </c>
       <c r="H16" t="n">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -2500,10 +2500,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1620</v>
+        <v>3870</v>
       </c>
       <c r="M16" t="n">
-        <v>120</v>
+        <v>750</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2515,7 +2515,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>118.93</v>
+        <v>13479.3</v>
       </c>
     </row>
     <row r="17">
@@ -2541,7 +2541,7 @@
         <v>90</v>
       </c>
       <c r="H17" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -2553,10 +2553,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>930</v>
+        <v>2010</v>
       </c>
       <c r="M17" t="n">
-        <v>120</v>
+        <v>870</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>50.79</v>
+        <v>5755.86</v>
       </c>
     </row>
     <row r="18">
@@ -2606,10 +2606,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>750</v>
+        <v>2160</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>1230</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -2621,7 +2621,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>19.04</v>
+        <v>2157.3</v>
       </c>
     </row>
     <row r="19">
@@ -2647,7 +2647,7 @@
         <v>60</v>
       </c>
       <c r="H19" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -2659,10 +2659,10 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>660</v>
+        <v>2220</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>1440</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -2674,7 +2674,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>7.67</v>
+        <v>869.04</v>
       </c>
     </row>
     <row r="20">
@@ -2712,7 +2712,7 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -2727,7 +2727,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.67</v>
+        <v>189.72</v>
       </c>
     </row>
     <row r="21">
@@ -2765,7 +2765,7 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -2780,7 +2780,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.24</v>
+        <v>27.54</v>
       </c>
     </row>
     <row r="22">
@@ -3197,7 +3197,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>853.2</v>
+        <v>1263.6</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -3209,22 +3209,22 @@
         <v>2.98</v>
       </c>
       <c r="L5" t="n">
-        <v>5676.3</v>
+        <v>4296.6</v>
       </c>
       <c r="M5" t="n">
-        <v>255.6</v>
+        <v>118.8</v>
       </c>
       <c r="N5" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="O5" t="n">
         <v>1.5</v>
       </c>
-      <c r="O5" t="n">
-        <v>3</v>
-      </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>22.65</v>
+        <v>2566.73</v>
       </c>
     </row>
     <row r="6">
@@ -3250,7 +3250,7 @@
         <v>456</v>
       </c>
       <c r="H6" t="n">
-        <v>1607.4</v>
+        <v>1504.8</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -3262,22 +3262,22 @@
         <v>5.58</v>
       </c>
       <c r="L6" t="n">
-        <v>11388.6</v>
+        <v>8613.6</v>
       </c>
       <c r="M6" t="n">
-        <v>813.6</v>
+        <v>463.2</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="O6" t="n">
-        <v>232.5</v>
+        <v>202.5</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>715.78</v>
+        <v>81121.37</v>
       </c>
     </row>
     <row r="7">
@@ -3303,7 +3303,7 @@
         <v>2434.5</v>
       </c>
       <c r="H7" t="n">
-        <v>2518.5</v>
+        <v>1817.7</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -3315,22 +3315,22 @@
         <v>8.289999999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>23040</v>
+        <v>20268</v>
       </c>
       <c r="M7" t="n">
-        <v>2331</v>
+        <v>1018.5</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>147</v>
+        <v>168</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1079.83</v>
+        <v>122380.42</v>
       </c>
     </row>
     <row r="8">
@@ -3356,7 +3356,7 @@
         <v>12850.5</v>
       </c>
       <c r="H8" t="n">
-        <v>3187.5</v>
+        <v>4258.5</v>
       </c>
       <c r="I8" t="n">
         <v>0.74</v>
@@ -3368,22 +3368,22 @@
         <v>6.62</v>
       </c>
       <c r="L8" t="n">
-        <v>35336.7</v>
+        <v>33419.7</v>
       </c>
       <c r="M8" t="n">
-        <v>2178</v>
+        <v>1749</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>67.5</v>
+        <v>81</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1333.08</v>
+        <v>151082.6</v>
       </c>
     </row>
     <row r="9">
@@ -3409,7 +3409,7 @@
         <v>15861</v>
       </c>
       <c r="H9" t="n">
-        <v>3330</v>
+        <v>3240</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -3421,22 +3421,22 @@
         <v>2.41</v>
       </c>
       <c r="L9" t="n">
-        <v>35891.1</v>
+        <v>37130.4</v>
       </c>
       <c r="M9" t="n">
-        <v>2100</v>
+        <v>1092</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>49.5</v>
+        <v>99</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1335.17</v>
+        <v>151318.84</v>
       </c>
     </row>
     <row r="10">
@@ -3462,7 +3462,7 @@
         <v>20550</v>
       </c>
       <c r="H10" t="n">
-        <v>4530</v>
+        <v>4080</v>
       </c>
       <c r="I10" t="n">
         <v>1.74</v>
@@ -3474,22 +3474,22 @@
         <v>3.48</v>
       </c>
       <c r="L10" t="n">
-        <v>52972.8</v>
+        <v>50089.2</v>
       </c>
       <c r="M10" t="n">
-        <v>1657.5</v>
+        <v>3085.5</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>105</v>
+        <v>42</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1276.99</v>
+        <v>144725.76</v>
       </c>
     </row>
     <row r="11">
@@ -3515,7 +3515,7 @@
         <v>32610</v>
       </c>
       <c r="H11" t="n">
-        <v>4500</v>
+        <v>5100</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -3527,22 +3527,22 @@
         <v>3.59</v>
       </c>
       <c r="L11" t="n">
-        <v>93660</v>
+        <v>96540</v>
       </c>
       <c r="M11" t="n">
-        <v>837</v>
+        <v>4077</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>127.5</v>
+        <v>204</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1849.55</v>
+        <v>209616.12</v>
       </c>
     </row>
     <row r="12">
@@ -3568,7 +3568,7 @@
         <v>28290</v>
       </c>
       <c r="H12" t="n">
-        <v>1230</v>
+        <v>1590</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -3580,10 +3580,10 @@
         <v>5.56</v>
       </c>
       <c r="L12" t="n">
-        <v>64500</v>
+        <v>75690</v>
       </c>
       <c r="M12" t="n">
-        <v>285</v>
+        <v>3420</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -3595,7 +3595,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1756.24</v>
+        <v>199040.76</v>
       </c>
     </row>
     <row r="13">
@@ -3621,7 +3621,7 @@
         <v>13710</v>
       </c>
       <c r="H13" t="n">
-        <v>840</v>
+        <v>780</v>
       </c>
       <c r="I13" t="n">
         <v>0.95</v>
@@ -3633,10 +3633,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>31290</v>
+        <v>37500</v>
       </c>
       <c r="M13" t="n">
-        <v>240</v>
+        <v>3840</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -3648,7 +3648,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>945.08</v>
+        <v>107109.18</v>
       </c>
     </row>
     <row r="14">
@@ -3674,7 +3674,7 @@
         <v>4200</v>
       </c>
       <c r="H14" t="n">
-        <v>240</v>
+        <v>480</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -3686,10 +3686,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>12810</v>
+        <v>18270</v>
       </c>
       <c r="M14" t="n">
-        <v>150</v>
+        <v>3390</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -3701,7 +3701,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>398.3</v>
+        <v>45141.12</v>
       </c>
     </row>
     <row r="15">
@@ -3727,7 +3727,7 @@
         <v>3060</v>
       </c>
       <c r="H15" t="n">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -3739,10 +3739,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>5400</v>
+        <v>11580</v>
       </c>
       <c r="M15" t="n">
-        <v>60</v>
+        <v>1830</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -3754,7 +3754,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>269.57</v>
+        <v>30551.04</v>
       </c>
     </row>
     <row r="16">
@@ -3780,7 +3780,7 @@
         <v>510</v>
       </c>
       <c r="H16" t="n">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -3792,10 +3792,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1620</v>
+        <v>3870</v>
       </c>
       <c r="M16" t="n">
-        <v>120</v>
+        <v>750</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -3807,7 +3807,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>118.93</v>
+        <v>13479.3</v>
       </c>
     </row>
     <row r="17">
@@ -3833,7 +3833,7 @@
         <v>90</v>
       </c>
       <c r="H17" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -3845,10 +3845,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>930</v>
+        <v>2010</v>
       </c>
       <c r="M17" t="n">
-        <v>120</v>
+        <v>870</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -3860,7 +3860,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>50.79</v>
+        <v>5755.86</v>
       </c>
     </row>
     <row r="18">
@@ -3898,10 +3898,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>750</v>
+        <v>2160</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>1230</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -3913,7 +3913,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>19.04</v>
+        <v>2157.3</v>
       </c>
     </row>
     <row r="19">
@@ -3939,7 +3939,7 @@
         <v>60</v>
       </c>
       <c r="H19" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -3951,10 +3951,10 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>660</v>
+        <v>2220</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>1440</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -3966,7 +3966,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>7.67</v>
+        <v>869.04</v>
       </c>
     </row>
     <row r="20">
@@ -4004,7 +4004,7 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -4019,7 +4019,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.67</v>
+        <v>189.72</v>
       </c>
     </row>
     <row r="21">
@@ -4057,7 +4057,7 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -4072,7 +4072,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.24</v>
+        <v>27.54</v>
       </c>
     </row>
     <row r="22">
@@ -4489,7 +4489,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>4863240</v>
+        <v>7202520</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -4501,22 +4501,22 @@
         <v>144648.32</v>
       </c>
       <c r="L5" t="n">
-        <v>1021734</v>
+        <v>773388</v>
       </c>
       <c r="M5" t="n">
-        <v>89460</v>
+        <v>41580</v>
       </c>
       <c r="N5" t="n">
+        <v>1071</v>
+      </c>
+      <c r="O5" t="n">
         <v>255</v>
       </c>
-      <c r="O5" t="n">
-        <v>510</v>
-      </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>13588.56</v>
+        <v>1540036.8</v>
       </c>
     </row>
     <row r="6">
@@ -4542,7 +4542,7 @@
         <v>24624</v>
       </c>
       <c r="H6" t="n">
-        <v>9162180</v>
+        <v>8577360</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -4554,22 +4554,22 @@
         <v>270796.81</v>
       </c>
       <c r="L6" t="n">
-        <v>2049948</v>
+        <v>1550448</v>
       </c>
       <c r="M6" t="n">
-        <v>284760</v>
+        <v>162120</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1275</v>
       </c>
       <c r="O6" t="n">
-        <v>39525</v>
+        <v>34425</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>429466.05</v>
+        <v>48672819</v>
       </c>
     </row>
     <row r="7">
@@ -4595,7 +4595,7 @@
         <v>131463</v>
       </c>
       <c r="H7" t="n">
-        <v>14355450</v>
+        <v>10360890</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -4607,22 +4607,22 @@
         <v>402723.46</v>
       </c>
       <c r="L7" t="n">
-        <v>4147200</v>
+        <v>3648240</v>
       </c>
       <c r="M7" t="n">
-        <v>815850</v>
+        <v>356475</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>24990</v>
+        <v>28560</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>647896.3199999999</v>
+        <v>73428249.59999999</v>
       </c>
     </row>
     <row r="8">
@@ -4648,7 +4648,7 @@
         <v>693927</v>
       </c>
       <c r="H8" t="n">
-        <v>18168750</v>
+        <v>24273450</v>
       </c>
       <c r="I8" t="n">
         <v>142948.86</v>
@@ -4660,22 +4660,22 @@
         <v>321634.94</v>
       </c>
       <c r="L8" t="n">
-        <v>6360606</v>
+        <v>6015546</v>
       </c>
       <c r="M8" t="n">
-        <v>762300</v>
+        <v>612150</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>11475</v>
+        <v>13770</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>799849.08</v>
+        <v>90649562.40000001</v>
       </c>
     </row>
     <row r="9">
@@ -4701,7 +4701,7 @@
         <v>856494</v>
       </c>
       <c r="H9" t="n">
-        <v>18981000</v>
+        <v>18468000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -4713,22 +4713,22 @@
         <v>116971.4</v>
       </c>
       <c r="L9" t="n">
-        <v>6460398</v>
+        <v>6683472</v>
       </c>
       <c r="M9" t="n">
-        <v>735000</v>
+        <v>382200</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>8415</v>
+        <v>16830</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>801099.72</v>
+        <v>90791301.59999999</v>
       </c>
     </row>
     <row r="10">
@@ -4754,7 +4754,7 @@
         <v>1109700</v>
       </c>
       <c r="H10" t="n">
-        <v>25821000</v>
+        <v>23256000</v>
       </c>
       <c r="I10" t="n">
         <v>337949.76</v>
@@ -4766,22 +4766,22 @@
         <v>168974.88</v>
       </c>
       <c r="L10" t="n">
-        <v>9535104</v>
+        <v>9016056</v>
       </c>
       <c r="M10" t="n">
-        <v>580125</v>
+        <v>1079925</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>17850</v>
+        <v>7140</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>766195.2</v>
+        <v>86835456</v>
       </c>
     </row>
     <row r="11">
@@ -4807,7 +4807,7 @@
         <v>1760940</v>
       </c>
       <c r="H11" t="n">
-        <v>25650000</v>
+        <v>29070000</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -4819,22 +4819,22 @@
         <v>174510.26</v>
       </c>
       <c r="L11" t="n">
-        <v>16858800</v>
+        <v>17377200</v>
       </c>
       <c r="M11" t="n">
-        <v>292950</v>
+        <v>1426950</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>21675</v>
+        <v>34680</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1109732.4</v>
+        <v>125769672</v>
       </c>
     </row>
     <row r="12">
@@ -4860,7 +4860,7 @@
         <v>1527660</v>
       </c>
       <c r="H12" t="n">
-        <v>7011000</v>
+        <v>9063000</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -4872,10 +4872,10 @@
         <v>270068.47</v>
       </c>
       <c r="L12" t="n">
-        <v>11610000</v>
+        <v>13624200</v>
       </c>
       <c r="M12" t="n">
-        <v>99750</v>
+        <v>1197000</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -4887,7 +4887,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1053745.2</v>
+        <v>119424456</v>
       </c>
     </row>
     <row r="13">
@@ -4913,7 +4913,7 @@
         <v>740340</v>
       </c>
       <c r="H13" t="n">
-        <v>4788000</v>
+        <v>4446000</v>
       </c>
       <c r="I13" t="n">
         <v>184415.69</v>
@@ -4925,10 +4925,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>5632200</v>
+        <v>6750000</v>
       </c>
       <c r="M13" t="n">
-        <v>84000</v>
+        <v>1344000</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -4940,7 +4940,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>567048.6</v>
+        <v>64265508</v>
       </c>
     </row>
     <row r="14">
@@ -4966,7 +4966,7 @@
         <v>226800</v>
       </c>
       <c r="H14" t="n">
-        <v>1368000</v>
+        <v>2736000</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -4978,10 +4978,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>2305800</v>
+        <v>3288600</v>
       </c>
       <c r="M14" t="n">
-        <v>52500</v>
+        <v>1186500</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -4993,7 +4993,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>238982.4</v>
+        <v>27084672</v>
       </c>
     </row>
     <row r="15">
@@ -5019,7 +5019,7 @@
         <v>165240</v>
       </c>
       <c r="H15" t="n">
-        <v>513000</v>
+        <v>855000</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -5031,10 +5031,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>972000</v>
+        <v>2084400</v>
       </c>
       <c r="M15" t="n">
-        <v>21000</v>
+        <v>640500</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -5046,7 +5046,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>161740.8</v>
+        <v>18330624</v>
       </c>
     </row>
     <row r="16">
@@ -5072,7 +5072,7 @@
         <v>27540</v>
       </c>
       <c r="H16" t="n">
-        <v>513000</v>
+        <v>855000</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -5084,10 +5084,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>291600</v>
+        <v>696600</v>
       </c>
       <c r="M16" t="n">
-        <v>42000</v>
+        <v>262500</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -5099,7 +5099,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>71361</v>
+        <v>8087580</v>
       </c>
     </row>
     <row r="17">
@@ -5125,7 +5125,7 @@
         <v>4860</v>
       </c>
       <c r="H17" t="n">
-        <v>342000</v>
+        <v>684000</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -5137,10 +5137,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>167400</v>
+        <v>361800</v>
       </c>
       <c r="M17" t="n">
-        <v>42000</v>
+        <v>304500</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -5152,7 +5152,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>30472.2</v>
+        <v>3453516</v>
       </c>
     </row>
     <row r="18">
@@ -5190,10 +5190,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>135000</v>
+        <v>388800</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>430500</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -5205,7 +5205,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>11421</v>
+        <v>1294380</v>
       </c>
     </row>
     <row r="19">
@@ -5231,7 +5231,7 @@
         <v>3240</v>
       </c>
       <c r="H19" t="n">
-        <v>342000</v>
+        <v>684000</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -5243,10 +5243,10 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>118800</v>
+        <v>399600</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>504000</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -5258,7 +5258,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>4600.8</v>
+        <v>521424</v>
       </c>
     </row>
     <row r="20">
@@ -5296,7 +5296,7 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>10800</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -5311,7 +5311,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>1004.4</v>
+        <v>113832</v>
       </c>
     </row>
     <row r="21">
@@ -5349,7 +5349,7 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>5400</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -5364,7 +5364,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>145.8</v>
+        <v>16524</v>
       </c>
     </row>
     <row r="22">
@@ -5728,7 +5728,7 @@
         <v>41610</v>
       </c>
       <c r="H4" t="n">
-        <v>4440</v>
+        <v>6360</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -5740,22 +5740,22 @@
         <v>33</v>
       </c>
       <c r="L4" t="n">
-        <v>126180</v>
+        <v>146490</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>8790</v>
+        <v>7530</v>
       </c>
       <c r="O4" t="n">
-        <v>18900</v>
+        <v>20670</v>
       </c>
       <c r="P4" t="n">
-        <v>11130</v>
+        <v>8520</v>
       </c>
       <c r="Q4" t="n">
-        <v>22657.98</v>
+        <v>119252.52</v>
       </c>
     </row>
     <row r="5">
@@ -5781,7 +5781,7 @@
         <v>14610</v>
       </c>
       <c r="H5" t="n">
-        <v>510</v>
+        <v>1380</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -5793,22 +5793,22 @@
         <v>10</v>
       </c>
       <c r="L5" t="n">
-        <v>47730</v>
+        <v>63240</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>8640</v>
+        <v>10530</v>
       </c>
       <c r="O5" t="n">
-        <v>6390</v>
+        <v>10260</v>
       </c>
       <c r="P5" t="n">
-        <v>8580</v>
+        <v>11850</v>
       </c>
       <c r="Q5" t="n">
-        <v>9421.139999999999</v>
+        <v>49584.96</v>
       </c>
     </row>
     <row r="6">
@@ -5834,7 +5834,7 @@
         <v>1740</v>
       </c>
       <c r="H6" t="n">
-        <v>150</v>
+        <v>270</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -5846,22 +5846,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>9540</v>
+        <v>14700</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>240</v>
+        <v>630</v>
       </c>
       <c r="O6" t="n">
-        <v>360</v>
+        <v>1170</v>
       </c>
       <c r="P6" t="n">
-        <v>6090</v>
+        <v>9090</v>
       </c>
       <c r="Q6" t="n">
-        <v>827.5700000000001</v>
+        <v>4355.64</v>
       </c>
     </row>
     <row r="7">
@@ -5887,7 +5887,7 @@
         <v>480</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -5899,7 +5899,7 @@
         <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>2190</v>
+        <v>3930</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -5911,10 +5911,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>5580</v>
+        <v>8340</v>
       </c>
       <c r="Q7" t="n">
-        <v>84.95</v>
+        <v>447.12</v>
       </c>
     </row>
     <row r="8">
@@ -5952,7 +5952,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>420</v>
+        <v>1950</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -5964,10 +5964,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>5130</v>
+        <v>10200</v>
       </c>
       <c r="Q8" t="n">
-        <v>45.35</v>
+        <v>238.68</v>
       </c>
     </row>
     <row r="9">
@@ -6005,7 +6005,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>150</v>
+        <v>780</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -6017,10 +6017,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>4080</v>
+        <v>10170</v>
       </c>
       <c r="Q9" t="n">
-        <v>22.16</v>
+        <v>116.64</v>
       </c>
     </row>
     <row r="10">
@@ -6058,7 +6058,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -6070,10 +6070,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1560</v>
+        <v>4350</v>
       </c>
       <c r="Q10" t="n">
-        <v>9.44</v>
+        <v>49.68</v>
       </c>
     </row>
     <row r="11">
@@ -7073,7 +7073,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>183.6</v>
+        <v>496.8</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -7085,22 +7085,22 @@
         <v>3.31</v>
       </c>
       <c r="L5" t="n">
-        <v>10023.3</v>
+        <v>13280.4</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>86.40000000000001</v>
+        <v>105.3</v>
       </c>
       <c r="O5" t="n">
-        <v>319.5</v>
+        <v>513</v>
       </c>
       <c r="P5" t="n">
-        <v>171.6</v>
+        <v>237</v>
       </c>
       <c r="Q5" t="n">
-        <v>471.06</v>
+        <v>2479.25</v>
       </c>
     </row>
     <row r="6">
@@ -7126,7 +7126,7 @@
         <v>87</v>
       </c>
       <c r="H6" t="n">
-        <v>85.5</v>
+        <v>153.9</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -7138,22 +7138,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>3529.8</v>
+        <v>5439</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>12</v>
+        <v>31.5</v>
       </c>
       <c r="O6" t="n">
-        <v>90</v>
+        <v>292.5</v>
       </c>
       <c r="P6" t="n">
-        <v>913.5</v>
+        <v>1363.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>620.6799999999999</v>
+        <v>3266.73</v>
       </c>
     </row>
     <row r="7">
@@ -7179,7 +7179,7 @@
         <v>72</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>109.5</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -7191,7 +7191,7 @@
         <v>0.64</v>
       </c>
       <c r="L7" t="n">
-        <v>1314</v>
+        <v>2358</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -7203,10 +7203,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1395</v>
+        <v>2085</v>
       </c>
       <c r="Q7" t="n">
-        <v>67.95999999999999</v>
+        <v>357.7</v>
       </c>
     </row>
     <row r="8">
@@ -7244,7 +7244,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>298.2</v>
+        <v>1384.5</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -7256,10 +7256,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1949.4</v>
+        <v>3876</v>
       </c>
       <c r="Q8" t="n">
-        <v>43.08</v>
+        <v>226.75</v>
       </c>
     </row>
     <row r="9">
@@ -7297,7 +7297,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>121.5</v>
+        <v>631.8</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -7309,10 +7309,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2040</v>
+        <v>5085</v>
       </c>
       <c r="Q9" t="n">
-        <v>21.5</v>
+        <v>113.14</v>
       </c>
     </row>
     <row r="10">
@@ -7350,7 +7350,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>106.8</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -7362,10 +7362,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1326</v>
+        <v>3697.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>9.44</v>
+        <v>49.68</v>
       </c>
     </row>
     <row r="11">
@@ -8365,7 +8365,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1046520</v>
+        <v>2831760</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -8377,22 +8377,22 @@
         <v>160720.36</v>
       </c>
       <c r="L5" t="n">
-        <v>1804194</v>
+        <v>2390472</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>14688</v>
+        <v>17901</v>
       </c>
       <c r="O5" t="n">
-        <v>54315</v>
+        <v>87210</v>
       </c>
       <c r="P5" t="n">
-        <v>11154</v>
+        <v>15405</v>
       </c>
       <c r="Q5" t="n">
-        <v>282634.27</v>
+        <v>1487548.8</v>
       </c>
     </row>
     <row r="6">
@@ -8418,7 +8418,7 @@
         <v>4698</v>
       </c>
       <c r="H6" t="n">
-        <v>487350</v>
+        <v>877230</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -8430,22 +8430,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>635364</v>
+        <v>979020</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2040</v>
+        <v>5355</v>
       </c>
       <c r="O6" t="n">
-        <v>15300</v>
+        <v>49725</v>
       </c>
       <c r="P6" t="n">
-        <v>59377.5</v>
+        <v>88627.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>372407.22</v>
+        <v>1960038</v>
       </c>
     </row>
     <row r="7">
@@ -8471,7 +8471,7 @@
         <v>3888</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>624150</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -8483,7 +8483,7 @@
         <v>30978.73</v>
       </c>
       <c r="L7" t="n">
-        <v>236520</v>
+        <v>424440</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -8495,10 +8495,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>90675</v>
+        <v>135525</v>
       </c>
       <c r="Q7" t="n">
-        <v>40777.34</v>
+        <v>214617.6</v>
       </c>
     </row>
     <row r="8">
@@ -8536,7 +8536,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>53676</v>
+        <v>249210</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -8548,10 +8548,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>126711</v>
+        <v>251940</v>
       </c>
       <c r="Q8" t="n">
-        <v>25849.04</v>
+        <v>136047.6</v>
       </c>
     </row>
     <row r="9">
@@ -8589,7 +8589,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>21870</v>
+        <v>113724</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -8601,10 +8601,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>132600</v>
+        <v>330525</v>
       </c>
       <c r="Q9" t="n">
-        <v>12898.05</v>
+        <v>67884.48</v>
       </c>
     </row>
     <row r="10">
@@ -8642,7 +8642,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>19224</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -8654,10 +8654,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>86190</v>
+        <v>240337.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>5663.52</v>
+        <v>29808</v>
       </c>
     </row>
     <row r="11">
@@ -9604,7 +9604,7 @@
         <v>72180</v>
       </c>
       <c r="H4" t="n">
-        <v>4650</v>
+        <v>4740</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -9616,22 +9616,22 @@
         <v>26</v>
       </c>
       <c r="L4" t="n">
-        <v>107280</v>
+        <v>128730</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>18900</v>
+        <v>21630</v>
       </c>
       <c r="O4" t="n">
-        <v>31620</v>
+        <v>31920</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>28202.78</v>
+        <v>153038.34</v>
       </c>
     </row>
     <row r="5">
@@ -9657,7 +9657,7 @@
         <v>19050</v>
       </c>
       <c r="H5" t="n">
-        <v>3060</v>
+        <v>3780</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -9669,22 +9669,22 @@
         <v>5</v>
       </c>
       <c r="L5" t="n">
-        <v>34710</v>
+        <v>42540</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>7650</v>
+        <v>8850</v>
       </c>
       <c r="O5" t="n">
-        <v>26340</v>
+        <v>26610</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>6326.06</v>
+        <v>34327.44</v>
       </c>
     </row>
     <row r="6">
@@ -9710,7 +9710,7 @@
         <v>6270</v>
       </c>
       <c r="H6" t="n">
-        <v>1140</v>
+        <v>1650</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -9722,22 +9722,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>8700</v>
+        <v>14400</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3600</v>
+        <v>4290</v>
       </c>
       <c r="O6" t="n">
-        <v>21660</v>
+        <v>23580</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>907.21</v>
+        <v>4922.82</v>
       </c>
     </row>
     <row r="7">
@@ -9763,7 +9763,7 @@
         <v>2040</v>
       </c>
       <c r="H7" t="n">
-        <v>180</v>
+        <v>480</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -9775,22 +9775,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>3210</v>
+        <v>5040</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>1110</v>
+        <v>2520</v>
       </c>
       <c r="O7" t="n">
-        <v>9180</v>
+        <v>11280</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>236.5</v>
+        <v>1283.31</v>
       </c>
     </row>
     <row r="8">
@@ -9816,7 +9816,7 @@
         <v>390</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -9828,22 +9828,22 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>1320</v>
+        <v>2400</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>90</v>
+        <v>330</v>
       </c>
       <c r="O8" t="n">
-        <v>2070</v>
+        <v>4290</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>80.45999999999999</v>
+        <v>436.59</v>
       </c>
     </row>
     <row r="9">
@@ -9890,13 +9890,13 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>360</v>
+        <v>810</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.25</v>
+        <v>17.64</v>
       </c>
     </row>
     <row r="10">
@@ -10949,7 +10949,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1101.6</v>
+        <v>1360.8</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -10961,22 +10961,22 @@
         <v>1.66</v>
       </c>
       <c r="L5" t="n">
-        <v>7289.1</v>
+        <v>8933.4</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>76.5</v>
+        <v>88.5</v>
       </c>
       <c r="O5" t="n">
-        <v>1317</v>
+        <v>1330.5</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>316.3</v>
+        <v>1716.37</v>
       </c>
     </row>
     <row r="6">
@@ -11002,7 +11002,7 @@
         <v>313.5</v>
       </c>
       <c r="H6" t="n">
-        <v>649.8</v>
+        <v>940.5</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -11014,22 +11014,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>3219</v>
+        <v>5328</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>180</v>
+        <v>214.5</v>
       </c>
       <c r="O6" t="n">
-        <v>5415</v>
+        <v>5895</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>680.4</v>
+        <v>3692.12</v>
       </c>
     </row>
     <row r="7">
@@ -11055,7 +11055,7 @@
         <v>306</v>
       </c>
       <c r="H7" t="n">
-        <v>131.4</v>
+        <v>350.4</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -11067,22 +11067,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1926</v>
+        <v>3024</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>77.7</v>
+        <v>176.4</v>
       </c>
       <c r="O7" t="n">
-        <v>3213</v>
+        <v>3948</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>189.2</v>
+        <v>1026.65</v>
       </c>
     </row>
     <row r="8">
@@ -11108,7 +11108,7 @@
         <v>253.5</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -11120,22 +11120,22 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>937.2</v>
+        <v>1704</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>18</v>
+        <v>66</v>
       </c>
       <c r="O8" t="n">
-        <v>931.5</v>
+        <v>1930.5</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>76.43000000000001</v>
+        <v>414.76</v>
       </c>
     </row>
     <row r="9">
@@ -11182,13 +11182,13 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>198</v>
+        <v>445.5</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.15</v>
+        <v>17.11</v>
       </c>
     </row>
     <row r="10">
@@ -12241,7 +12241,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>6279120</v>
+        <v>7756560</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -12253,22 +12253,22 @@
         <v>80360.17999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>1312038</v>
+        <v>1608012</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>13005</v>
+        <v>15045</v>
       </c>
       <c r="O5" t="n">
-        <v>223890</v>
+        <v>226185</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>189781.7</v>
+        <v>1029823.2</v>
       </c>
     </row>
     <row r="6">
@@ -12294,7 +12294,7 @@
         <v>16929</v>
       </c>
       <c r="H6" t="n">
-        <v>3703860</v>
+        <v>5360850</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -12306,22 +12306,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>579420</v>
+        <v>959040</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>30600</v>
+        <v>36465</v>
       </c>
       <c r="O6" t="n">
-        <v>920550</v>
+        <v>1002150</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>408242.43</v>
+        <v>2215269</v>
       </c>
     </row>
     <row r="7">
@@ -12347,7 +12347,7 @@
         <v>16524</v>
       </c>
       <c r="H7" t="n">
-        <v>748980</v>
+        <v>1997280</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -12359,22 +12359,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>346680</v>
+        <v>544320</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>13209</v>
+        <v>29988</v>
       </c>
       <c r="O7" t="n">
-        <v>546210</v>
+        <v>671160</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>113517.94</v>
+        <v>615988.8</v>
       </c>
     </row>
     <row r="8">
@@ -12400,7 +12400,7 @@
         <v>13689</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>290700</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -12412,22 +12412,22 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>168696</v>
+        <v>306720</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3060</v>
+        <v>11220</v>
       </c>
       <c r="O8" t="n">
-        <v>158355</v>
+        <v>328185</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>45860.66</v>
+        <v>248856.3</v>
       </c>
     </row>
     <row r="9">
@@ -12474,13 +12474,13 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>33660</v>
+        <v>75735</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1891.97</v>
+        <v>10266.48</v>
       </c>
     </row>
     <row r="10">
@@ -13480,7 +13480,7 @@
         <v>81480</v>
       </c>
       <c r="H4" t="n">
-        <v>8880</v>
+        <v>9840</v>
       </c>
       <c r="I4" t="n">
         <v>5</v>
@@ -13492,19 +13492,19 @@
         <v>133</v>
       </c>
       <c r="L4" t="n">
-        <v>194130</v>
+        <v>192870</v>
       </c>
       <c r="M4" t="n">
-        <v>16830</v>
+        <v>780</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>37530</v>
+        <v>40920</v>
       </c>
       <c r="P4" t="n">
-        <v>23340</v>
+        <v>4650</v>
       </c>
       <c r="Q4" t="n">
         <v>34484.18</v>
@@ -13533,7 +13533,7 @@
         <v>86400</v>
       </c>
       <c r="H5" t="n">
-        <v>7440</v>
+        <v>8070</v>
       </c>
       <c r="I5" t="n">
         <v>3</v>
@@ -13545,19 +13545,19 @@
         <v>87</v>
       </c>
       <c r="L5" t="n">
-        <v>193380</v>
+        <v>180960</v>
       </c>
       <c r="M5" t="n">
-        <v>18690</v>
+        <v>1800</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>31050</v>
+        <v>38340</v>
       </c>
       <c r="P5" t="n">
-        <v>34620</v>
+        <v>15570</v>
       </c>
       <c r="Q5" t="n">
         <v>36589.73</v>
@@ -13586,7 +13586,7 @@
         <v>84660</v>
       </c>
       <c r="H6" t="n">
-        <v>12180</v>
+        <v>12630</v>
       </c>
       <c r="I6" t="n">
         <v>1</v>
@@ -13598,19 +13598,19 @@
         <v>84</v>
       </c>
       <c r="L6" t="n">
-        <v>208650</v>
+        <v>192750</v>
       </c>
       <c r="M6" t="n">
-        <v>11160</v>
+        <v>3930</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>24030</v>
+        <v>22200</v>
       </c>
       <c r="P6" t="n">
-        <v>34860</v>
+        <v>22470</v>
       </c>
       <c r="Q6" t="n">
         <v>43169.78</v>
@@ -13639,7 +13639,7 @@
         <v>66630</v>
       </c>
       <c r="H7" t="n">
-        <v>4500</v>
+        <v>4770</v>
       </c>
       <c r="I7" t="n">
         <v>3</v>
@@ -13651,19 +13651,19 @@
         <v>43</v>
       </c>
       <c r="L7" t="n">
-        <v>137640</v>
+        <v>128850</v>
       </c>
       <c r="M7" t="n">
-        <v>6990</v>
+        <v>5250</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>20940</v>
+        <v>22650</v>
       </c>
       <c r="P7" t="n">
-        <v>36120</v>
+        <v>28770</v>
       </c>
       <c r="Q7" t="n">
         <v>35456.1</v>
@@ -13692,7 +13692,7 @@
         <v>40140</v>
       </c>
       <c r="H8" t="n">
-        <v>600</v>
+        <v>780</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -13704,19 +13704,19 @@
         <v>33</v>
       </c>
       <c r="L8" t="n">
-        <v>84090</v>
+        <v>90060</v>
       </c>
       <c r="M8" t="n">
-        <v>3690</v>
+        <v>10560</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>27840</v>
+        <v>26730</v>
       </c>
       <c r="P8" t="n">
-        <v>32280</v>
+        <v>33180</v>
       </c>
       <c r="Q8" t="n">
         <v>29448.34</v>
@@ -13745,7 +13745,7 @@
         <v>21750</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -13757,19 +13757,19 @@
         <v>10</v>
       </c>
       <c r="L9" t="n">
-        <v>43200</v>
+        <v>51210</v>
       </c>
       <c r="M9" t="n">
-        <v>2190</v>
+        <v>12630</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>11580</v>
+        <v>16980</v>
       </c>
       <c r="P9" t="n">
-        <v>35370</v>
+        <v>35760</v>
       </c>
       <c r="Q9" t="n">
         <v>17973.29</v>
@@ -13810,19 +13810,19 @@
         <v>2</v>
       </c>
       <c r="L10" t="n">
+        <v>22620</v>
+      </c>
+      <c r="M10" t="n">
         <v>10680</v>
       </c>
-      <c r="M10" t="n">
-        <v>990</v>
-      </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>990</v>
+        <v>2340</v>
       </c>
       <c r="P10" t="n">
-        <v>38670</v>
+        <v>43380</v>
       </c>
       <c r="Q10" t="n">
         <v>2223.96</v>
@@ -13863,10 +13863,10 @@
         <v>2</v>
       </c>
       <c r="L11" t="n">
-        <v>4620</v>
+        <v>29550</v>
       </c>
       <c r="M11" t="n">
-        <v>330</v>
+        <v>10590</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -13875,7 +13875,7 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>31680</v>
+        <v>47700</v>
       </c>
       <c r="Q11" t="n">
         <v>369.95</v>
@@ -13904,7 +13904,7 @@
         <v>240</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -13916,19 +13916,19 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>3450</v>
+        <v>25170</v>
       </c>
       <c r="M12" t="n">
-        <v>240</v>
+        <v>5880</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="P12" t="n">
-        <v>25890</v>
+        <v>46140</v>
       </c>
       <c r="Q12" t="n">
         <v>238.71</v>
@@ -13969,10 +13969,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1440</v>
+        <v>11730</v>
       </c>
       <c r="M13" t="n">
-        <v>150</v>
+        <v>9750</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -13981,7 +13981,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>16080</v>
+        <v>30510</v>
       </c>
       <c r="Q13" t="n">
         <v>140.06</v>
@@ -14022,10 +14022,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>480</v>
+        <v>3450</v>
       </c>
       <c r="M14" t="n">
-        <v>30</v>
+        <v>960</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -14034,7 +14034,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>10680</v>
+        <v>9780</v>
       </c>
       <c r="Q14" t="n">
         <v>16.96</v>
@@ -14075,10 +14075,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>390</v>
+        <v>6150</v>
       </c>
       <c r="M15" t="n">
-        <v>30</v>
+        <v>540</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -14087,7 +14087,7 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>12120</v>
+        <v>20730</v>
       </c>
       <c r="Q15" t="n">
         <v>21.65</v>
@@ -14128,10 +14128,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>300</v>
+        <v>2790</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -14140,7 +14140,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>11460</v>
+        <v>26100</v>
       </c>
       <c r="Q16" t="n">
         <v>13.28</v>
@@ -14181,10 +14181,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>300</v>
+        <v>2850</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -14193,7 +14193,7 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>3780</v>
+        <v>8520</v>
       </c>
       <c r="Q17" t="n">
         <v>6.36</v>
@@ -14234,7 +14234,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>660</v>
+        <v>1200</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -14246,7 +14246,7 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>720</v>
+        <v>1290</v>
       </c>
       <c r="Q18" t="n">
         <v>2.12</v>
@@ -14287,7 +14287,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>120</v>
+        <v>480</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -14825,7 +14825,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>17550</v>
+        <v>20239.2</v>
       </c>
       <c r="I5" t="n">
         <v>0.99</v>
@@ -14837,22 +14837,22 @@
         <v>76.79000000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>179203.5</v>
+        <v>187992</v>
       </c>
       <c r="M5" t="n">
-        <v>1009.8</v>
+        <v>642.6</v>
       </c>
       <c r="N5" t="n">
-        <v>608.4</v>
+        <v>746.1</v>
       </c>
       <c r="O5" t="n">
-        <v>8391</v>
+        <v>9651</v>
       </c>
       <c r="P5" t="n">
-        <v>1185</v>
+        <v>762.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>6826.97</v>
+        <v>70747.21000000001</v>
       </c>
     </row>
     <row r="6">
@@ -14878,7 +14878,7 @@
         <v>12465</v>
       </c>
       <c r="H6" t="n">
-        <v>32113.8</v>
+        <v>32233.5</v>
       </c>
       <c r="I6" t="n">
         <v>0.51</v>
@@ -14890,22 +14890,22 @@
         <v>87.70999999999999</v>
       </c>
       <c r="L6" t="n">
-        <v>234942.6</v>
+        <v>235586.4</v>
       </c>
       <c r="M6" t="n">
-        <v>2450.4</v>
+        <v>2112</v>
       </c>
       <c r="N6" t="n">
-        <v>781.5</v>
+        <v>1263</v>
       </c>
       <c r="O6" t="n">
-        <v>27322.5</v>
+        <v>29460</v>
       </c>
       <c r="P6" t="n">
-        <v>8995.5</v>
+        <v>6511.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>79975.52</v>
+        <v>828778.55</v>
       </c>
     </row>
     <row r="7">
@@ -14931,7 +14931,7 @@
         <v>30712.5</v>
       </c>
       <c r="H7" t="n">
-        <v>21943.8</v>
+        <v>23279.7</v>
       </c>
       <c r="I7" t="n">
         <v>2.55</v>
@@ -14943,22 +14943,22 @@
         <v>70.18000000000001</v>
       </c>
       <c r="L7" t="n">
-        <v>302220</v>
+        <v>305190</v>
       </c>
       <c r="M7" t="n">
-        <v>7329</v>
+        <v>9544.5</v>
       </c>
       <c r="N7" t="n">
-        <v>264.6</v>
+        <v>543.9</v>
       </c>
       <c r="O7" t="n">
-        <v>25777.5</v>
+        <v>28959</v>
       </c>
       <c r="P7" t="n">
-        <v>17565</v>
+        <v>13440</v>
       </c>
       <c r="Q7" t="n">
-        <v>71686.03999999999</v>
+        <v>742875.46</v>
       </c>
     </row>
     <row r="8">
@@ -14984,7 +14984,7 @@
         <v>107620.5</v>
       </c>
       <c r="H8" t="n">
-        <v>6834</v>
+        <v>9180</v>
       </c>
       <c r="I8" t="n">
         <v>0.74</v>
@@ -14996,22 +14996,22 @@
         <v>76.54000000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>282331.5</v>
+        <v>293471.4</v>
       </c>
       <c r="M8" t="n">
-        <v>7293</v>
+        <v>17193</v>
       </c>
       <c r="N8" t="n">
-        <v>18</v>
+        <v>84</v>
       </c>
       <c r="O8" t="n">
-        <v>27891</v>
+        <v>31144.5</v>
       </c>
       <c r="P8" t="n">
-        <v>26402.4</v>
+        <v>24350.4</v>
       </c>
       <c r="Q8" t="n">
-        <v>73569.82000000001</v>
+        <v>762396.95</v>
       </c>
     </row>
     <row r="9">
@@ -15037,7 +15037,7 @@
         <v>115413</v>
       </c>
       <c r="H9" t="n">
-        <v>3870</v>
+        <v>4230</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -15049,22 +15049,22 @@
         <v>52.2</v>
       </c>
       <c r="L9" t="n">
-        <v>235880.1</v>
+        <v>263752.2</v>
       </c>
       <c r="M9" t="n">
-        <v>7308</v>
+        <v>21693</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>20955</v>
+        <v>29535</v>
       </c>
       <c r="P9" t="n">
-        <v>36345</v>
+        <v>35070</v>
       </c>
       <c r="Q9" t="n">
-        <v>61888.64</v>
+        <v>641346.01</v>
       </c>
     </row>
     <row r="10">
@@ -15090,7 +15090,7 @@
         <v>80220</v>
       </c>
       <c r="H10" t="n">
-        <v>4890</v>
+        <v>4620</v>
       </c>
       <c r="I10" t="n">
         <v>2.61</v>
@@ -15102,22 +15102,22 @@
         <v>33.93</v>
       </c>
       <c r="L10" t="n">
-        <v>158598</v>
+        <v>186419.4</v>
       </c>
       <c r="M10" t="n">
-        <v>5814</v>
+        <v>22210.5</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>8715</v>
+        <v>16485</v>
       </c>
       <c r="P10" t="n">
-        <v>69462</v>
+        <v>77239.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>39063.57</v>
+        <v>404812.01</v>
       </c>
     </row>
     <row r="11">
@@ -15143,7 +15143,7 @@
         <v>59970</v>
       </c>
       <c r="H11" t="n">
-        <v>4560</v>
+        <v>5490</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -15155,22 +15155,22 @@
         <v>13.48</v>
       </c>
       <c r="L11" t="n">
-        <v>162570</v>
+        <v>207420</v>
       </c>
       <c r="M11" t="n">
-        <v>3294</v>
+        <v>23760</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>4360.5</v>
+        <v>12699</v>
       </c>
       <c r="P11" t="n">
-        <v>59454</v>
+        <v>92178</v>
       </c>
       <c r="Q11" t="n">
-        <v>28410.57</v>
+        <v>294415.99</v>
       </c>
     </row>
     <row r="12">
@@ -15196,7 +15196,7 @@
         <v>47610</v>
       </c>
       <c r="H12" t="n">
-        <v>1260</v>
+        <v>1830</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -15208,22 +15208,22 @@
         <v>6.49</v>
       </c>
       <c r="L12" t="n">
-        <v>96930</v>
+        <v>143130</v>
       </c>
       <c r="M12" t="n">
-        <v>2707.5</v>
+        <v>15532.5</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>2370</v>
+        <v>3930</v>
       </c>
       <c r="P12" t="n">
-        <v>48030</v>
+        <v>81780</v>
       </c>
       <c r="Q12" t="n">
-        <v>19338.16</v>
+        <v>200399.48</v>
       </c>
     </row>
     <row r="13">
@@ -15249,7 +15249,7 @@
         <v>23430</v>
       </c>
       <c r="H13" t="n">
-        <v>840</v>
+        <v>780</v>
       </c>
       <c r="I13" t="n">
         <v>0.95</v>
@@ -15261,10 +15261,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>42900</v>
+        <v>64980</v>
       </c>
       <c r="M13" t="n">
-        <v>1410</v>
+        <v>20580</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -15273,10 +15273,10 @@
         <v>3600</v>
       </c>
       <c r="P13" t="n">
-        <v>33420</v>
+        <v>52200</v>
       </c>
       <c r="Q13" t="n">
-        <v>9795.690000000001</v>
+        <v>101511.79</v>
       </c>
     </row>
     <row r="14">
@@ -15302,7 +15302,7 @@
         <v>5970</v>
       </c>
       <c r="H14" t="n">
-        <v>240</v>
+        <v>480</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -15314,22 +15314,22 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>16410</v>
+        <v>30450</v>
       </c>
       <c r="M14" t="n">
-        <v>300</v>
+        <v>6540</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>630</v>
+        <v>990</v>
       </c>
       <c r="P14" t="n">
-        <v>28770</v>
+        <v>29790</v>
       </c>
       <c r="Q14" t="n">
-        <v>3832.57</v>
+        <v>39716.52</v>
       </c>
     </row>
     <row r="15">
@@ -15355,7 +15355,7 @@
         <v>4020</v>
       </c>
       <c r="H15" t="n">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -15367,22 +15367,22 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>6780</v>
+        <v>23370</v>
       </c>
       <c r="M15" t="n">
+        <v>3180</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
         <v>150</v>
       </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>30</v>
-      </c>
       <c r="P15" t="n">
-        <v>38970</v>
+        <v>55170</v>
       </c>
       <c r="Q15" t="n">
-        <v>2205.55</v>
+        <v>22855.91</v>
       </c>
     </row>
     <row r="16">
@@ -15408,7 +15408,7 @@
         <v>1170</v>
       </c>
       <c r="H16" t="n">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -15420,10 +15420,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>2160</v>
+        <v>9450</v>
       </c>
       <c r="M16" t="n">
-        <v>210</v>
+        <v>1530</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -15432,10 +15432,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>25500</v>
+        <v>42780</v>
       </c>
       <c r="Q16" t="n">
-        <v>1220.68</v>
+        <v>12649.8</v>
       </c>
     </row>
     <row r="17">
@@ -15461,7 +15461,7 @@
         <v>240</v>
       </c>
       <c r="H17" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -15473,10 +15473,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>1440</v>
+        <v>6210</v>
       </c>
       <c r="M17" t="n">
-        <v>150</v>
+        <v>990</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -15485,10 +15485,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>17010</v>
+        <v>23460</v>
       </c>
       <c r="Q17" t="n">
-        <v>520.0599999999999</v>
+        <v>5389.29</v>
       </c>
     </row>
     <row r="18">
@@ -15526,22 +15526,22 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>1530</v>
+        <v>4920</v>
       </c>
       <c r="M18" t="n">
-        <v>120</v>
+        <v>1320</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="P18" t="n">
-        <v>18120</v>
+        <v>24090</v>
       </c>
       <c r="Q18" t="n">
-        <v>251.66</v>
+        <v>2607.91</v>
       </c>
     </row>
     <row r="19">
@@ -15567,7 +15567,7 @@
         <v>3780</v>
       </c>
       <c r="H19" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -15579,10 +15579,10 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>780</v>
+        <v>2790</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>1530</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -15591,10 +15591,10 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>6870</v>
+        <v>18030</v>
       </c>
       <c r="Q19" t="n">
-        <v>106.13</v>
+        <v>1099.83</v>
       </c>
     </row>
     <row r="20">
@@ -15632,7 +15632,7 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -15644,10 +15644,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="Q20" t="n">
-        <v>16.29</v>
+        <v>168.85</v>
       </c>
     </row>
     <row r="21">
@@ -15685,7 +15685,7 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -15700,7 +15700,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.79</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="22">
@@ -16117,7 +16117,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>2678.4</v>
+        <v>2905.2</v>
       </c>
       <c r="I5" t="n">
         <v>0.99</v>
@@ -16129,19 +16129,19 @@
         <v>28.8</v>
       </c>
       <c r="L5" t="n">
-        <v>40609.8</v>
+        <v>38001.6</v>
       </c>
       <c r="M5" t="n">
-        <v>373.8</v>
+        <v>36</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>1552.5</v>
+        <v>1917</v>
       </c>
       <c r="P5" t="n">
-        <v>692.4</v>
+        <v>311.4</v>
       </c>
       <c r="Q5" t="n">
         <v>1829.49</v>
@@ -16170,7 +16170,7 @@
         <v>4233</v>
       </c>
       <c r="H6" t="n">
-        <v>6942.6</v>
+        <v>7199.1</v>
       </c>
       <c r="I6" t="n">
         <v>0.51</v>
@@ -16182,19 +16182,19 @@
         <v>42.59</v>
       </c>
       <c r="L6" t="n">
-        <v>77200.5</v>
+        <v>71317.5</v>
       </c>
       <c r="M6" t="n">
-        <v>892.8</v>
+        <v>314.4</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>6007.5</v>
+        <v>5550</v>
       </c>
       <c r="P6" t="n">
-        <v>5229</v>
+        <v>3370.5</v>
       </c>
       <c r="Q6" t="n">
         <v>32377.34</v>
@@ -16223,7 +16223,7 @@
         <v>9994.5</v>
       </c>
       <c r="H7" t="n">
-        <v>3285</v>
+        <v>3482.1</v>
       </c>
       <c r="I7" t="n">
         <v>1.91</v>
@@ -16235,19 +16235,19 @@
         <v>27.43</v>
       </c>
       <c r="L7" t="n">
-        <v>82584</v>
+        <v>77310</v>
       </c>
       <c r="M7" t="n">
-        <v>2446.5</v>
+        <v>1837.5</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>7329</v>
+        <v>7927.5</v>
       </c>
       <c r="P7" t="n">
-        <v>9030</v>
+        <v>7192.5</v>
       </c>
       <c r="Q7" t="n">
         <v>28364.88</v>
@@ -16276,7 +16276,7 @@
         <v>26091</v>
       </c>
       <c r="H8" t="n">
-        <v>510</v>
+        <v>663</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -16288,19 +16288,19 @@
         <v>24.29</v>
       </c>
       <c r="L8" t="n">
-        <v>59703.9</v>
+        <v>63942.6</v>
       </c>
       <c r="M8" t="n">
-        <v>2029.5</v>
+        <v>5808</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>12528</v>
+        <v>12028.5</v>
       </c>
       <c r="P8" t="n">
-        <v>12266.4</v>
+        <v>12608.4</v>
       </c>
       <c r="Q8" t="n">
         <v>27975.92</v>
@@ -16329,7 +16329,7 @@
         <v>18487.5</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -16341,19 +16341,19 @@
         <v>8.029999999999999</v>
       </c>
       <c r="L9" t="n">
-        <v>34992</v>
+        <v>41480.1</v>
       </c>
       <c r="M9" t="n">
-        <v>1533</v>
+        <v>8841</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>6369</v>
+        <v>9339</v>
       </c>
       <c r="P9" t="n">
-        <v>17685</v>
+        <v>17880</v>
       </c>
       <c r="Q9" t="n">
         <v>17434.09</v>
@@ -16394,19 +16394,19 @@
         <v>1.74</v>
       </c>
       <c r="L10" t="n">
-        <v>9505.200000000001</v>
+        <v>20131.8</v>
       </c>
       <c r="M10" t="n">
-        <v>841.5</v>
+        <v>9078</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>693</v>
+        <v>1638</v>
       </c>
       <c r="P10" t="n">
-        <v>32869.5</v>
+        <v>36873</v>
       </c>
       <c r="Q10" t="n">
         <v>2223.96</v>
@@ -16447,10 +16447,10 @@
         <v>1.8</v>
       </c>
       <c r="L11" t="n">
-        <v>4620</v>
+        <v>29550</v>
       </c>
       <c r="M11" t="n">
-        <v>297</v>
+        <v>9531</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -16459,7 +16459,7 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>28512</v>
+        <v>42930</v>
       </c>
       <c r="Q11" t="n">
         <v>369.95</v>
@@ -16488,7 +16488,7 @@
         <v>240</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -16500,19 +16500,19 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>3450</v>
+        <v>25170</v>
       </c>
       <c r="M12" t="n">
-        <v>228</v>
+        <v>5586</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="P12" t="n">
-        <v>25890</v>
+        <v>46140</v>
       </c>
       <c r="Q12" t="n">
         <v>238.71</v>
@@ -16553,10 +16553,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1440</v>
+        <v>11730</v>
       </c>
       <c r="M13" t="n">
-        <v>150</v>
+        <v>9750</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -16565,7 +16565,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>16080</v>
+        <v>30510</v>
       </c>
       <c r="Q13" t="n">
         <v>140.06</v>
@@ -16606,10 +16606,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>480</v>
+        <v>3450</v>
       </c>
       <c r="M14" t="n">
-        <v>30</v>
+        <v>960</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -16618,7 +16618,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>10680</v>
+        <v>9780</v>
       </c>
       <c r="Q14" t="n">
         <v>16.96</v>
@@ -16659,10 +16659,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>390</v>
+        <v>6150</v>
       </c>
       <c r="M15" t="n">
-        <v>30</v>
+        <v>540</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -16671,7 +16671,7 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>12120</v>
+        <v>20730</v>
       </c>
       <c r="Q15" t="n">
         <v>21.65</v>
@@ -16712,10 +16712,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>300</v>
+        <v>2790</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -16724,7 +16724,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>11460</v>
+        <v>26100</v>
       </c>
       <c r="Q16" t="n">
         <v>13.28</v>
@@ -16765,10 +16765,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>300</v>
+        <v>2850</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -16777,7 +16777,7 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>3780</v>
+        <v>8520</v>
       </c>
       <c r="Q17" t="n">
         <v>6.36</v>
@@ -16818,7 +16818,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>660</v>
+        <v>1200</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -16830,7 +16830,7 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>720</v>
+        <v>1290</v>
       </c>
       <c r="Q18" t="n">
         <v>2.12</v>
@@ -16871,7 +16871,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>120</v>
+        <v>480</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -17409,7 +17409,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>15266880</v>
+        <v>16559640</v>
       </c>
       <c r="I5" t="n">
         <v>192864.43</v>
@@ -17421,19 +17421,19 @@
         <v>1398267.13</v>
       </c>
       <c r="L5" t="n">
-        <v>7309764</v>
+        <v>6840288</v>
       </c>
       <c r="M5" t="n">
-        <v>130830</v>
+        <v>12600</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>263925</v>
+        <v>325890</v>
       </c>
       <c r="P5" t="n">
-        <v>45006</v>
+        <v>20241</v>
       </c>
       <c r="Q5" t="n">
         <v>1097692.02</v>
@@ -17462,7 +17462,7 @@
         <v>228582</v>
       </c>
       <c r="H6" t="n">
-        <v>39572820</v>
+        <v>41034870</v>
       </c>
       <c r="I6" t="n">
         <v>98471.57000000001</v>
@@ -17474,19 +17474,19 @@
         <v>2067902.93</v>
       </c>
       <c r="L6" t="n">
-        <v>13896090</v>
+        <v>12837150</v>
       </c>
       <c r="M6" t="n">
-        <v>312480</v>
+        <v>110040</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>1021275</v>
+        <v>943500</v>
       </c>
       <c r="P6" t="n">
-        <v>339885</v>
+        <v>219082.5</v>
       </c>
       <c r="Q6" t="n">
         <v>19426401.72</v>
@@ -17515,7 +17515,7 @@
         <v>539703</v>
       </c>
       <c r="H7" t="n">
-        <v>18724500</v>
+        <v>19847970</v>
       </c>
       <c r="I7" t="n">
         <v>371744.74</v>
@@ -17527,19 +17527,19 @@
         <v>1332085.3</v>
       </c>
       <c r="L7" t="n">
-        <v>14865120</v>
+        <v>13915800</v>
       </c>
       <c r="M7" t="n">
-        <v>856275</v>
+        <v>643125</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>1245930</v>
+        <v>1347675</v>
       </c>
       <c r="P7" t="n">
-        <v>586950</v>
+        <v>467512.5</v>
       </c>
       <c r="Q7" t="n">
         <v>17018928.58</v>
@@ -17568,7 +17568,7 @@
         <v>1408914</v>
       </c>
       <c r="H8" t="n">
-        <v>2907000</v>
+        <v>3779100</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -17580,19 +17580,19 @@
         <v>1179328.13</v>
       </c>
       <c r="L8" t="n">
-        <v>10746702</v>
+        <v>11509668</v>
       </c>
       <c r="M8" t="n">
-        <v>710325</v>
+        <v>2032800</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2129760</v>
+        <v>2044845</v>
       </c>
       <c r="P8" t="n">
-        <v>797316</v>
+        <v>819546</v>
       </c>
       <c r="Q8" t="n">
         <v>16785552.89</v>
@@ -17621,7 +17621,7 @@
         <v>998325</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>855000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -17633,19 +17633,19 @@
         <v>389904.68</v>
       </c>
       <c r="L9" t="n">
-        <v>6298560</v>
+        <v>7466418</v>
       </c>
       <c r="M9" t="n">
-        <v>536550</v>
+        <v>3094350</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>1082730</v>
+        <v>1587630</v>
       </c>
       <c r="P9" t="n">
-        <v>1149525</v>
+        <v>1162200</v>
       </c>
       <c r="Q9" t="n">
         <v>10460455.71</v>
@@ -17686,19 +17686,19 @@
         <v>84487.44</v>
       </c>
       <c r="L10" t="n">
-        <v>1710936</v>
+        <v>3623724</v>
       </c>
       <c r="M10" t="n">
-        <v>294525</v>
+        <v>3177300</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>117810</v>
+        <v>278460</v>
       </c>
       <c r="P10" t="n">
-        <v>2136517.5</v>
+        <v>2396745</v>
       </c>
       <c r="Q10" t="n">
         <v>1334378.88</v>
@@ -17739,10 +17739,10 @@
         <v>87255.13</v>
       </c>
       <c r="L11" t="n">
-        <v>831600</v>
+        <v>5319000</v>
       </c>
       <c r="M11" t="n">
-        <v>103950</v>
+        <v>3335850</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -17751,7 +17751,7 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1853280</v>
+        <v>2790450</v>
       </c>
       <c r="Q11" t="n">
         <v>221972.4</v>
@@ -17780,7 +17780,7 @@
         <v>12960</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>513000</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -17792,19 +17792,19 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>621000</v>
+        <v>4530600</v>
       </c>
       <c r="M12" t="n">
-        <v>79800</v>
+        <v>1955100</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>5100</v>
       </c>
       <c r="P12" t="n">
-        <v>1682850</v>
+        <v>2999100</v>
       </c>
       <c r="Q12" t="n">
         <v>143227.44</v>
@@ -17845,10 +17845,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>259200</v>
+        <v>2111400</v>
       </c>
       <c r="M13" t="n">
-        <v>52500</v>
+        <v>3412500</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -17857,7 +17857,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1045200</v>
+        <v>1983150</v>
       </c>
       <c r="Q13" t="n">
         <v>84034.8</v>
@@ -17898,10 +17898,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>86400</v>
+        <v>621000</v>
       </c>
       <c r="M14" t="n">
-        <v>10500</v>
+        <v>336000</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -17910,7 +17910,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>694200</v>
+        <v>635700</v>
       </c>
       <c r="Q14" t="n">
         <v>10177.92</v>
@@ -17951,10 +17951,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>70200</v>
+        <v>1107000</v>
       </c>
       <c r="M15" t="n">
-        <v>10500</v>
+        <v>189000</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -17963,7 +17963,7 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>787800</v>
+        <v>1347450</v>
       </c>
       <c r="Q15" t="n">
         <v>12990.24</v>
@@ -18004,10 +18004,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>54000</v>
+        <v>502200</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>21000</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -18016,7 +18016,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>744900</v>
+        <v>1696500</v>
       </c>
       <c r="Q16" t="n">
         <v>7968.24</v>
@@ -18057,10 +18057,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>54000</v>
+        <v>513000</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>10500</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -18069,7 +18069,7 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>245700</v>
+        <v>553800</v>
       </c>
       <c r="Q17" t="n">
         <v>3816.72</v>
@@ -18110,7 +18110,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>118800</v>
+        <v>216000</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -18122,7 +18122,7 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>46800</v>
+        <v>83850</v>
       </c>
       <c r="Q18" t="n">
         <v>1272.24</v>
@@ -18163,7 +18163,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>21600</v>
+        <v>86400</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -18648,7 +18648,7 @@
         <v>89010</v>
       </c>
       <c r="H4" t="n">
-        <v>10320</v>
+        <v>13110</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
@@ -18660,22 +18660,22 @@
         <v>39</v>
       </c>
       <c r="L4" t="n">
-        <v>289500</v>
+        <v>331920</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>15630</v>
+        <v>12510</v>
       </c>
       <c r="O4" t="n">
-        <v>51150</v>
+        <v>54270</v>
       </c>
       <c r="P4" t="n">
-        <v>6330</v>
+        <v>2970</v>
       </c>
       <c r="Q4" t="n">
-        <v>28500.6</v>
+        <v>326569.32</v>
       </c>
     </row>
     <row r="5">
@@ -18701,7 +18701,7 @@
         <v>20280</v>
       </c>
       <c r="H5" t="n">
-        <v>2040</v>
+        <v>3450</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -18713,22 +18713,22 @@
         <v>11</v>
       </c>
       <c r="L5" t="n">
-        <v>85800</v>
+        <v>114210</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>21660</v>
+        <v>26940</v>
       </c>
       <c r="O5" t="n">
-        <v>26760</v>
+        <v>38340</v>
       </c>
       <c r="P5" t="n">
-        <v>5520</v>
+        <v>7590</v>
       </c>
       <c r="Q5" t="n">
-        <v>8221.219999999999</v>
+        <v>94201.47</v>
       </c>
     </row>
     <row r="6">
@@ -18754,7 +18754,7 @@
         <v>2130</v>
       </c>
       <c r="H6" t="n">
-        <v>300</v>
+        <v>420</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -18766,22 +18766,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>12960</v>
+        <v>20970</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3090</v>
+        <v>7050</v>
       </c>
       <c r="O6" t="n">
-        <v>4260</v>
+        <v>6420</v>
       </c>
       <c r="P6" t="n">
-        <v>3480</v>
+        <v>7110</v>
       </c>
       <c r="Q6" t="n">
-        <v>727.66</v>
+        <v>8337.780000000001</v>
       </c>
     </row>
     <row r="7">
@@ -18819,22 +18819,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1230</v>
+        <v>4290</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>60</v>
+        <v>240</v>
       </c>
       <c r="O7" t="n">
-        <v>330</v>
+        <v>900</v>
       </c>
       <c r="P7" t="n">
-        <v>3690</v>
+        <v>9210</v>
       </c>
       <c r="Q7" t="n">
-        <v>105.58</v>
+        <v>1209.78</v>
       </c>
     </row>
     <row r="8">
@@ -18872,7 +18872,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>210</v>
+        <v>540</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -18884,10 +18884,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1200</v>
+        <v>4200</v>
       </c>
       <c r="Q8" t="n">
-        <v>7.78</v>
+        <v>89.09999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -18925,7 +18925,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -18937,10 +18937,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.09</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="10">
@@ -18978,7 +18978,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -19031,7 +19031,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -19993,7 +19993,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>734.4</v>
+        <v>1242</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -20005,22 +20005,22 @@
         <v>3.64</v>
       </c>
       <c r="L5" t="n">
-        <v>18018</v>
+        <v>23984.1</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>216.6</v>
+        <v>269.4</v>
       </c>
       <c r="O5" t="n">
-        <v>1338</v>
+        <v>1917</v>
       </c>
       <c r="P5" t="n">
-        <v>110.4</v>
+        <v>151.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>411.06</v>
+        <v>4710.07</v>
       </c>
     </row>
     <row r="6">
@@ -20046,7 +20046,7 @@
         <v>106.5</v>
       </c>
       <c r="H6" t="n">
-        <v>171</v>
+        <v>239.4</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -20058,22 +20058,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>4795.2</v>
+        <v>7758.9</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>154.5</v>
+        <v>352.5</v>
       </c>
       <c r="O6" t="n">
-        <v>1065</v>
+        <v>1605</v>
       </c>
       <c r="P6" t="n">
-        <v>522</v>
+        <v>1066.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>545.75</v>
+        <v>6253.34</v>
       </c>
     </row>
     <row r="7">
@@ -20111,22 +20111,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>738</v>
+        <v>2574</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>4.2</v>
+        <v>16.8</v>
       </c>
       <c r="O7" t="n">
-        <v>115.5</v>
+        <v>315</v>
       </c>
       <c r="P7" t="n">
-        <v>922.5</v>
+        <v>2302.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>84.45999999999999</v>
+        <v>967.8200000000001</v>
       </c>
     </row>
     <row r="8">
@@ -20164,7 +20164,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>149.1</v>
+        <v>383.4</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -20176,10 +20176,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>456</v>
+        <v>1596</v>
       </c>
       <c r="Q8" t="n">
-        <v>7.39</v>
+        <v>84.64</v>
       </c>
     </row>
     <row r="9">
@@ -20217,7 +20217,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>48.6</v>
+        <v>121.5</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -20229,10 +20229,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.08</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="10">
@@ -20270,7 +20270,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>133.5</v>
+        <v>160.2</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -20323,7 +20323,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -21285,7 +21285,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>4186080</v>
+        <v>7079400</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -21297,22 +21297,22 @@
         <v>176792.4</v>
       </c>
       <c r="L5" t="n">
-        <v>3243240</v>
+        <v>4317138</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>36822</v>
+        <v>45798</v>
       </c>
       <c r="O5" t="n">
-        <v>227460</v>
+        <v>325890</v>
       </c>
       <c r="P5" t="n">
-        <v>7176</v>
+        <v>9867</v>
       </c>
       <c r="Q5" t="n">
-        <v>246636.58</v>
+        <v>2826044.1</v>
       </c>
     </row>
     <row r="6">
@@ -21338,7 +21338,7 @@
         <v>5751</v>
       </c>
       <c r="H6" t="n">
-        <v>974700</v>
+        <v>1364580</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -21350,22 +21350,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>863136</v>
+        <v>1396602</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>26265</v>
+        <v>59925</v>
       </c>
       <c r="O6" t="n">
-        <v>181050</v>
+        <v>272850</v>
       </c>
       <c r="P6" t="n">
-        <v>33930</v>
+        <v>69322.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>327447.36</v>
+        <v>3752001</v>
       </c>
     </row>
     <row r="7">
@@ -21403,22 +21403,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>132840</v>
+        <v>463320</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>714</v>
+        <v>2856</v>
       </c>
       <c r="O7" t="n">
-        <v>19635</v>
+        <v>53550</v>
       </c>
       <c r="P7" t="n">
-        <v>59962.5</v>
+        <v>149662.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>50678.78</v>
+        <v>580694.4</v>
       </c>
     </row>
     <row r="8">
@@ -21456,7 +21456,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>26838</v>
+        <v>69012</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -21468,10 +21468,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>29640</v>
+        <v>103740</v>
       </c>
       <c r="Q8" t="n">
-        <v>4432.32</v>
+        <v>50787</v>
       </c>
     </row>
     <row r="9">
@@ -21509,7 +21509,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>8748</v>
+        <v>21870</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -21521,10 +21521,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>975</v>
+        <v>2925</v>
       </c>
       <c r="Q9" t="n">
-        <v>50.28</v>
+        <v>576.1799999999999</v>
       </c>
     </row>
     <row r="10">
@@ -21562,7 +21562,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>24030</v>
+        <v>28836</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -21615,7 +21615,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>16200</v>
+        <v>27000</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -22577,7 +22577,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>100035000</v>
+        <v>115363440</v>
       </c>
       <c r="I5" t="n">
         <v>192864.43</v>
@@ -22589,22 +22589,22 @@
         <v>3728712.35</v>
       </c>
       <c r="L5" t="n">
-        <v>32256630</v>
+        <v>33838560</v>
       </c>
       <c r="M5" t="n">
-        <v>353430</v>
+        <v>224910</v>
       </c>
       <c r="N5" t="n">
-        <v>103428</v>
+        <v>126837</v>
       </c>
       <c r="O5" t="n">
-        <v>1426470</v>
+        <v>1640670</v>
       </c>
       <c r="P5" t="n">
-        <v>77025</v>
+        <v>49569</v>
       </c>
       <c r="Q5" t="n">
-        <v>4096180.91</v>
+        <v>42448326.35</v>
       </c>
     </row>
     <row r="6">
@@ -22630,7 +22630,7 @@
         <v>673110</v>
       </c>
       <c r="H6" t="n">
-        <v>183048660</v>
+        <v>183730950</v>
       </c>
       <c r="I6" t="n">
         <v>98471.57000000001</v>
@@ -22642,22 +22642,22 @@
         <v>4258895.32</v>
       </c>
       <c r="L6" t="n">
-        <v>42289668</v>
+        <v>42405552</v>
       </c>
       <c r="M6" t="n">
-        <v>857640</v>
+        <v>739200</v>
       </c>
       <c r="N6" t="n">
-        <v>132855</v>
+        <v>214710</v>
       </c>
       <c r="O6" t="n">
-        <v>4644825</v>
+        <v>5008200</v>
       </c>
       <c r="P6" t="n">
-        <v>584707.5</v>
+        <v>423247.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>47985310.44</v>
+        <v>497267128.35</v>
       </c>
     </row>
     <row r="7">
@@ -22683,7 +22683,7 @@
         <v>1658475</v>
       </c>
       <c r="H7" t="n">
-        <v>125079660</v>
+        <v>132694290</v>
       </c>
       <c r="I7" t="n">
         <v>495659.65</v>
@@ -22695,22 +22695,22 @@
         <v>3407660.08</v>
       </c>
       <c r="L7" t="n">
-        <v>54399600</v>
+        <v>54934200</v>
       </c>
       <c r="M7" t="n">
-        <v>2565150</v>
+        <v>3340575</v>
       </c>
       <c r="N7" t="n">
-        <v>44982</v>
+        <v>92463</v>
       </c>
       <c r="O7" t="n">
-        <v>4382175</v>
+        <v>4923030</v>
       </c>
       <c r="P7" t="n">
-        <v>1141725</v>
+        <v>873600</v>
       </c>
       <c r="Q7" t="n">
-        <v>43011622.08</v>
+        <v>445725277.2</v>
       </c>
     </row>
     <row r="8">
@@ -22736,7 +22736,7 @@
         <v>5811507</v>
       </c>
       <c r="H8" t="n">
-        <v>38953800</v>
+        <v>52326000</v>
       </c>
       <c r="I8" t="n">
         <v>142948.86</v>
@@ -22748,22 +22748,22 @@
         <v>3716670.46</v>
       </c>
       <c r="L8" t="n">
-        <v>50819670</v>
+        <v>52824852</v>
       </c>
       <c r="M8" t="n">
-        <v>2552550</v>
+        <v>6017550</v>
       </c>
       <c r="N8" t="n">
-        <v>3060</v>
+        <v>14280</v>
       </c>
       <c r="O8" t="n">
-        <v>4741470</v>
+        <v>5294565</v>
       </c>
       <c r="P8" t="n">
-        <v>1716156</v>
+        <v>1582776</v>
       </c>
       <c r="Q8" t="n">
-        <v>44141893.49</v>
+        <v>457438170.42</v>
       </c>
     </row>
     <row r="9">
@@ -22789,7 +22789,7 @@
         <v>6232302</v>
       </c>
       <c r="H9" t="n">
-        <v>22059000</v>
+        <v>24111000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -22801,22 +22801,22 @@
         <v>2534380.42</v>
       </c>
       <c r="L9" t="n">
-        <v>42458418</v>
+        <v>47475396</v>
       </c>
       <c r="M9" t="n">
-        <v>2557800</v>
+        <v>7592550</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>3562350</v>
+        <v>5020950</v>
       </c>
       <c r="P9" t="n">
-        <v>2362425</v>
+        <v>2279550</v>
       </c>
       <c r="Q9" t="n">
-        <v>37133185.6</v>
+        <v>384807608.85</v>
       </c>
     </row>
     <row r="10">
@@ -22842,7 +22842,7 @@
         <v>4331880</v>
       </c>
       <c r="H10" t="n">
-        <v>27873000</v>
+        <v>26334000</v>
       </c>
       <c r="I10" t="n">
         <v>506924.64</v>
@@ -22854,22 +22854,22 @@
         <v>1647505.08</v>
       </c>
       <c r="L10" t="n">
-        <v>28547640</v>
+        <v>33555492</v>
       </c>
       <c r="M10" t="n">
-        <v>2034900</v>
+        <v>7773675</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>1481550</v>
+        <v>2802450</v>
       </c>
       <c r="P10" t="n">
-        <v>4515030</v>
+        <v>5020567.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>23438142.72</v>
+        <v>242887204.8</v>
       </c>
     </row>
     <row r="11">
@@ -22895,7 +22895,7 @@
         <v>3238380</v>
       </c>
       <c r="H11" t="n">
-        <v>25992000</v>
+        <v>31293000</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -22907,22 +22907,22 @@
         <v>654413.49</v>
       </c>
       <c r="L11" t="n">
-        <v>29262600</v>
+        <v>37335600</v>
       </c>
       <c r="M11" t="n">
-        <v>1152900</v>
+        <v>8316000</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>741285</v>
+        <v>2158830</v>
       </c>
       <c r="P11" t="n">
-        <v>3864510</v>
+        <v>5991570</v>
       </c>
       <c r="Q11" t="n">
-        <v>17046342</v>
+        <v>176649592.5</v>
       </c>
     </row>
     <row r="12">
@@ -22948,7 +22948,7 @@
         <v>2570940</v>
       </c>
       <c r="H12" t="n">
-        <v>7182000</v>
+        <v>10431000</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -22960,22 +22960,22 @@
         <v>315079.88</v>
       </c>
       <c r="L12" t="n">
-        <v>17447400</v>
+        <v>25763400</v>
       </c>
       <c r="M12" t="n">
-        <v>947625</v>
+        <v>5436375</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>402900</v>
+        <v>668100</v>
       </c>
       <c r="P12" t="n">
-        <v>3121950</v>
+        <v>5315700</v>
       </c>
       <c r="Q12" t="n">
-        <v>11602895.76</v>
+        <v>120239685.9</v>
       </c>
     </row>
     <row r="13">
@@ -23001,7 +23001,7 @@
         <v>1265220</v>
       </c>
       <c r="H13" t="n">
-        <v>4788000</v>
+        <v>4446000</v>
       </c>
       <c r="I13" t="n">
         <v>184415.69</v>
@@ -23013,10 +23013,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>7722000</v>
+        <v>11696400</v>
       </c>
       <c r="M13" t="n">
-        <v>493500</v>
+        <v>7203000</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -23025,10 +23025,10 @@
         <v>612000</v>
       </c>
       <c r="P13" t="n">
-        <v>2172300</v>
+        <v>3393000</v>
       </c>
       <c r="Q13" t="n">
-        <v>5877414</v>
+        <v>60907072.5</v>
       </c>
     </row>
     <row r="14">
@@ -23054,7 +23054,7 @@
         <v>322380</v>
       </c>
       <c r="H14" t="n">
-        <v>1368000</v>
+        <v>2736000</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -23066,22 +23066,22 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>2953800</v>
+        <v>5481000</v>
       </c>
       <c r="M14" t="n">
-        <v>105000</v>
+        <v>2289000</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>107100</v>
+        <v>168300</v>
       </c>
       <c r="P14" t="n">
-        <v>1870050</v>
+        <v>1936350</v>
       </c>
       <c r="Q14" t="n">
-        <v>2299540.32</v>
+        <v>23829913.8</v>
       </c>
     </row>
     <row r="15">
@@ -23107,7 +23107,7 @@
         <v>217080</v>
       </c>
       <c r="H15" t="n">
-        <v>513000</v>
+        <v>855000</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -23119,22 +23119,22 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>1220400</v>
+        <v>4206600</v>
       </c>
       <c r="M15" t="n">
-        <v>52500</v>
+        <v>1113000</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>5100</v>
+        <v>25500</v>
       </c>
       <c r="P15" t="n">
-        <v>2533050</v>
+        <v>3586050</v>
       </c>
       <c r="Q15" t="n">
-        <v>1323330.48</v>
+        <v>13713545.7</v>
       </c>
     </row>
     <row r="16">
@@ -23160,7 +23160,7 @@
         <v>63180</v>
       </c>
       <c r="H16" t="n">
-        <v>513000</v>
+        <v>855000</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -23172,10 +23172,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>388800</v>
+        <v>1701000</v>
       </c>
       <c r="M16" t="n">
-        <v>73500</v>
+        <v>535500</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -23184,10 +23184,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1657500</v>
+        <v>2780700</v>
       </c>
       <c r="Q16" t="n">
-        <v>732408.48</v>
+        <v>7589878.2</v>
       </c>
     </row>
     <row r="17">
@@ -23213,7 +23213,7 @@
         <v>12960</v>
       </c>
       <c r="H17" t="n">
-        <v>342000</v>
+        <v>684000</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -23225,10 +23225,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>259200</v>
+        <v>1117800</v>
       </c>
       <c r="M17" t="n">
-        <v>52500</v>
+        <v>346500</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -23237,10 +23237,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1105650</v>
+        <v>1524900</v>
       </c>
       <c r="Q17" t="n">
-        <v>312033.6</v>
+        <v>3233574</v>
       </c>
     </row>
     <row r="18">
@@ -23278,22 +23278,22 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>275400</v>
+        <v>885600</v>
       </c>
       <c r="M18" t="n">
-        <v>42000</v>
+        <v>462000</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>10200</v>
+        <v>25500</v>
       </c>
       <c r="P18" t="n">
-        <v>1177800</v>
+        <v>1565850</v>
       </c>
       <c r="Q18" t="n">
-        <v>150994.8</v>
+        <v>1564744.5</v>
       </c>
     </row>
     <row r="19">
@@ -23319,7 +23319,7 @@
         <v>204120</v>
       </c>
       <c r="H19" t="n">
-        <v>342000</v>
+        <v>684000</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -23331,10 +23331,10 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>140400</v>
+        <v>502200</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>535500</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -23343,10 +23343,10 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>446550</v>
+        <v>1171950</v>
       </c>
       <c r="Q19" t="n">
-        <v>63678.96</v>
+        <v>659898.9</v>
       </c>
     </row>
     <row r="20">
@@ -23384,7 +23384,7 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>10800</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -23396,10 +23396,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1950</v>
+        <v>9750</v>
       </c>
       <c r="Q20" t="n">
-        <v>9776.16</v>
+        <v>101309.4</v>
       </c>
     </row>
     <row r="21">
@@ -23437,7 +23437,7 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>5400</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -23452,7 +23452,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>1071.36</v>
+        <v>11102.4</v>
       </c>
     </row>
     <row r="22">
@@ -23816,7 +23816,7 @@
         <v>53250</v>
       </c>
       <c r="H4" t="n">
-        <v>8580</v>
+        <v>8100</v>
       </c>
       <c r="I4" t="n">
         <v>2</v>
@@ -23828,22 +23828,22 @@
         <v>66</v>
       </c>
       <c r="L4" t="n">
-        <v>155010</v>
+        <v>142890</v>
       </c>
       <c r="M4" t="n">
-        <v>32760</v>
+        <v>42360</v>
       </c>
       <c r="N4" t="n">
-        <v>17490</v>
+        <v>17460</v>
       </c>
       <c r="O4" t="n">
-        <v>16590</v>
+        <v>17160</v>
       </c>
       <c r="P4" t="n">
-        <v>2820</v>
+        <v>1080</v>
       </c>
       <c r="Q4" t="n">
-        <v>13189.64</v>
+        <v>129310.2</v>
       </c>
     </row>
     <row r="5">
@@ -23869,7 +23869,7 @@
         <v>67170</v>
       </c>
       <c r="H5" t="n">
-        <v>11520</v>
+        <v>12330</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -23881,22 +23881,22 @@
         <v>61</v>
       </c>
       <c r="L5" t="n">
-        <v>187860</v>
+        <v>175080</v>
       </c>
       <c r="M5" t="n">
-        <v>13290</v>
+        <v>21900</v>
       </c>
       <c r="N5" t="n">
-        <v>14580</v>
+        <v>16590</v>
       </c>
       <c r="O5" t="n">
-        <v>20310</v>
+        <v>21540</v>
       </c>
       <c r="P5" t="n">
-        <v>3510</v>
+        <v>1260</v>
       </c>
       <c r="Q5" t="n">
-        <v>21112.44</v>
+        <v>206984.7</v>
       </c>
     </row>
     <row r="6">
@@ -23922,7 +23922,7 @@
         <v>70230</v>
       </c>
       <c r="H6" t="n">
-        <v>16680</v>
+        <v>15180</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -23934,22 +23934,22 @@
         <v>59</v>
       </c>
       <c r="L6" t="n">
-        <v>198090</v>
+        <v>193710</v>
       </c>
       <c r="M6" t="n">
-        <v>6150</v>
+        <v>13770</v>
       </c>
       <c r="N6" t="n">
-        <v>6960</v>
+        <v>9570</v>
       </c>
       <c r="O6" t="n">
-        <v>20940</v>
+        <v>20700</v>
       </c>
       <c r="P6" t="n">
-        <v>4140</v>
+        <v>2370</v>
       </c>
       <c r="Q6" t="n">
-        <v>26262.05</v>
+        <v>257471.1</v>
       </c>
     </row>
     <row r="7">
@@ -23975,7 +23975,7 @@
         <v>87390</v>
       </c>
       <c r="H7" t="n">
-        <v>18450</v>
+        <v>19740</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
@@ -23987,22 +23987,22 @@
         <v>48</v>
       </c>
       <c r="L7" t="n">
-        <v>247020</v>
+        <v>251430</v>
       </c>
       <c r="M7" t="n">
-        <v>5280</v>
+        <v>14010</v>
       </c>
       <c r="N7" t="n">
-        <v>1620</v>
+        <v>3000</v>
       </c>
       <c r="O7" t="n">
-        <v>22920</v>
+        <v>23970</v>
       </c>
       <c r="P7" t="n">
-        <v>5970</v>
+        <v>4500</v>
       </c>
       <c r="Q7" t="n">
-        <v>26189.25</v>
+        <v>256757.4</v>
       </c>
     </row>
     <row r="8">
@@ -24028,7 +24028,7 @@
         <v>97770</v>
       </c>
       <c r="H8" t="n">
-        <v>3180</v>
+        <v>4260</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -24040,22 +24040,22 @@
         <v>62</v>
       </c>
       <c r="L8" t="n">
-        <v>236730</v>
+        <v>242730</v>
       </c>
       <c r="M8" t="n">
-        <v>4320</v>
+        <v>11670</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>19410</v>
+        <v>21300</v>
       </c>
       <c r="P8" t="n">
-        <v>8700</v>
+        <v>6180</v>
       </c>
       <c r="Q8" t="n">
-        <v>28471.49</v>
+        <v>279132.3</v>
       </c>
     </row>
     <row r="9">
@@ -24081,7 +24081,7 @@
         <v>90810</v>
       </c>
       <c r="H9" t="n">
-        <v>450</v>
+        <v>690</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -24093,22 +24093,22 @@
         <v>51</v>
       </c>
       <c r="L9" t="n">
-        <v>193650</v>
+        <v>213690</v>
       </c>
       <c r="M9" t="n">
-        <v>4950</v>
+        <v>10500</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>22860</v>
+        <v>26430</v>
       </c>
       <c r="P9" t="n">
-        <v>10830</v>
+        <v>5400</v>
       </c>
       <c r="Q9" t="n">
-        <v>29399.13</v>
+        <v>288226.8</v>
       </c>
     </row>
     <row r="10">
@@ -24134,7 +24134,7 @@
         <v>55920</v>
       </c>
       <c r="H10" t="n">
-        <v>300</v>
+        <v>360</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -24146,22 +24146,22 @@
         <v>33</v>
       </c>
       <c r="L10" t="n">
-        <v>104940</v>
+        <v>122790</v>
       </c>
       <c r="M10" t="n">
-        <v>3600</v>
+        <v>7110</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>10920</v>
+        <v>18270</v>
       </c>
       <c r="P10" t="n">
-        <v>15660</v>
+        <v>8910</v>
       </c>
       <c r="Q10" t="n">
-        <v>23445.9</v>
+        <v>229861.8</v>
       </c>
     </row>
     <row r="11">
@@ -24187,7 +24187,7 @@
         <v>25980</v>
       </c>
       <c r="H11" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -24199,22 +24199,22 @@
         <v>9</v>
       </c>
       <c r="L11" t="n">
-        <v>63240</v>
+        <v>75960</v>
       </c>
       <c r="M11" t="n">
-        <v>2310</v>
+        <v>6060</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>5070</v>
+        <v>14700</v>
       </c>
       <c r="P11" t="n">
-        <v>14880</v>
+        <v>14910</v>
       </c>
       <c r="Q11" t="n">
-        <v>15429.47</v>
+        <v>151269.3</v>
       </c>
     </row>
     <row r="12">
@@ -24252,22 +24252,22 @@
         <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>28890</v>
+        <v>39570</v>
       </c>
       <c r="M12" t="n">
-        <v>2220</v>
+        <v>4590</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>2370</v>
+        <v>3900</v>
       </c>
       <c r="P12" t="n">
-        <v>12330</v>
+        <v>12030</v>
       </c>
       <c r="Q12" t="n">
-        <v>8891.200000000001</v>
+        <v>87168.60000000001</v>
       </c>
     </row>
     <row r="13">
@@ -24305,10 +24305,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>10080</v>
+        <v>15330</v>
       </c>
       <c r="M13" t="n">
-        <v>1020</v>
+        <v>4680</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -24317,10 +24317,10 @@
         <v>3600</v>
       </c>
       <c r="P13" t="n">
-        <v>12960</v>
+        <v>11400</v>
       </c>
       <c r="Q13" t="n">
-        <v>4143.39</v>
+        <v>40621.5</v>
       </c>
     </row>
     <row r="14">
@@ -24358,22 +24358,22 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>2610</v>
+        <v>8070</v>
       </c>
       <c r="M14" t="n">
-        <v>120</v>
+        <v>1830</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>630</v>
+        <v>990</v>
       </c>
       <c r="P14" t="n">
-        <v>16260</v>
+        <v>17010</v>
       </c>
       <c r="Q14" t="n">
-        <v>1352.76</v>
+        <v>13262.4</v>
       </c>
     </row>
     <row r="15">
@@ -24411,22 +24411,22 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>990</v>
+        <v>5640</v>
       </c>
       <c r="M15" t="n">
-        <v>60</v>
+        <v>810</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="P15" t="n">
-        <v>26550</v>
+        <v>33840</v>
       </c>
       <c r="Q15" t="n">
-        <v>534.64</v>
+        <v>5241.6</v>
       </c>
     </row>
     <row r="16">
@@ -24464,10 +24464,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>240</v>
+        <v>2790</v>
       </c>
       <c r="M16" t="n">
-        <v>90</v>
+        <v>720</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -24476,10 +24476,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>14040</v>
+        <v>16680</v>
       </c>
       <c r="Q16" t="n">
-        <v>199.11</v>
+        <v>1952.1</v>
       </c>
     </row>
     <row r="17">
@@ -24517,10 +24517,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>210</v>
+        <v>1350</v>
       </c>
       <c r="M17" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -24529,10 +24529,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>13260</v>
+        <v>14970</v>
       </c>
       <c r="Q17" t="n">
-        <v>118.88</v>
+        <v>1165.5</v>
       </c>
     </row>
     <row r="18">
@@ -24570,22 +24570,22 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>120</v>
+        <v>1560</v>
       </c>
       <c r="M18" t="n">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="P18" t="n">
-        <v>17400</v>
+        <v>22800</v>
       </c>
       <c r="Q18" t="n">
-        <v>100.7</v>
+        <v>987.3</v>
       </c>
     </row>
     <row r="19">
@@ -24623,10 +24623,10 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -24635,10 +24635,10 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>6870</v>
+        <v>18030</v>
       </c>
       <c r="Q19" t="n">
-        <v>47.83</v>
+        <v>468.9</v>
       </c>
     </row>
     <row r="20">
@@ -24688,10 +24688,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="Q20" t="n">
-        <v>7.71</v>
+        <v>75.59999999999999</v>
       </c>
     </row>
     <row r="21">
@@ -24744,7 +24744,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.64</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="22">
@@ -25161,7 +25161,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>4147.2</v>
+        <v>4438.8</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -25173,22 +25173,22 @@
         <v>20.19</v>
       </c>
       <c r="L5" t="n">
-        <v>39450.6</v>
+        <v>36766.8</v>
       </c>
       <c r="M5" t="n">
-        <v>265.8</v>
+        <v>438</v>
       </c>
       <c r="N5" t="n">
-        <v>145.8</v>
+        <v>165.9</v>
       </c>
       <c r="O5" t="n">
-        <v>1015.5</v>
+        <v>1077</v>
       </c>
       <c r="P5" t="n">
-        <v>70.2</v>
+        <v>25.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>1055.62</v>
+        <v>10349.24</v>
       </c>
     </row>
     <row r="6">
@@ -25214,7 +25214,7 @@
         <v>3511.5</v>
       </c>
       <c r="H6" t="n">
-        <v>9507.6</v>
+        <v>8652.6</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -25226,22 +25226,22 @@
         <v>29.91</v>
       </c>
       <c r="L6" t="n">
-        <v>73293.3</v>
+        <v>71672.7</v>
       </c>
       <c r="M6" t="n">
-        <v>492</v>
+        <v>1101.6</v>
       </c>
       <c r="N6" t="n">
-        <v>348</v>
+        <v>478.5</v>
       </c>
       <c r="O6" t="n">
-        <v>5235</v>
+        <v>5175</v>
       </c>
       <c r="P6" t="n">
-        <v>621</v>
+        <v>355.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>19696.54</v>
+        <v>193103.32</v>
       </c>
     </row>
     <row r="7">
@@ -25267,7 +25267,7 @@
         <v>13108.5</v>
       </c>
       <c r="H7" t="n">
-        <v>13468.5</v>
+        <v>14410.2</v>
       </c>
       <c r="I7" t="n">
         <v>0.64</v>
@@ -25279,22 +25279,22 @@
         <v>30.62</v>
       </c>
       <c r="L7" t="n">
-        <v>148212</v>
+        <v>150858</v>
       </c>
       <c r="M7" t="n">
-        <v>1848</v>
+        <v>4903.5</v>
       </c>
       <c r="N7" t="n">
-        <v>113.4</v>
+        <v>210</v>
       </c>
       <c r="O7" t="n">
-        <v>8022</v>
+        <v>8389.5</v>
       </c>
       <c r="P7" t="n">
-        <v>1492.5</v>
+        <v>1125</v>
       </c>
       <c r="Q7" t="n">
-        <v>20951.4</v>
+        <v>205405.92</v>
       </c>
     </row>
     <row r="8">
@@ -25320,7 +25320,7 @@
         <v>63550.5</v>
       </c>
       <c r="H8" t="n">
-        <v>2703</v>
+        <v>3621</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -25332,22 +25332,22 @@
         <v>45.63</v>
       </c>
       <c r="L8" t="n">
-        <v>168078.3</v>
+        <v>172338.3</v>
       </c>
       <c r="M8" t="n">
-        <v>2376</v>
+        <v>6418.5</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>8734.5</v>
+        <v>9585</v>
       </c>
       <c r="P8" t="n">
-        <v>3306</v>
+        <v>2348.4</v>
       </c>
       <c r="Q8" t="n">
-        <v>27047.92</v>
+        <v>265175.68</v>
       </c>
     </row>
     <row r="9">
@@ -25373,7 +25373,7 @@
         <v>77188.5</v>
       </c>
       <c r="H9" t="n">
-        <v>450</v>
+        <v>690</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -25385,22 +25385,22 @@
         <v>40.95</v>
       </c>
       <c r="L9" t="n">
-        <v>156856.5</v>
+        <v>173088.9</v>
       </c>
       <c r="M9" t="n">
-        <v>3465</v>
+        <v>7350</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>12573</v>
+        <v>14536.5</v>
       </c>
       <c r="P9" t="n">
-        <v>5415</v>
+        <v>2700</v>
       </c>
       <c r="Q9" t="n">
-        <v>28517.16</v>
+        <v>279580</v>
       </c>
     </row>
     <row r="10">
@@ -25426,7 +25426,7 @@
         <v>55920</v>
       </c>
       <c r="H10" t="n">
-        <v>300</v>
+        <v>360</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -25438,22 +25438,22 @@
         <v>28.71</v>
       </c>
       <c r="L10" t="n">
-        <v>93396.60000000001</v>
+        <v>109283.1</v>
       </c>
       <c r="M10" t="n">
-        <v>3060</v>
+        <v>6043.5</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>7644</v>
+        <v>12789</v>
       </c>
       <c r="P10" t="n">
-        <v>13311</v>
+        <v>7573.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>23445.9</v>
+        <v>229861.8</v>
       </c>
     </row>
     <row r="11">
@@ -25479,7 +25479,7 @@
         <v>25980</v>
       </c>
       <c r="H11" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -25491,22 +25491,22 @@
         <v>8.09</v>
       </c>
       <c r="L11" t="n">
-        <v>63240</v>
+        <v>75960</v>
       </c>
       <c r="M11" t="n">
-        <v>2079</v>
+        <v>5454</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>4309.5</v>
+        <v>12495</v>
       </c>
       <c r="P11" t="n">
-        <v>13392</v>
+        <v>13419</v>
       </c>
       <c r="Q11" t="n">
-        <v>15429.47</v>
+        <v>151269.3</v>
       </c>
     </row>
     <row r="12">
@@ -25544,22 +25544,22 @@
         <v>0.93</v>
       </c>
       <c r="L12" t="n">
-        <v>28890</v>
+        <v>39570</v>
       </c>
       <c r="M12" t="n">
-        <v>2109</v>
+        <v>4360.5</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>2370</v>
+        <v>3900</v>
       </c>
       <c r="P12" t="n">
-        <v>12330</v>
+        <v>12030</v>
       </c>
       <c r="Q12" t="n">
-        <v>8891.200000000001</v>
+        <v>87168.60000000001</v>
       </c>
     </row>
     <row r="13">
@@ -25597,10 +25597,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>10080</v>
+        <v>15330</v>
       </c>
       <c r="M13" t="n">
-        <v>1020</v>
+        <v>4680</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -25609,10 +25609,10 @@
         <v>3600</v>
       </c>
       <c r="P13" t="n">
-        <v>12960</v>
+        <v>11400</v>
       </c>
       <c r="Q13" t="n">
-        <v>4143.39</v>
+        <v>40621.5</v>
       </c>
     </row>
     <row r="14">
@@ -25650,22 +25650,22 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>2610</v>
+        <v>8070</v>
       </c>
       <c r="M14" t="n">
-        <v>120</v>
+        <v>1830</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>630</v>
+        <v>990</v>
       </c>
       <c r="P14" t="n">
-        <v>16260</v>
+        <v>17010</v>
       </c>
       <c r="Q14" t="n">
-        <v>1352.76</v>
+        <v>13262.4</v>
       </c>
     </row>
     <row r="15">
@@ -25703,22 +25703,22 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>990</v>
+        <v>5640</v>
       </c>
       <c r="M15" t="n">
-        <v>60</v>
+        <v>810</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="P15" t="n">
-        <v>26550</v>
+        <v>33840</v>
       </c>
       <c r="Q15" t="n">
-        <v>534.64</v>
+        <v>5241.6</v>
       </c>
     </row>
     <row r="16">
@@ -25756,10 +25756,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>240</v>
+        <v>2790</v>
       </c>
       <c r="M16" t="n">
-        <v>90</v>
+        <v>720</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -25768,10 +25768,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>14040</v>
+        <v>16680</v>
       </c>
       <c r="Q16" t="n">
-        <v>199.11</v>
+        <v>1952.1</v>
       </c>
     </row>
     <row r="17">
@@ -25809,10 +25809,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>210</v>
+        <v>1350</v>
       </c>
       <c r="M17" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -25821,10 +25821,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>13260</v>
+        <v>14970</v>
       </c>
       <c r="Q17" t="n">
-        <v>118.88</v>
+        <v>1165.5</v>
       </c>
     </row>
     <row r="18">
@@ -25862,22 +25862,22 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>120</v>
+        <v>1560</v>
       </c>
       <c r="M18" t="n">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="P18" t="n">
-        <v>17400</v>
+        <v>22800</v>
       </c>
       <c r="Q18" t="n">
-        <v>100.7</v>
+        <v>987.3</v>
       </c>
     </row>
     <row r="19">
@@ -25915,10 +25915,10 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -25927,10 +25927,10 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>6870</v>
+        <v>18030</v>
       </c>
       <c r="Q19" t="n">
-        <v>47.83</v>
+        <v>468.9</v>
       </c>
     </row>
     <row r="20">
@@ -25980,10 +25980,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="Q20" t="n">
-        <v>7.71</v>
+        <v>75.59999999999999</v>
       </c>
     </row>
     <row r="21">
@@ -26036,7 +26036,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.64</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="22">
@@ -26453,7 +26453,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>23639040</v>
+        <v>25301160</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -26465,22 +26465,22 @@
         <v>980394.2</v>
       </c>
       <c r="L5" t="n">
-        <v>7101108</v>
+        <v>6618024</v>
       </c>
       <c r="M5" t="n">
-        <v>93030</v>
+        <v>153300</v>
       </c>
       <c r="N5" t="n">
-        <v>24786</v>
+        <v>28203</v>
       </c>
       <c r="O5" t="n">
-        <v>172635</v>
+        <v>183090</v>
       </c>
       <c r="P5" t="n">
-        <v>4563</v>
+        <v>1638</v>
       </c>
       <c r="Q5" t="n">
-        <v>633373.1800000001</v>
+        <v>6209541</v>
       </c>
     </row>
     <row r="6">
@@ -26506,7 +26506,7 @@
         <v>189621</v>
       </c>
       <c r="H6" t="n">
-        <v>54193320</v>
+        <v>49319820</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -26518,22 +26518,22 @@
         <v>1452455.63</v>
       </c>
       <c r="L6" t="n">
-        <v>13192794</v>
+        <v>12901086</v>
       </c>
       <c r="M6" t="n">
-        <v>172200</v>
+        <v>385560</v>
       </c>
       <c r="N6" t="n">
-        <v>59160</v>
+        <v>81345</v>
       </c>
       <c r="O6" t="n">
-        <v>889950</v>
+        <v>879750</v>
       </c>
       <c r="P6" t="n">
-        <v>40365</v>
+        <v>23107.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>11817923.49</v>
+        <v>115861995</v>
       </c>
     </row>
     <row r="7">
@@ -26559,7 +26559,7 @@
         <v>707859</v>
       </c>
       <c r="H7" t="n">
-        <v>76770450</v>
+        <v>82138140</v>
       </c>
       <c r="I7" t="n">
         <v>123914.91</v>
@@ -26571,22 +26571,22 @@
         <v>1486978.94</v>
       </c>
       <c r="L7" t="n">
-        <v>26678160</v>
+        <v>27154440</v>
       </c>
       <c r="M7" t="n">
-        <v>646800</v>
+        <v>1716225</v>
       </c>
       <c r="N7" t="n">
-        <v>19278</v>
+        <v>35700</v>
       </c>
       <c r="O7" t="n">
-        <v>1363740</v>
+        <v>1426215</v>
       </c>
       <c r="P7" t="n">
-        <v>97012.5</v>
+        <v>73125</v>
       </c>
       <c r="Q7" t="n">
-        <v>12570842.3</v>
+        <v>123243552</v>
       </c>
     </row>
     <row r="8">
@@ -26612,7 +26612,7 @@
         <v>3431727</v>
       </c>
       <c r="H8" t="n">
-        <v>15407100</v>
+        <v>20639700</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -26624,22 +26624,22 @@
         <v>2215707.39</v>
       </c>
       <c r="L8" t="n">
-        <v>30254094</v>
+        <v>31020894</v>
       </c>
       <c r="M8" t="n">
-        <v>831600</v>
+        <v>2246475</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>1484865</v>
+        <v>1629450</v>
       </c>
       <c r="P8" t="n">
-        <v>214890</v>
+        <v>152646</v>
       </c>
       <c r="Q8" t="n">
-        <v>16228751.92</v>
+        <v>159105411</v>
       </c>
     </row>
     <row r="9">
@@ -26665,7 +26665,7 @@
         <v>4168179</v>
       </c>
       <c r="H9" t="n">
-        <v>2565000</v>
+        <v>3933000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -26677,22 +26677,22 @@
         <v>1988513.87</v>
       </c>
       <c r="L9" t="n">
-        <v>28234170</v>
+        <v>31156002</v>
       </c>
       <c r="M9" t="n">
-        <v>1212750</v>
+        <v>2572500</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>2137410</v>
+        <v>2471205</v>
       </c>
       <c r="P9" t="n">
-        <v>351975</v>
+        <v>175500</v>
       </c>
       <c r="Q9" t="n">
-        <v>17110295.76</v>
+        <v>167747997.6</v>
       </c>
     </row>
     <row r="10">
@@ -26718,7 +26718,7 @@
         <v>3019680</v>
       </c>
       <c r="H10" t="n">
-        <v>1710000</v>
+        <v>2052000</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -26730,22 +26730,22 @@
         <v>1394042.76</v>
       </c>
       <c r="L10" t="n">
-        <v>16811388</v>
+        <v>19670958</v>
       </c>
       <c r="M10" t="n">
-        <v>1071000</v>
+        <v>2115225</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>1299480</v>
+        <v>2174130</v>
       </c>
       <c r="P10" t="n">
-        <v>865215</v>
+        <v>492277.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>14067542.16</v>
+        <v>137917080</v>
       </c>
     </row>
     <row r="11">
@@ -26771,7 +26771,7 @@
         <v>1402920</v>
       </c>
       <c r="H11" t="n">
-        <v>171000</v>
+        <v>513000</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -26783,22 +26783,22 @@
         <v>392648.09</v>
       </c>
       <c r="L11" t="n">
-        <v>11383200</v>
+        <v>13672800</v>
       </c>
       <c r="M11" t="n">
-        <v>727650</v>
+        <v>1908900</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>732615</v>
+        <v>2124150</v>
       </c>
       <c r="P11" t="n">
-        <v>870480</v>
+        <v>872235</v>
       </c>
       <c r="Q11" t="n">
-        <v>9257681.16</v>
+        <v>90761580</v>
       </c>
     </row>
     <row r="12">
@@ -26836,22 +26836,22 @@
         <v>45011.41</v>
       </c>
       <c r="L12" t="n">
-        <v>5200200</v>
+        <v>7122600</v>
       </c>
       <c r="M12" t="n">
-        <v>738150</v>
+        <v>1526175</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>402900</v>
+        <v>663000</v>
       </c>
       <c r="P12" t="n">
-        <v>801450</v>
+        <v>781950</v>
       </c>
       <c r="Q12" t="n">
-        <v>5334718.32</v>
+        <v>52301160</v>
       </c>
     </row>
     <row r="13">
@@ -26889,10 +26889,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1814400</v>
+        <v>2759400</v>
       </c>
       <c r="M13" t="n">
-        <v>357000</v>
+        <v>1638000</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -26901,10 +26901,10 @@
         <v>612000</v>
       </c>
       <c r="P13" t="n">
-        <v>842400</v>
+        <v>741000</v>
       </c>
       <c r="Q13" t="n">
-        <v>2486035.8</v>
+        <v>24372900</v>
       </c>
     </row>
     <row r="14">
@@ -26942,22 +26942,22 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>469800</v>
+        <v>1452600</v>
       </c>
       <c r="M14" t="n">
-        <v>42000</v>
+        <v>640500</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>107100</v>
+        <v>168300</v>
       </c>
       <c r="P14" t="n">
-        <v>1056900</v>
+        <v>1105650</v>
       </c>
       <c r="Q14" t="n">
-        <v>811658.88</v>
+        <v>7957440</v>
       </c>
     </row>
     <row r="15">
@@ -26995,22 +26995,22 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>178200</v>
+        <v>1015200</v>
       </c>
       <c r="M15" t="n">
-        <v>21000</v>
+        <v>283500</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>5100</v>
+        <v>25500</v>
       </c>
       <c r="P15" t="n">
-        <v>1725750</v>
+        <v>2199600</v>
       </c>
       <c r="Q15" t="n">
-        <v>320785.92</v>
+        <v>3144960</v>
       </c>
     </row>
     <row r="16">
@@ -27048,10 +27048,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>43200</v>
+        <v>502200</v>
       </c>
       <c r="M16" t="n">
-        <v>31500</v>
+        <v>252000</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -27060,10 +27060,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>912600</v>
+        <v>1084200</v>
       </c>
       <c r="Q16" t="n">
-        <v>119468.52</v>
+        <v>1171260</v>
       </c>
     </row>
     <row r="17">
@@ -27101,10 +27101,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>37800</v>
+        <v>243000</v>
       </c>
       <c r="M17" t="n">
-        <v>10500</v>
+        <v>31500</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -27113,10 +27113,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>861900</v>
+        <v>973050</v>
       </c>
       <c r="Q17" t="n">
-        <v>71328.60000000001</v>
+        <v>699300</v>
       </c>
     </row>
     <row r="18">
@@ -27154,22 +27154,22 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>21600</v>
+        <v>280800</v>
       </c>
       <c r="M18" t="n">
-        <v>42000</v>
+        <v>31500</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>10200</v>
+        <v>25500</v>
       </c>
       <c r="P18" t="n">
-        <v>1131000</v>
+        <v>1482000</v>
       </c>
       <c r="Q18" t="n">
-        <v>60422.76</v>
+        <v>592380</v>
       </c>
     </row>
     <row r="19">
@@ -27207,10 +27207,10 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>16200</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>31500</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -27219,10 +27219,10 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>446550</v>
+        <v>1171950</v>
       </c>
       <c r="Q19" t="n">
-        <v>28696.68</v>
+        <v>281340</v>
       </c>
     </row>
     <row r="20">
@@ -27272,10 +27272,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1950</v>
+        <v>9750</v>
       </c>
       <c r="Q20" t="n">
-        <v>4626.72</v>
+        <v>45360</v>
       </c>
     </row>
     <row r="21">
@@ -27328,7 +27328,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>385.56</v>
+        <v>3780</v>
       </c>
     </row>
     <row r="22">
@@ -27692,7 +27692,7 @@
         <v>141120</v>
       </c>
       <c r="H4" t="n">
-        <v>24750</v>
+        <v>24120</v>
       </c>
       <c r="I4" t="n">
         <v>2</v>
@@ -27704,7 +27704,7 @@
         <v>89</v>
       </c>
       <c r="L4" t="n">
-        <v>401340</v>
+        <v>433590</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -27713,13 +27713,13 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>70530</v>
+        <v>67320</v>
       </c>
       <c r="P4" t="n">
-        <v>720</v>
+        <v>30</v>
       </c>
       <c r="Q4" t="n">
-        <v>42111.32</v>
+        <v>586360.17</v>
       </c>
     </row>
     <row r="5">
@@ -27745,7 +27745,7 @@
         <v>87660</v>
       </c>
       <c r="H5" t="n">
-        <v>18870</v>
+        <v>20400</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -27757,7 +27757,7 @@
         <v>49</v>
       </c>
       <c r="L5" t="n">
-        <v>216030</v>
+        <v>236160</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -27766,13 +27766,13 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>50790</v>
+        <v>52830</v>
       </c>
       <c r="P5" t="n">
-        <v>1050</v>
+        <v>30</v>
       </c>
       <c r="Q5" t="n">
-        <v>24884.36</v>
+        <v>346491.09</v>
       </c>
     </row>
     <row r="6">
@@ -27798,7 +27798,7 @@
         <v>53730</v>
       </c>
       <c r="H6" t="n">
-        <v>21000</v>
+        <v>21570</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -27810,7 +27810,7 @@
         <v>19</v>
       </c>
       <c r="L6" t="n">
-        <v>115230</v>
+        <v>123510</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -27819,13 +27819,13 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>33180</v>
+        <v>38010</v>
       </c>
       <c r="P6" t="n">
-        <v>2220</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>8981.780000000001</v>
+        <v>125062.74</v>
       </c>
     </row>
     <row r="7">
@@ -27851,7 +27851,7 @@
         <v>19260</v>
       </c>
       <c r="H7" t="n">
-        <v>3150</v>
+        <v>3750</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -27863,7 +27863,7 @@
         <v>5</v>
       </c>
       <c r="L7" t="n">
-        <v>46380</v>
+        <v>50460</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -27872,13 +27872,13 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>15030</v>
+        <v>18360</v>
       </c>
       <c r="P7" t="n">
-        <v>3150</v>
+        <v>360</v>
       </c>
       <c r="Q7" t="n">
-        <v>4529.92</v>
+        <v>63074.88</v>
       </c>
     </row>
     <row r="8">
@@ -27904,7 +27904,7 @@
         <v>690</v>
       </c>
       <c r="H8" t="n">
-        <v>510</v>
+        <v>660</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -27916,7 +27916,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>7020</v>
+        <v>8700</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -27925,13 +27925,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>6270</v>
+        <v>9810</v>
       </c>
       <c r="P8" t="n">
-        <v>4890</v>
+        <v>990</v>
       </c>
       <c r="Q8" t="n">
-        <v>254.18</v>
+        <v>3539.25</v>
       </c>
     </row>
     <row r="9">
@@ -27957,7 +27957,7 @@
         <v>150</v>
       </c>
       <c r="H9" t="n">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -27969,7 +27969,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1770</v>
+        <v>2820</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -27978,13 +27978,13 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>2730</v>
+        <v>8850</v>
       </c>
       <c r="P9" t="n">
-        <v>5010</v>
+        <v>3540</v>
       </c>
       <c r="Q9" t="n">
-        <v>39.89</v>
+        <v>555.39</v>
       </c>
     </row>
     <row r="10">
@@ -28010,7 +28010,7 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -28022,7 +28022,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>420</v>
+        <v>2340</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -28031,13 +28031,13 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>450</v>
+        <v>2940</v>
       </c>
       <c r="P10" t="n">
-        <v>5820</v>
+        <v>9000</v>
       </c>
       <c r="Q10" t="n">
-        <v>19.2</v>
+        <v>267.3</v>
       </c>
     </row>
     <row r="11">
@@ -28063,7 +28063,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -28075,7 +28075,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>150</v>
+        <v>1740</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -28084,13 +28084,13 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="P11" t="n">
-        <v>2670</v>
+        <v>6600</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.62</v>
+        <v>64.34999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -28116,7 +28116,7 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -28128,7 +28128,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>30</v>
+        <v>1230</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -28140,10 +28140,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1770</v>
+        <v>5730</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.5</v>
+        <v>6.93</v>
       </c>
     </row>
     <row r="13">
@@ -28181,7 +28181,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>390</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -28193,10 +28193,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>420</v>
+        <v>1560</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.21</v>
+        <v>2.97</v>
       </c>
     </row>
     <row r="14">
@@ -28234,7 +28234,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -28246,7 +28246,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>30</v>
+        <v>330</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -29037,7 +29037,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>6793.2</v>
+        <v>7344</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -29049,7 +29049,7 @@
         <v>16.22</v>
       </c>
       <c r="L5" t="n">
-        <v>45366.3</v>
+        <v>49593.6</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -29058,13 +29058,13 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>2539.5</v>
+        <v>2641.5</v>
       </c>
       <c r="P5" t="n">
-        <v>21</v>
+        <v>0.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>1244.22</v>
+        <v>17324.55</v>
       </c>
     </row>
     <row r="6">
@@ -29090,7 +29090,7 @@
         <v>2686.5</v>
       </c>
       <c r="H6" t="n">
-        <v>11970</v>
+        <v>12294.9</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -29102,7 +29102,7 @@
         <v>9.630000000000001</v>
       </c>
       <c r="L6" t="n">
-        <v>42635.1</v>
+        <v>45698.7</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -29111,13 +29111,13 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>8295</v>
+        <v>9502.5</v>
       </c>
       <c r="P6" t="n">
-        <v>333</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>6736.33</v>
+        <v>93797.06</v>
       </c>
     </row>
     <row r="7">
@@ -29143,7 +29143,7 @@
         <v>2889</v>
       </c>
       <c r="H7" t="n">
-        <v>2299.5</v>
+        <v>2737.5</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -29155,7 +29155,7 @@
         <v>3.19</v>
       </c>
       <c r="L7" t="n">
-        <v>27828</v>
+        <v>30276</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -29164,13 +29164,13 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>5260.5</v>
+        <v>6426</v>
       </c>
       <c r="P7" t="n">
-        <v>787.5</v>
+        <v>90</v>
       </c>
       <c r="Q7" t="n">
-        <v>3623.94</v>
+        <v>50459.9</v>
       </c>
     </row>
     <row r="8">
@@ -29196,7 +29196,7 @@
         <v>448.5</v>
       </c>
       <c r="H8" t="n">
-        <v>433.5</v>
+        <v>561</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -29208,7 +29208,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>4984.2</v>
+        <v>6177</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -29217,13 +29217,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2821.5</v>
+        <v>4414.5</v>
       </c>
       <c r="P8" t="n">
-        <v>1858.2</v>
+        <v>376.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>241.47</v>
+        <v>3362.29</v>
       </c>
     </row>
     <row r="9">
@@ -29249,7 +29249,7 @@
         <v>127.5</v>
       </c>
       <c r="H9" t="n">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -29261,7 +29261,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1433.7</v>
+        <v>2284.2</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -29270,13 +29270,13 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>1501.5</v>
+        <v>4867.5</v>
       </c>
       <c r="P9" t="n">
-        <v>2505</v>
+        <v>1770</v>
       </c>
       <c r="Q9" t="n">
-        <v>38.69</v>
+        <v>538.73</v>
       </c>
     </row>
     <row r="10">
@@ -29302,7 +29302,7 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -29314,7 +29314,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>373.8</v>
+        <v>2082.6</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -29323,13 +29323,13 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>315</v>
+        <v>2058</v>
       </c>
       <c r="P10" t="n">
-        <v>4947</v>
+        <v>7650</v>
       </c>
       <c r="Q10" t="n">
-        <v>19.2</v>
+        <v>267.3</v>
       </c>
     </row>
     <row r="11">
@@ -29355,7 +29355,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -29367,7 +29367,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>150</v>
+        <v>1740</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -29376,13 +29376,13 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="P11" t="n">
-        <v>2403</v>
+        <v>5940</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.62</v>
+        <v>64.34999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -29408,7 +29408,7 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -29420,7 +29420,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>30</v>
+        <v>1230</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -29432,10 +29432,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1770</v>
+        <v>5730</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.5</v>
+        <v>6.93</v>
       </c>
     </row>
     <row r="13">
@@ -29473,7 +29473,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>390</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -29485,10 +29485,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>420</v>
+        <v>1560</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.21</v>
+        <v>2.97</v>
       </c>
     </row>
     <row r="14">
@@ -29526,7 +29526,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -29538,7 +29538,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>30</v>
+        <v>330</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -30329,7 +30329,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>38721240</v>
+        <v>41860800</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -30341,7 +30341,7 @@
         <v>787529.76</v>
       </c>
       <c r="L5" t="n">
-        <v>8165934</v>
+        <v>8926848</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -30350,13 +30350,13 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>431715</v>
+        <v>449055</v>
       </c>
       <c r="P5" t="n">
-        <v>1365</v>
+        <v>39</v>
       </c>
       <c r="Q5" t="n">
-        <v>746530.8</v>
+        <v>10394732.7</v>
       </c>
     </row>
     <row r="6">
@@ -30382,7 +30382,7 @@
         <v>145071</v>
       </c>
       <c r="H6" t="n">
-        <v>68229000</v>
+        <v>70080930</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -30394,7 +30394,7 @@
         <v>467739.95</v>
       </c>
       <c r="L6" t="n">
-        <v>7674318</v>
+        <v>8225766</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -30403,13 +30403,13 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>1410150</v>
+        <v>1615425</v>
       </c>
       <c r="P6" t="n">
-        <v>21645</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>4041800.37</v>
+        <v>56278233</v>
       </c>
     </row>
     <row r="7">
@@ -30435,7 +30435,7 @@
         <v>156006</v>
       </c>
       <c r="H7" t="n">
-        <v>13107150</v>
+        <v>15603750</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -30447,7 +30447,7 @@
         <v>154893.64</v>
       </c>
       <c r="L7" t="n">
-        <v>5009040</v>
+        <v>5449680</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -30456,13 +30456,13 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>894285</v>
+        <v>1092420</v>
       </c>
       <c r="P7" t="n">
-        <v>51187.5</v>
+        <v>5850</v>
       </c>
       <c r="Q7" t="n">
-        <v>2174363.14</v>
+        <v>30275942.4</v>
       </c>
     </row>
     <row r="8">
@@ -30488,7 +30488,7 @@
         <v>24219</v>
       </c>
       <c r="H8" t="n">
-        <v>2470950</v>
+        <v>3197700</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -30500,7 +30500,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>897156</v>
+        <v>1111860</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -30509,13 +30509,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>479655</v>
+        <v>750465</v>
       </c>
       <c r="P8" t="n">
-        <v>120783</v>
+        <v>24453</v>
       </c>
       <c r="Q8" t="n">
-        <v>144884.02</v>
+        <v>2017372.5</v>
       </c>
     </row>
     <row r="9">
@@ -30541,7 +30541,7 @@
         <v>6885</v>
       </c>
       <c r="H9" t="n">
-        <v>513000</v>
+        <v>1026000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -30553,7 +30553,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>258066</v>
+        <v>411156</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -30562,13 +30562,13 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>255255</v>
+        <v>827475</v>
       </c>
       <c r="P9" t="n">
-        <v>162825</v>
+        <v>115050</v>
       </c>
       <c r="Q9" t="n">
-        <v>23214.29</v>
+        <v>323236.98</v>
       </c>
     </row>
     <row r="10">
@@ -30594,7 +30594,7 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>342000</v>
+        <v>513000</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -30606,7 +30606,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>67284</v>
+        <v>374868</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -30615,13 +30615,13 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>53550</v>
+        <v>349860</v>
       </c>
       <c r="P10" t="n">
-        <v>321555</v>
+        <v>497250</v>
       </c>
       <c r="Q10" t="n">
-        <v>11518.2</v>
+        <v>160380</v>
       </c>
     </row>
     <row r="11">
@@ -30647,7 +30647,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>1539000</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -30659,7 +30659,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>27000</v>
+        <v>313200</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -30668,13 +30668,13 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>17340</v>
       </c>
       <c r="P11" t="n">
-        <v>156195</v>
+        <v>386100</v>
       </c>
       <c r="Q11" t="n">
-        <v>2772.9</v>
+        <v>38610</v>
       </c>
     </row>
     <row r="12">
@@ -30700,7 +30700,7 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>171000</v>
+        <v>855000</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -30712,7 +30712,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>5400</v>
+        <v>221400</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -30724,10 +30724,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>115050</v>
+        <v>372450</v>
       </c>
       <c r="Q12" t="n">
-        <v>298.62</v>
+        <v>4158</v>
       </c>
     </row>
     <row r="13">
@@ -30765,7 +30765,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>70200</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -30777,10 +30777,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>27300</v>
+        <v>101400</v>
       </c>
       <c r="Q13" t="n">
-        <v>127.98</v>
+        <v>1782</v>
       </c>
     </row>
     <row r="14">
@@ -30818,7 +30818,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>10800</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -30830,7 +30830,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1950</v>
+        <v>21450</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
